--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP100" headerRowCount="1">
-  <autoFilter ref="A1:EP100"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP101" headerRowCount="1">
+  <autoFilter ref="A1:EP101"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP100"/>
+  <dimension ref="A1:EP101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2781,7 +2781,7 @@
         <v>0.83</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DE12" t="n">
         <v>1</v>
@@ -12773,7 +12773,7 @@
         <v>1.67</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -14694,7 +14694,7 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DE29" t="n">
         <v>0.8</v>
@@ -19481,7 +19481,7 @@
         <v>1.33</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF39" t="n">
         <v>0.5</v>
@@ -24706,7 +24706,7 @@
         <v>100</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DE50" t="n">
         <v>1.2</v>
@@ -29021,7 +29021,7 @@
         <v>0.83</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF59" t="n">
         <v>0.33</v>
@@ -33770,7 +33770,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DE69" t="n">
         <v>0.8</v>
@@ -36645,7 +36645,7 @@
         <v>1.17</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF75" t="n">
         <v>1</v>
@@ -41119,170 +41119,170 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
         <v>45962.75</v>
       </c>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I85" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M85" t="n">
         <v>2</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>6</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T85" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="U85" t="n">
+        <v>2</v>
+      </c>
+      <c r="V85" t="n">
+        <v>24</v>
+      </c>
+      <c r="W85" t="n">
         <v>10</v>
       </c>
-      <c r="V85" t="n">
-        <v>12</v>
-      </c>
-      <c r="W85" t="n">
-        <v>20</v>
-      </c>
       <c r="X85" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y85" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="Z85" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Campo do Cevadeiro</t>
+          <t>Estádio do Rio Ave Futebol Clube</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Estrada Nacional 10, Vila Franca de Xira</t>
+          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE85" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AG85" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AI85" t="n">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="AJ85" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="AK85" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AL85" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AM85" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AN85" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AO85" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AR85" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AS85" t="n">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AU85" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW85" t="n">
         <v>2</v>
       </c>
       <c r="AX85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BA85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB85" t="n">
-        <v>15804</v>
+        <v>164</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -41297,76 +41297,76 @@
         <v>1</v>
       </c>
       <c r="BI85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ85" t="n">
         <v>2</v>
       </c>
       <c r="BR85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU85" t="n">
         <v>1</v>
       </c>
       <c r="BV85" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="BW85" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="BX85" t="n">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="BY85" t="n">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="BZ85" t="n">
-        <v>1.2</v>
+        <v>0.22</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.32</v>
+        <v>2.37</v>
       </c>
       <c r="CB85" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="CC85" t="n">
         <v>0</v>
       </c>
       <c r="CD85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CE85" t="n">
         <v>0</v>
       </c>
       <c r="CF85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CG85" t="n">
         <v>0</v>
@@ -41387,10 +41387,10 @@
         <v>0</v>
       </c>
       <c r="CM85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CN85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO85" t="n">
         <v>0</v>
@@ -41402,73 +41402,73 @@
         <v>1</v>
       </c>
       <c r="CR85" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CS85" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CT85" t="n">
         <v>1</v>
       </c>
       <c r="CU85" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CV85" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CW85" t="n">
         <v>1</v>
       </c>
       <c r="CX85" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CY85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CZ85" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="DA85" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB85" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DC85" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="DD85" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG85" t="n">
         <v>0.5</v>
       </c>
-      <c r="DG85" t="n">
-        <v>0.75</v>
-      </c>
       <c r="DH85" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="DI85" t="n">
         <v>0.78</v>
       </c>
       <c r="DJ85" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="DK85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL85" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="DN85" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="DO85" t="n">
         <v>11</v>
@@ -41486,23 +41486,23 @@
         <v>1</v>
       </c>
       <c r="DT85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW85" t="n">
-        <v>20.42</v>
+        <v>15.06</v>
       </c>
       <c r="DX85" t="n">
-        <v>8.41</v>
+        <v>4.25</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
@@ -41512,74 +41512,82 @@
       </c>
       <c r="EA85" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EB85" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EC85" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EG85" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH85" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EM85" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EN85" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EO85" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EP85" t="inlineStr">
+        <is>
           <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED85" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EE85" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF85" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EG85" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH85" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI85" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EJ85" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
-      </c>
-      <c r="EK85" t="inlineStr"/>
-      <c r="EL85" t="inlineStr"/>
-      <c r="EM85" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EN85" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="EO85" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EP85" t="inlineStr">
-        <is>
-          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -41599,170 +41607,170 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
         <v>45962.75</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H86" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>8</v>
+      </c>
+      <c r="J86" t="n">
+        <v>5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>2</v>
+      </c>
+      <c r="L86" t="n">
+        <v>7</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
         <v>4</v>
-      </c>
-      <c r="I86" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>6</v>
-      </c>
-      <c r="L86" t="n">
-        <v>6</v>
-      </c>
-      <c r="M86" t="n">
-        <v>2</v>
-      </c>
-      <c r="N86" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>6</v>
       </c>
       <c r="S86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V86" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="X86" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y86" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="Z86" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Estádio do Rio Ave Futebol Clube</t>
+          <t>Campo do Cevadeiro</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
+          <t>Estrada Nacional 10, Vila Franca de Xira</t>
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE86" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AF86" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AG86" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH86" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT86" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI86" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ86" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AK86" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL86" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM86" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN86" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO86" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AP86" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ86" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR86" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS86" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AT86" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AU86" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW86" t="n">
         <v>2</v>
       </c>
       <c r="AX86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BA86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB86" t="n">
-        <v>164</v>
+        <v>15804</v>
       </c>
       <c r="BC86" t="n">
         <v>0</v>
       </c>
       <c r="BD86" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="BE86" t="n">
         <v>0</v>
@@ -41777,76 +41785,76 @@
         <v>1</v>
       </c>
       <c r="BI86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ86" t="n">
         <v>2</v>
       </c>
       <c r="BR86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU86" t="n">
         <v>1</v>
       </c>
       <c r="BV86" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BW86" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="BX86" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="BY86" t="n">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="BZ86" t="n">
-        <v>0.22</v>
+        <v>1.2</v>
       </c>
       <c r="CA86" t="n">
-        <v>2.37</v>
+        <v>1.32</v>
       </c>
       <c r="CB86" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="CC86" t="n">
         <v>0</v>
       </c>
       <c r="CD86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE86" t="n">
         <v>0</v>
       </c>
       <c r="CF86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CG86" t="n">
         <v>0</v>
@@ -41867,10 +41875,10 @@
         <v>0</v>
       </c>
       <c r="CM86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CN86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO86" t="n">
         <v>0</v>
@@ -41882,73 +41890,73 @@
         <v>1</v>
       </c>
       <c r="CR86" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS86" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU86" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV86" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX86" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY86" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ86" t="n">
         <v>13</v>
       </c>
-      <c r="CS86" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU86" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV86" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX86" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CZ86" t="n">
+      <c r="DA86" t="n">
         <v>75</v>
       </c>
-      <c r="DA86" t="n">
-        <v>100</v>
-      </c>
       <c r="DB86" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC86" t="n">
         <v>63</v>
       </c>
-      <c r="DC86" t="n">
-        <v>100</v>
-      </c>
       <c r="DD86" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="DE86" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF86" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="DG86" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="DH86" t="n">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="DI86" t="n">
         <v>0.78</v>
       </c>
       <c r="DJ86" t="n">
+        <v>88</v>
+      </c>
+      <c r="DK86" t="n">
         <v>25</v>
       </c>
-      <c r="DK86" t="n">
-        <v>0</v>
-      </c>
       <c r="DL86" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="DM86" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="DN86" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="DO86" t="n">
         <v>11</v>
@@ -41966,23 +41974,23 @@
         <v>1</v>
       </c>
       <c r="DT86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW86" t="n">
-        <v>15.06</v>
+        <v>20.42</v>
       </c>
       <c r="DX86" t="n">
-        <v>4.25</v>
+        <v>8.41</v>
       </c>
       <c r="DY86" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ86" t="inlineStr">
@@ -41992,82 +42000,74 @@
       </c>
       <c r="EA86" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EB86" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EC86" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="ED86" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EE86" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EF86" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EG86" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EH86" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI86" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EJ86" t="inlineStr">
         <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EK86" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EL86" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="EK86" t="inlineStr"/>
+      <c r="EL86" t="inlineStr"/>
       <c r="EM86" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EN86" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EO86" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EP86" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -42406,7 +42406,7 @@
         <v>75</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DE87" t="n">
         <v>2.6</v>
@@ -46399,12 +46399,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
@@ -46420,111 +46420,119 @@
         <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L96" t="n">
+        <v>5</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
         <v>8</v>
       </c>
-      <c r="M96" t="n">
-        <v>3</v>
-      </c>
-      <c r="N96" t="n">
-        <v>4</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>4</v>
-      </c>
       <c r="R96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T96" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U96" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V96" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="W96" t="n">
         <v>12</v>
       </c>
       <c r="X96" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y96" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="Z96" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Estádio Clube Desportivo das Aves</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
+        </is>
+      </c>
       <c r="AC96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.42</v>
+        <v>5.75</v>
       </c>
       <c r="AF96" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.96</v>
+        <v>1.63</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI96" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AJ96" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AK96" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AL96" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AM96" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AN96" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AO96" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR96" t="n">
         <v>3.22</v>
       </c>
       <c r="AS96" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AT96" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU96" t="n">
         <v>2</v>
@@ -46554,7 +46562,7 @@
         <v>0</v>
       </c>
       <c r="BD96" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE96" t="n">
         <v>0</v>
@@ -46572,175 +46580,175 @@
         <v>1</v>
       </c>
       <c r="BJ96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM96" t="n">
         <v>5</v>
       </c>
-      <c r="BK96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM96" t="n">
+      <c r="BN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
         <v>6</v>
       </c>
-      <c r="BN96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT96" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV96" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW96" t="n">
-        <v>44</v>
-      </c>
-      <c r="BX96" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY96" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ96" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CA96" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB96" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="CC96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR96" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS96" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU96" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV96" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX96" t="n">
-        <v>7</v>
-      </c>
       <c r="CY96" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CZ96" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DA96" t="n">
         <v>70</v>
       </c>
       <c r="DB96" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DC96" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="DF96" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="DG96" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DH96" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DI96" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="DJ96" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="DK96" t="n">
         <v>30</v>
       </c>
       <c r="DL96" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="DM96" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="DN96" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="DO96" t="n">
         <v>11</v>
@@ -46767,67 +46775,87 @@
         <v>1</v>
       </c>
       <c r="DW96" t="n">
-        <v>16.49</v>
+        <v>16.28</v>
       </c>
       <c r="DX96" t="n">
-        <v>2.95</v>
+        <v>1.64</v>
       </c>
       <c r="DY96" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ96" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA96" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EB96" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="EC96" t="inlineStr">
         <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG96" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH96" t="inlineStr"/>
+      <c r="EI96" t="inlineStr"/>
+      <c r="EJ96" t="inlineStr"/>
+      <c r="EK96" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM96" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EO96" t="inlineStr">
+        <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="ED96" t="inlineStr"/>
-      <c r="EE96" t="inlineStr"/>
-      <c r="EF96" t="inlineStr"/>
-      <c r="EG96" t="inlineStr"/>
-      <c r="EH96" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EI96" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EJ96" t="inlineStr">
-        <is>
-          <t>4.24</t>
-        </is>
-      </c>
-      <c r="EK96" t="inlineStr"/>
-      <c r="EL96" t="inlineStr"/>
-      <c r="EM96" t="inlineStr"/>
-      <c r="EN96" t="inlineStr"/>
-      <c r="EO96" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
       <c r="EP96" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
@@ -46847,12 +46875,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
@@ -46868,20 +46896,20 @@
         <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
+        <v>6</v>
+      </c>
+      <c r="L97" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3</v>
+      </c>
+      <c r="N97" t="n">
         <v>4</v>
       </c>
-      <c r="L97" t="n">
-        <v>5</v>
-      </c>
-      <c r="M97" t="n">
-        <v>1</v>
-      </c>
-      <c r="N97" t="n">
-        <v>5</v>
-      </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
@@ -46889,98 +46917,90 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T97" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U97" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V97" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W97" t="n">
         <v>12</v>
       </c>
       <c r="X97" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y97" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="Z97" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Estádio Clube Desportivo das Aves</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE97" t="n">
-        <v>5.75</v>
+        <v>2.42</v>
       </c>
       <c r="AF97" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI97" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AJ97" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AK97" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AL97" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AN97" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AO97" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AR97" t="n">
         <v>3.22</v>
       </c>
       <c r="AS97" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AT97" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU97" t="n">
         <v>2</v>
@@ -47010,7 +47030,7 @@
         <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE97" t="n">
         <v>0</v>
@@ -47028,70 +47048,70 @@
         <v>1</v>
       </c>
       <c r="BJ97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT97" t="n">
         <v>4</v>
       </c>
-      <c r="BK97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM97" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR97" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT97" t="n">
-        <v>5</v>
-      </c>
       <c r="BU97" t="n">
         <v>1</v>
       </c>
       <c r="BV97" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW97" t="n">
         <v>44</v>
       </c>
-      <c r="BW97" t="n">
-        <v>47</v>
-      </c>
       <c r="BX97" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BY97" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="BZ97" t="n">
-        <v>1.88</v>
+        <v>1.37</v>
       </c>
       <c r="CA97" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="CC97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD97" t="n">
         <v>0</v>
       </c>
       <c r="CE97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF97" t="n">
         <v>0</v>
@@ -47112,13 +47132,13 @@
         <v>0</v>
       </c>
       <c r="CL97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM97" t="n">
         <v>0</v>
       </c>
       <c r="CN97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CO97" t="n">
         <v>0</v>
@@ -47130,73 +47150,73 @@
         <v>1</v>
       </c>
       <c r="CR97" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CS97" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CT97" t="n">
         <v>1</v>
       </c>
       <c r="CU97" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV97" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX97" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY97" t="n">
         <v>11</v>
       </c>
-      <c r="CW97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX97" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY97" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ97" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DA97" t="n">
         <v>70</v>
       </c>
       <c r="DB97" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DC97" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD97" t="n">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="DF97" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG97" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="DH97" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="DI97" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="DJ97" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="DK97" t="n">
         <v>30</v>
       </c>
       <c r="DL97" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="DM97" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="DN97" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="DO97" t="n">
         <v>11</v>
@@ -47223,87 +47243,67 @@
         <v>1</v>
       </c>
       <c r="DW97" t="n">
-        <v>16.28</v>
+        <v>16.49</v>
       </c>
       <c r="DX97" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="DY97" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="DZ97" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA97" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EB97" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EC97" t="inlineStr">
         <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="ED97" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EE97" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EF97" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG97" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EH97" t="inlineStr"/>
-      <c r="EI97" t="inlineStr"/>
-      <c r="EJ97" t="inlineStr"/>
-      <c r="EK97" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EL97" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EM97" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EN97" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr"/>
+      <c r="EE97" t="inlineStr"/>
+      <c r="EF97" t="inlineStr"/>
+      <c r="EG97" t="inlineStr"/>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EK97" t="inlineStr"/>
+      <c r="EL97" t="inlineStr"/>
+      <c r="EM97" t="inlineStr"/>
+      <c r="EN97" t="inlineStr"/>
       <c r="EO97" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EP97" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -48728,6 +48728,462 @@
       <c r="EP100" t="inlineStr">
         <is>
           <t>1.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>12</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Vitória Guimarães</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AVS</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>45989.84375</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>4</v>
+      </c>
+      <c r="J101" t="n">
+        <v>7</v>
+      </c>
+      <c r="K101" t="n">
+        <v>3</v>
+      </c>
+      <c r="L101" t="n">
+        <v>10</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>4</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>7</v>
+      </c>
+      <c r="T101" t="n">
+        <v>8</v>
+      </c>
+      <c r="U101" t="n">
+        <v>11</v>
+      </c>
+      <c r="V101" t="n">
+        <v>9</v>
+      </c>
+      <c r="W101" t="n">
+        <v>11</v>
+      </c>
+      <c r="X101" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Estádio Dom Afonso Henriques</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Rua de São Gonçalo 505, Guimarães</t>
+        </is>
+      </c>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>175</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX101" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY101" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>60</v>
+      </c>
+      <c r="DC101" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE101" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DI101" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DJ101" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL101" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM101" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DN101" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DO101" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW101" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="DX101" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ101" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="EA101" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="ED101" t="inlineStr"/>
+      <c r="EE101" t="inlineStr"/>
+      <c r="EF101" t="inlineStr"/>
+      <c r="EG101" t="inlineStr"/>
+      <c r="EH101" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EJ101" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="EK101" t="inlineStr"/>
+      <c r="EL101" t="inlineStr"/>
+      <c r="EM101" t="inlineStr"/>
+      <c r="EN101" t="inlineStr"/>
+      <c r="EO101" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EP101" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP108" headerRowCount="1">
-  <autoFilter ref="A1:EP108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP109" headerRowCount="1">
+  <autoFilter ref="A1:EP109"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP108"/>
+  <dimension ref="A1:EP109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE4" t="n">
         <v>0.17</v>
@@ -2811,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -8029,7 +8029,7 @@
         <v>1.17</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8059,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -11338,7 +11338,7 @@
         <v>50</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE22" t="n">
         <v>1.17</v>
@@ -11371,7 +11371,7 @@
         <v>1.05</v>
       </c>
       <c r="DO22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12803,7 +12803,7 @@
         <v>2.56</v>
       </c>
       <c r="DO25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -14727,7 +14727,7 @@
         <v>2.4</v>
       </c>
       <c r="DO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -16799,37 +16799,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45900.8125</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>8</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
         <v>2</v>
@@ -16844,116 +16844,108 @@
         <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T34" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V34" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="W34" t="n">
         <v>13</v>
       </c>
       <c r="X34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Z34" t="n">
-        <v>72</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Estádio do Rio Ave Futebol Clube</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
         <v>2</v>
       </c>
       <c r="AE34" t="n">
-        <v>4.36</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.81</v>
+        <v>3.96</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AL34" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AU34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
         <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
         <v>-1</v>
@@ -16977,37 +16969,37 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BM34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT34" t="n">
         <v>2</v>
@@ -17016,34 +17008,34 @@
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="BW34" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="BX34" t="n">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="BY34" t="n">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0.61</v>
+        <v>1.5</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.55</v>
+        <v>0.35</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.17</v>
+        <v>1.85</v>
       </c>
       <c r="CC34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD34" t="n">
         <v>0</v>
       </c>
       <c r="CE34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF34" t="n">
         <v>0</v>
@@ -17067,7 +17059,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -17082,10 +17074,10 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="CS34" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
@@ -17100,70 +17092,70 @@
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="CY34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA34" t="n">
         <v>50</v>
       </c>
-      <c r="DA34" t="n">
-        <v>100</v>
-      </c>
       <c r="DB34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC34" t="n">
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DH34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI34" t="n">
-        <v>2.33</v>
+        <v>0.67</v>
       </c>
       <c r="DJ34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK34" t="n">
         <v>50</v>
       </c>
-      <c r="DK34" t="n">
-        <v>0</v>
-      </c>
       <c r="DL34" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.54</v>
+        <v>1.12</v>
       </c>
       <c r="DN34" t="n">
-        <v>3.64</v>
+        <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT34" t="b">
         <v>0</v>
@@ -17172,102 +17164,86 @@
         <v>0</v>
       </c>
       <c r="DV34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW34" t="n">
-        <v>19.24</v>
+        <v>21.4</v>
       </c>
       <c r="DX34" t="n">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EK34" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EL34" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EM34" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EN34" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr"/>
+      <c r="EL34" t="inlineStr"/>
+      <c r="EM34" t="inlineStr"/>
+      <c r="EN34" t="inlineStr"/>
       <c r="EO34" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EP34" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -17287,37 +17263,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>45900.8125</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L35" t="n">
         <v>8</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
         <v>2</v>
@@ -17332,108 +17308,116 @@
         <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="U35" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="W35" t="n">
         <v>13</v>
       </c>
       <c r="X35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y35" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z35" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Estádio do Rio Ave Futebol Clube</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
+        </is>
+      </c>
       <c r="AC35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD35" t="n">
         <v>2</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>4.36</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.96</v>
+        <v>1.81</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="AJ35" t="n">
-        <v>5</v>
+        <v>3.12</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX35" t="n">
         <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB35" t="n">
         <v>-1</v>
@@ -17457,37 +17441,37 @@
         <v>1</v>
       </c>
       <c r="BI35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BM35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT35" t="n">
         <v>2</v>
@@ -17496,34 +17480,34 @@
         <v>1</v>
       </c>
       <c r="BV35" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="BW35" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="BX35" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="BY35" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1.5</v>
+        <v>0.61</v>
       </c>
       <c r="CA35" t="n">
-        <v>0.35</v>
+        <v>2.55</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="CC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD35" t="n">
         <v>0</v>
       </c>
       <c r="CE35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF35" t="n">
         <v>0</v>
@@ -17547,7 +17531,7 @@
         <v>0</v>
       </c>
       <c r="CM35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
@@ -17562,10 +17546,10 @@
         <v>1</v>
       </c>
       <c r="CR35" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="CS35" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="CT35" t="n">
         <v>1</v>
@@ -17580,70 +17564,70 @@
         <v>1</v>
       </c>
       <c r="CX35" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="CY35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CZ35" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA35" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB35" t="n">
         <v>50</v>
-      </c>
-      <c r="DB35" t="n">
-        <v>0</v>
       </c>
       <c r="DC35" t="n">
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DF35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI35" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
       <c r="DJ35" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK35" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL35" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="DM35" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="DN35" t="n">
-        <v>2.49</v>
+        <v>3.64</v>
       </c>
       <c r="DO35" t="n">
         <v>12</v>
       </c>
       <c r="DP35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT35" t="b">
         <v>0</v>
@@ -17652,86 +17636,102 @@
         <v>0</v>
       </c>
       <c r="DV35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW35" t="n">
-        <v>21.4</v>
+        <v>19.24</v>
       </c>
       <c r="DX35" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="DY35" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="DZ35" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA35" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EB35" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EC35" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="ED35" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EE35" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EF35" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EG35" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EH35" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI35" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EJ35" t="inlineStr">
         <is>
-          <t>6.16</t>
-        </is>
-      </c>
-      <c r="EK35" t="inlineStr"/>
-      <c r="EL35" t="inlineStr"/>
-      <c r="EM35" t="inlineStr"/>
-      <c r="EN35" t="inlineStr"/>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EK35" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EL35" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EM35" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EN35" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
       <c r="EO35" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EP35" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -19159,12 +19159,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -19180,19 +19180,19 @@
         <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -19201,122 +19201,122 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R39" t="n">
         <v>4</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
       </c>
       <c r="V39" t="n">
+        <v>15</v>
+      </c>
+      <c r="W39" t="n">
         <v>12</v>
       </c>
-      <c r="W39" t="n">
-        <v>11</v>
-      </c>
       <c r="X39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Z39" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Estádio António Coimbra da Mota</t>
+          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Rua Dom Bosco, Estoril</t>
+          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.42</v>
+        <v>3.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI39" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU39" t="n">
         <v>4</v>
       </c>
       <c r="AV39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY39" t="n">
         <v>1</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
@@ -19337,64 +19337,64 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM39" t="n">
         <v>2</v>
       </c>
       <c r="BN39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BO39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BP39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BT39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BW39" t="n">
         <v>39</v>
       </c>
       <c r="BX39" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BY39" t="n">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="CB39" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="CC39" t="n">
         <v>0</v>
@@ -19442,34 +19442,34 @@
         <v>1</v>
       </c>
       <c r="CR39" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS39" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU39" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX39" t="n">
         <v>10</v>
       </c>
-      <c r="CS39" t="n">
-        <v>31</v>
-      </c>
-      <c r="CT39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU39" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV39" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX39" t="n">
-        <v>17</v>
-      </c>
       <c r="CY39" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CZ39" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DA39" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB39" t="n">
         <v>25</v>
@@ -19478,37 +19478,37 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.33</v>
+        <v>2.17</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.17</v>
+        <v>1.17</v>
       </c>
       <c r="DF39" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DG39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DH39" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="DI39" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="DJ39" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK39" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL39" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="DM39" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="DN39" t="n">
-        <v>2.26</v>
+        <v>2.79</v>
       </c>
       <c r="DO39" t="n">
         <v>12</v>
@@ -19535,83 +19535,99 @@
         <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>20.1</v>
+        <v>22.33</v>
       </c>
       <c r="DX39" t="n">
-        <v>9.27</v>
+        <v>8.09</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="ED39" t="inlineStr"/>
-      <c r="EE39" t="inlineStr"/>
-      <c r="EF39" t="inlineStr"/>
-      <c r="EG39" t="inlineStr"/>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="ED39" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EE39" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EF39" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG39" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EI39" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -19631,12 +19647,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -19652,19 +19668,19 @@
         <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -19673,122 +19689,122 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
         <v>4</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U40" t="n">
         <v>15</v>
       </c>
       <c r="V40" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y40" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Z40" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
+          <t>Estádio António Coimbra da Mota</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
+          <t>Rua Dom Bosco, Estoril</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.25</v>
+        <v>4.42</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AR40" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU40" t="n">
         <v>4</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY40" t="n">
         <v>1</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB40" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
@@ -19809,64 +19825,64 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM40" t="n">
         <v>2</v>
       </c>
       <c r="BN40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BO40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BP40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BT40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BW40" t="n">
         <v>39</v>
       </c>
       <c r="BX40" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BY40" t="n">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="CB40" t="n">
-        <v>3.32</v>
+        <v>2.82</v>
       </c>
       <c r="CC40" t="n">
         <v>0</v>
@@ -19914,34 +19930,34 @@
         <v>1</v>
       </c>
       <c r="CR40" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CS40" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CV40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW40" t="n">
         <v>1</v>
       </c>
       <c r="CX40" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="CY40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ40" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA40" t="n">
         <v>75</v>
-      </c>
-      <c r="DA40" t="n">
-        <v>100</v>
       </c>
       <c r="DB40" t="n">
         <v>25</v>
@@ -19950,37 +19966,37 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.17</v>
+        <v>1.33</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
       <c r="DF40" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DG40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DH40" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="DI40" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="DJ40" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK40" t="n">
         <v>25</v>
       </c>
-      <c r="DK40" t="n">
-        <v>0</v>
-      </c>
       <c r="DL40" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="DM40" t="n">
-        <v>1.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DN40" t="n">
-        <v>2.79</v>
+        <v>2.26</v>
       </c>
       <c r="DO40" t="n">
         <v>12</v>
@@ -20007,99 +20023,83 @@
         <v>1</v>
       </c>
       <c r="DW40" t="n">
-        <v>22.33</v>
+        <v>20.1</v>
       </c>
       <c r="DX40" t="n">
-        <v>8.09</v>
+        <v>9.27</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="ED40" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EE40" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EF40" t="inlineStr">
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="ED40" t="inlineStr"/>
+      <c r="EE40" t="inlineStr"/>
+      <c r="EF40" t="inlineStr"/>
+      <c r="EG40" t="inlineStr"/>
+      <c r="EH40" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI40" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="EG40" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EH40" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EI40" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -21818,7 +21818,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE44" t="n">
         <v>1.17</v>
@@ -21851,7 +21851,7 @@
         <v>2.16</v>
       </c>
       <c r="DO44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22331,7 +22331,7 @@
         <v>3.35</v>
       </c>
       <c r="DO45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23771,7 +23771,7 @@
         <v>1.72</v>
       </c>
       <c r="DO48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24709,7 +24709,7 @@
         <v>1.83</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF50" t="n">
         <v>2</v>
@@ -24739,7 +24739,7 @@
         <v>3.53</v>
       </c>
       <c r="DO50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -30483,7 +30483,7 @@
         <v>2.74</v>
       </c>
       <c r="DO62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31402,7 +31402,7 @@
         <v>84</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE64" t="n">
         <v>3</v>
@@ -31435,7 +31435,7 @@
         <v>2.94</v>
       </c>
       <c r="DO64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32015,170 +32015,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="n">
         <v>5</v>
       </c>
-      <c r="J66" t="n">
-        <v>2</v>
-      </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L66" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
         <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>7</v>
       </c>
       <c r="R66" t="n">
+        <v>5</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8</v>
+      </c>
+      <c r="T66" t="n">
+        <v>10</v>
+      </c>
+      <c r="U66" t="n">
+        <v>15</v>
+      </c>
+      <c r="V66" t="n">
+        <v>15</v>
+      </c>
+      <c r="W66" t="n">
+        <v>13</v>
+      </c>
+      <c r="X66" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Estádio Cidade de Barcelos</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>strada Nacional 103, Vila Boa, Barcelos</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
         <v>4</v>
       </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="n">
-        <v>6</v>
-      </c>
-      <c r="U66" t="n">
-        <v>17</v>
-      </c>
-      <c r="V66" t="n">
-        <v>10</v>
-      </c>
-      <c r="W66" t="n">
-        <v>12</v>
-      </c>
-      <c r="X66" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
-      <c r="AC66" t="n">
-        <v>1</v>
-      </c>
       <c r="AD66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="AF66" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AG66" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AI66" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AN66" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AO66" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AR66" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AU66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
         <v>2</v>
       </c>
       <c r="BB66" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32193,73 +32193,73 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM66" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT66" t="n">
         <v>4</v>
       </c>
-      <c r="BN66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT66" t="n">
-        <v>3</v>
-      </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BW66" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="BX66" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="BY66" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BZ66" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="CB66" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="CC66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD66" t="n">
         <v>0</v>
       </c>
       <c r="CE66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF66" t="n">
         <v>0</v>
@@ -32280,10 +32280,10 @@
         <v>0</v>
       </c>
       <c r="CL66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN66" t="n">
         <v>0</v>
@@ -32298,73 +32298,73 @@
         <v>1</v>
       </c>
       <c r="CR66" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS66" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
       </c>
       <c r="CX66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY66" t="n">
         <v>8</v>
       </c>
       <c r="CZ66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA66" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DB66" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="n">
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DE66" t="n">
         <v>1</v>
       </c>
       <c r="DF66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DG66" t="n">
         <v>1</v>
       </c>
       <c r="DH66" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="DI66" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="DJ66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK66" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="DN66" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="DO66" t="n">
         <v>12</v>
@@ -32376,114 +32376,114 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU66" t="b">
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>24.96</v>
+        <v>25.52</v>
       </c>
       <c r="DX66" t="n">
-        <v>6.88</v>
+        <v>6.19</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EH66" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI66" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ66" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EK66" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EL66" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM66" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN66" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EO66" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP66" t="inlineStr">
+        <is>
           <t>1.72</t>
-        </is>
-      </c>
-      <c r="EH66" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI66" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ66" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="EK66" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="EL66" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EM66" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EN66" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EO66" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EP66" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -32503,170 +32503,170 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>7</v>
       </c>
       <c r="R67" t="n">
+        <v>4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="n">
+        <v>6</v>
+      </c>
+      <c r="U67" t="n">
+        <v>17</v>
+      </c>
+      <c r="V67" t="n">
+        <v>10</v>
+      </c>
+      <c r="W67" t="n">
+        <v>12</v>
+      </c>
+      <c r="X67" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="n">
         <v>5</v>
       </c>
-      <c r="S67" t="n">
-        <v>8</v>
-      </c>
-      <c r="T67" t="n">
-        <v>10</v>
-      </c>
-      <c r="U67" t="n">
-        <v>15</v>
-      </c>
-      <c r="V67" t="n">
-        <v>15</v>
-      </c>
-      <c r="W67" t="n">
-        <v>13</v>
-      </c>
-      <c r="X67" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Estádio Cidade de Barcelos</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>strada Nacional 103, Vila Boa, Barcelos</t>
-        </is>
-      </c>
-      <c r="AC67" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>3</v>
-      </c>
       <c r="AE67" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="AF67" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AG67" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI67" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ67" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AK67" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AL67" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AN67" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AO67" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR67" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AS67" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AU67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
       </c>
       <c r="BB67" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32681,178 +32681,178 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM67" t="n">
         <v>4</v>
       </c>
-      <c r="BJ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL67" t="n">
+      <c r="BN67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC67" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE67" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX67" t="n">
         <v>6</v>
-      </c>
-      <c r="BM67" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN67" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ67" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT67" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV67" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW67" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX67" t="n">
-        <v>83</v>
-      </c>
-      <c r="BY67" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ67" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA67" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CB67" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CC67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR67" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS67" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU67" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV67" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX67" t="n">
-        <v>8</v>
       </c>
       <c r="CY67" t="n">
         <v>8</v>
       </c>
       <c r="CZ67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA67" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DB67" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DC67" t="n">
         <v>50</v>
       </c>
       <c r="DD67" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DE67" t="n">
         <v>1</v>
       </c>
       <c r="DF67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DG67" t="n">
         <v>1</v>
       </c>
       <c r="DH67" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="DI67" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DJ67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK67" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="DM67" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="DN67" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="DO67" t="n">
         <v>12</v>
@@ -32864,69 +32864,69 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU67" t="b">
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW67" t="n">
-        <v>25.52</v>
+        <v>24.96</v>
       </c>
       <c r="DX67" t="n">
-        <v>6.19</v>
+        <v>6.88</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EA67" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EB67" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EC67" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="ED67" t="inlineStr">
         <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EE67" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF67" t="inlineStr">
+        <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="EE67" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EF67" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
@@ -32936,42 +32936,42 @@
       </c>
       <c r="EI67" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EJ67" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="EK67" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EL67" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM67" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EN67" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EO67" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP67" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -34250,7 +34250,7 @@
         <v>50</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE70" t="n">
         <v>2</v>
@@ -34283,7 +34283,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35197,7 +35197,7 @@
         <v>2.17</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF72" t="n">
         <v>2</v>
@@ -35227,7 +35227,7 @@
         <v>4.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36811,41 +36811,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45955.8125</v>
       </c>
       <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" t="n">
         <v>5</v>
       </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
+      <c r="L76" t="n">
+        <v>9</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
         <v>5</v>
       </c>
-      <c r="J76" t="n">
-        <v>9</v>
-      </c>
-      <c r="K76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" t="n">
-        <v>10</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2</v>
-      </c>
-      <c r="N76" t="n">
-        <v>2</v>
-      </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
@@ -36853,34 +36853,34 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
+        <v>2</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2</v>
+      </c>
+      <c r="S76" t="n">
+        <v>14</v>
+      </c>
+      <c r="T76" t="n">
+        <v>6</v>
+      </c>
+      <c r="U76" t="n">
+        <v>16</v>
+      </c>
+      <c r="V76" t="n">
         <v>8</v>
       </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>9</v>
-      </c>
-      <c r="T76" t="n">
-        <v>5</v>
-      </c>
-      <c r="U76" t="n">
-        <v>17</v>
-      </c>
-      <c r="V76" t="n">
-        <v>5</v>
-      </c>
       <c r="W76" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X76" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y76" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Z76" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
@@ -36888,85 +36888,85 @@
         <v>2</v>
       </c>
       <c r="AD76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="AF76" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="AG76" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.08</v>
+        <v>3.54</v>
       </c>
       <c r="AK76" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL76" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AN76" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.41</v>
+        <v>2.19</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AS76" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AU76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW76" t="n">
         <v>0</v>
       </c>
       <c r="AX76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ76" t="n">
         <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB76" t="n">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36981,73 +36981,73 @@
         <v>1</v>
       </c>
       <c r="BI76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN76" t="n">
         <v>6</v>
       </c>
       <c r="BO76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU76" t="n">
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="BW76" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="BX76" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="BY76" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="BZ76" t="n">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="CA76" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="CB76" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="CC76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD76" t="n">
         <v>0</v>
       </c>
       <c r="CE76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF76" t="n">
         <v>0</v>
@@ -37065,13 +37065,13 @@
         <v>1</v>
       </c>
       <c r="CK76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL76" t="n">
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN76" t="n">
         <v>0</v>
@@ -37080,82 +37080,82 @@
         <v>0</v>
       </c>
       <c r="CP76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ76" t="n">
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="CS76" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY76" t="n">
         <v>15</v>
       </c>
-      <c r="CV76" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX76" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY76" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ76" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DA76" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB76" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="DC76" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DD76" t="n">
-        <v>2</v>
+        <v>0.83</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="DF76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DG76" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DH76" t="n">
-        <v>2.25</v>
+        <v>0.88</v>
       </c>
       <c r="DI76" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DJ76" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DK76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL76" t="n">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="DM76" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="DN76" t="n">
-        <v>3.06</v>
+        <v>2.46</v>
       </c>
       <c r="DO76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37167,103 +37167,111 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU76" t="b">
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW76" t="n">
-        <v>22.85</v>
+        <v>21.83</v>
       </c>
       <c r="DX76" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>13.66</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EG76" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EH76" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI76" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="EK76" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EL76" t="inlineStr">
         <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EM76" t="inlineStr"/>
-      <c r="EN76" t="inlineStr"/>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EM76" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN76" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
       <c r="EO76" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EP76" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -37283,76 +37291,76 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
         <v>45955.8125</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>10</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>8</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>9</v>
+      </c>
+      <c r="T77" t="n">
         <v>5</v>
       </c>
-      <c r="L77" t="n">
-        <v>9</v>
-      </c>
-      <c r="M77" t="n">
-        <v>2</v>
-      </c>
-      <c r="N77" t="n">
+      <c r="U77" t="n">
+        <v>17</v>
+      </c>
+      <c r="V77" t="n">
         <v>5</v>
       </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>2</v>
-      </c>
-      <c r="R77" t="n">
-        <v>2</v>
-      </c>
-      <c r="S77" t="n">
-        <v>14</v>
-      </c>
-      <c r="T77" t="n">
-        <v>6</v>
-      </c>
-      <c r="U77" t="n">
-        <v>16</v>
-      </c>
-      <c r="V77" t="n">
-        <v>8</v>
-      </c>
       <c r="W77" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y77" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Z77" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
@@ -37360,85 +37368,85 @@
         <v>2</v>
       </c>
       <c r="AD77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AU77" t="n">
         <v>5</v>
       </c>
-      <c r="AE77" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL77" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>3</v>
-      </c>
       <c r="AV77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW77" t="n">
         <v>0</v>
       </c>
       <c r="AX77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ77" t="n">
         <v>2</v>
       </c>
       <c r="BA77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB77" t="n">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="BC77" t="n">
         <v>0</v>
       </c>
       <c r="BD77" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="BE77" t="n">
         <v>0</v>
@@ -37453,73 +37461,73 @@
         <v>1</v>
       </c>
       <c r="BI77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN77" t="n">
         <v>6</v>
       </c>
       <c r="BO77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU77" t="n">
         <v>1</v>
       </c>
       <c r="BV77" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="BW77" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="BX77" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="BY77" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="BZ77" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="CA77" t="n">
-        <v>0.85</v>
+        <v>0.61</v>
       </c>
       <c r="CB77" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="CC77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CD77" t="n">
         <v>0</v>
       </c>
       <c r="CE77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF77" t="n">
         <v>0</v>
@@ -37537,13 +37545,13 @@
         <v>1</v>
       </c>
       <c r="CK77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL77" t="n">
         <v>0</v>
       </c>
       <c r="CM77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
@@ -37552,79 +37560,79 @@
         <v>0</v>
       </c>
       <c r="CP77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ77" t="n">
         <v>1</v>
       </c>
       <c r="CR77" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="CS77" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CT77" t="n">
         <v>1</v>
       </c>
       <c r="CU77" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV77" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CW77" t="n">
         <v>1</v>
       </c>
       <c r="CX77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY77" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CZ77" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DA77" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB77" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="DC77" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DD77" t="n">
-        <v>0.83</v>
+        <v>2</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="DF77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DG77" t="n">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="DH77" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DI77" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL77" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DM77" t="n">
         <v>0.88</v>
       </c>
-      <c r="DI77" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ77" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK77" t="n">
-        <v>25</v>
-      </c>
-      <c r="DL77" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DM77" t="n">
-        <v>1.1</v>
-      </c>
       <c r="DN77" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="DO77" t="n">
         <v>12</v>
@@ -37639,111 +37647,103 @@
         <v>1</v>
       </c>
       <c r="DS77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU77" t="b">
         <v>0</v>
       </c>
       <c r="DV77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW77" t="n">
-        <v>21.83</v>
+        <v>22.85</v>
       </c>
       <c r="DX77" t="n">
-        <v>4.62</v>
+        <v>4.75</v>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>13.66</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="EC77" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EF77" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EG77" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EH77" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EI77" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ77" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EK77" t="inlineStr">
+        <is>
           <t>2.12</t>
         </is>
       </c>
-      <c r="EJ77" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="EK77" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
-      </c>
       <c r="EL77" t="inlineStr">
         <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EM77" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN77" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EM77" t="inlineStr"/>
+      <c r="EN77" t="inlineStr"/>
       <c r="EO77" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EP77" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.77</t>
         </is>
       </c>
     </row>
@@ -37763,170 +37763,162 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45956.64583333334</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>2</v>
       </c>
       <c r="J78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L78" t="n">
+        <v>9</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>10</v>
+      </c>
+      <c r="R78" t="n">
+        <v>3</v>
+      </c>
+      <c r="S78" t="n">
         <v>5</v>
       </c>
-      <c r="L78" t="n">
-        <v>11</v>
-      </c>
-      <c r="M78" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" t="n">
-        <v>3</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>4</v>
-      </c>
-      <c r="R78" t="n">
-        <v>4</v>
-      </c>
-      <c r="S78" t="n">
-        <v>9</v>
-      </c>
       <c r="T78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U78" t="n">
+        <v>15</v>
+      </c>
+      <c r="V78" t="n">
         <v>13</v>
       </c>
-      <c r="V78" t="n">
-        <v>9</v>
-      </c>
       <c r="W78" t="n">
+        <v>20</v>
+      </c>
+      <c r="X78" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>1033</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
         <v>13</v>
-      </c>
-      <c r="X78" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Estádio António Coimbra da Mota</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>Rua Dom Bosco, Estoril</t>
-        </is>
-      </c>
-      <c r="AC78" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB78" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>38</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37947,25 +37939,25 @@
         <v>2</v>
       </c>
       <c r="BK78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM78" t="n">
         <v>5</v>
       </c>
       <c r="BN78" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR78" t="n">
         <v>1</v>
@@ -37974,40 +37966,40 @@
         <v>2</v>
       </c>
       <c r="BT78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU78" t="n">
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="BW78" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="BX78" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="BY78" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="CB78" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="CC78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD78" t="n">
         <v>0</v>
       </c>
       <c r="CE78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF78" t="n">
         <v>0</v>
@@ -38031,7 +38023,7 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
@@ -38046,10 +38038,10 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CS78" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="CT78" t="n">
         <v>1</v>
@@ -38058,61 +38050,61 @@
         <v>14</v>
       </c>
       <c r="CV78" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="CW78" t="n">
         <v>1</v>
       </c>
       <c r="CX78" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CY78" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="CZ78" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="DA78" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DB78" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DC78" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DD78" t="n">
         <v>1.33</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DF78" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG78" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="DH78" t="n">
-        <v>0.75</v>
+        <v>1.63</v>
       </c>
       <c r="DI78" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DJ78" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DK78" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DL78" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="DM78" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="DN78" t="n">
-        <v>2.38</v>
+        <v>2.87</v>
       </c>
       <c r="DO78" t="n">
         <v>12</v>
@@ -38136,102 +38128,102 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW78" t="n">
-        <v>19.34</v>
+        <v>19.55</v>
       </c>
       <c r="DX78" t="n">
-        <v>4.82</v>
+        <v>3.46</v>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EC78" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="ED78" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EE78" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EF78" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EG78" t="inlineStr">
         <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="EH78" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EI78" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
       <c r="EJ78" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EK78" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EL78" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EM78" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EN78" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EO78" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EP78" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -38251,141 +38243,149 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45956.64583333334</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
         <v>2</v>
       </c>
       <c r="J79" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" t="n">
         <v>5</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
+        <v>11</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
         <v>4</v>
       </c>
-      <c r="L79" t="n">
+      <c r="R79" t="n">
+        <v>4</v>
+      </c>
+      <c r="S79" t="n">
         <v>9</v>
       </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>10</v>
-      </c>
-      <c r="R79" t="n">
-        <v>3</v>
-      </c>
-      <c r="S79" t="n">
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="T79" t="n">
-        <v>10</v>
-      </c>
       <c r="U79" t="n">
+        <v>13</v>
+      </c>
+      <c r="V79" t="n">
+        <v>9</v>
+      </c>
+      <c r="W79" t="n">
+        <v>13</v>
+      </c>
+      <c r="X79" t="n">
         <v>15</v>
       </c>
-      <c r="V79" t="n">
-        <v>13</v>
-      </c>
-      <c r="W79" t="n">
-        <v>20</v>
-      </c>
-      <c r="X79" t="n">
-        <v>14</v>
-      </c>
       <c r="Y79" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Z79" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Estádio António Coimbra da Mota</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Rua Dom Bosco, Estoril</t>
+        </is>
+      </c>
       <c r="AC79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE79" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP79" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF79" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH79" t="n">
+      <c r="AQ79" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI79" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AR79" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
         <v>2</v>
       </c>
       <c r="AV79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX79" t="n">
         <v>1</v>
@@ -38400,13 +38400,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>1033</v>
+        <v>-1</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38427,67 +38427,67 @@
         <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM79" t="n">
         <v>5</v>
       </c>
       <c r="BN79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT79" t="n">
         <v>4</v>
       </c>
-      <c r="BO79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>1</v>
-      </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="BW79" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="BX79" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="BY79" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="CB79" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="CC79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD79" t="n">
         <v>0</v>
       </c>
       <c r="CE79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF79" t="n">
         <v>0</v>
@@ -38511,7 +38511,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38526,10 +38526,10 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CS79" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
@@ -38538,61 +38538,61 @@
         <v>14</v>
       </c>
       <c r="CV79" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CY79" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CZ79" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="DA79" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB79" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DC79" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DD79" t="n">
         <v>1.33</v>
       </c>
       <c r="DE79" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI79" t="n">
         <v>1.25</v>
       </c>
-      <c r="DG79" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>1.38</v>
-      </c>
       <c r="DJ79" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DK79" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.87</v>
+        <v>2.38</v>
       </c>
       <c r="DO79" t="n">
         <v>12</v>
@@ -38616,102 +38616,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>19.55</v>
+        <v>19.34</v>
       </c>
       <c r="DX79" t="n">
-        <v>3.46</v>
+        <v>4.82</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EO79" t="inlineStr">
+        <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="ED79" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EE79" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="EK79" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN79" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EO79" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -43382,7 +43382,7 @@
         <v>65</v>
       </c>
       <c r="DD89" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DE89" t="n">
         <v>1</v>
@@ -43415,7 +43415,7 @@
         <v>1.91</v>
       </c>
       <c r="DO89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43873,7 +43873,7 @@
         <v>2.67</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DF90" t="n">
         <v>2.5</v>
@@ -43903,7 +43903,7 @@
         <v>3.54</v>
       </c>
       <c r="DO90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44871,7 +44871,7 @@
         <v>2.11</v>
       </c>
       <c r="DO92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -47803,12 +47803,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
@@ -47818,16 +47818,16 @@
         <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L99" t="n">
         <v>8</v>
@@ -47845,34 +47845,34 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S99" t="n">
+        <v>13</v>
+      </c>
+      <c r="T99" t="n">
+        <v>3</v>
+      </c>
+      <c r="U99" t="n">
+        <v>19</v>
+      </c>
+      <c r="V99" t="n">
+        <v>7</v>
+      </c>
+      <c r="W99" t="n">
         <v>8</v>
       </c>
-      <c r="T99" t="n">
-        <v>10</v>
-      </c>
-      <c r="U99" t="n">
-        <v>11</v>
-      </c>
-      <c r="V99" t="n">
-        <v>11</v>
-      </c>
-      <c r="W99" t="n">
-        <v>13</v>
-      </c>
       <c r="X99" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y99" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="Z99" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -47883,55 +47883,55 @@
         <v>2</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AF99" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AJ99" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AK99" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AL99" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AN99" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AS99" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AU99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV99" t="n">
         <v>1</v>
@@ -47943,22 +47943,22 @@
         <v>1</v>
       </c>
       <c r="AY99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA99" t="n">
         <v>1</v>
       </c>
       <c r="BB99" t="n">
-        <v>172</v>
+        <v>-1</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47973,64 +47973,64 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ99" t="n">
         <v>2</v>
       </c>
       <c r="BK99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT99" t="n">
         <v>4</v>
       </c>
-      <c r="BL99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN99" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT99" t="n">
-        <v>5</v>
-      </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="BW99" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="BX99" t="n">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="BY99" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.23</v>
+        <v>2.19</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="CB99" t="n">
-        <v>2.28</v>
+        <v>3.06</v>
       </c>
       <c r="CC99" t="n">
         <v>1</v>
@@ -48078,76 +48078,76 @@
         <v>1</v>
       </c>
       <c r="CR99" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CS99" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="CT99" t="n">
         <v>1</v>
       </c>
       <c r="CU99" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="CV99" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CW99" t="n">
         <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CY99" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="CZ99" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DA99" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="DB99" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DC99" t="n">
         <v>80</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DE99" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF99" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="DG99" t="n">
         <v>1.2</v>
       </c>
       <c r="DH99" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="DI99" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="DJ99" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DK99" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="DM99" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="DN99" t="n">
-        <v>2.42</v>
+        <v>3.17</v>
       </c>
       <c r="DO99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48159,7 +48159,7 @@
         <v>1</v>
       </c>
       <c r="DS99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT99" t="b">
         <v>0</v>
@@ -48171,99 +48171,83 @@
         <v>1</v>
       </c>
       <c r="DW99" t="n">
-        <v>16.36</v>
+        <v>17.32</v>
       </c>
       <c r="DX99" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EE99" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF99" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr"/>
+      <c r="EF99" t="inlineStr"/>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI99" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EJ99" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EM99" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EN99" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="inlineStr"/>
       <c r="EO99" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EP99" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
@@ -48283,12 +48267,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
@@ -48298,16 +48282,16 @@
         <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L100" t="n">
         <v>8</v>
@@ -48325,34 +48309,34 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
+        <v>8</v>
+      </c>
+      <c r="T100" t="n">
+        <v>10</v>
+      </c>
+      <c r="U100" t="n">
+        <v>11</v>
+      </c>
+      <c r="V100" t="n">
+        <v>11</v>
+      </c>
+      <c r="W100" t="n">
         <v>13</v>
       </c>
-      <c r="T100" t="n">
-        <v>3</v>
-      </c>
-      <c r="U100" t="n">
-        <v>19</v>
-      </c>
-      <c r="V100" t="n">
-        <v>7</v>
-      </c>
-      <c r="W100" t="n">
-        <v>8</v>
-      </c>
       <c r="X100" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y100" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="Z100" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -48363,55 +48347,55 @@
         <v>2</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AF100" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG100" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AI100" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM100" t="n">
         <v>1.62</v>
       </c>
-      <c r="AJ100" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AN100" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AU100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV100" t="n">
         <v>1</v>
@@ -48423,22 +48407,22 @@
         <v>1</v>
       </c>
       <c r="AY100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA100" t="n">
         <v>1</v>
       </c>
       <c r="BB100" t="n">
-        <v>-1</v>
+        <v>172</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48453,178 +48437,178 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ100" t="n">
         <v>2</v>
       </c>
       <c r="BK100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN100" t="n">
         <v>5</v>
       </c>
-      <c r="BN100" t="n">
-        <v>3</v>
-      </c>
       <c r="BO100" t="n">
         <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ100" t="n">
         <v>3</v>
       </c>
       <c r="BR100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="BW100" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
         <v>19</v>
       </c>
-      <c r="BX100" t="n">
-        <v>144</v>
-      </c>
-      <c r="BY100" t="n">
-        <v>55</v>
-      </c>
-      <c r="BZ100" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CA100" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>21</v>
-      </c>
       <c r="CS100" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="CT100" t="n">
         <v>1</v>
       </c>
       <c r="CU100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
         <v>7</v>
       </c>
-      <c r="CV100" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>1</v>
-      </c>
       <c r="CY100" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="CZ100" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DA100" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="DB100" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DC100" t="n">
         <v>80</v>
       </c>
       <c r="DD100" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF100" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG100" t="n">
         <v>1.2</v>
       </c>
       <c r="DH100" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="DI100" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="DJ100" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DK100" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DL100" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DN100" t="n">
-        <v>3.17</v>
+        <v>2.42</v>
       </c>
       <c r="DO100" t="n">
         <v>12</v>
@@ -48639,7 +48623,7 @@
         <v>1</v>
       </c>
       <c r="DS100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT100" t="b">
         <v>0</v>
@@ -48651,83 +48635,99 @@
         <v>1</v>
       </c>
       <c r="DW100" t="n">
-        <v>17.32</v>
+        <v>16.36</v>
       </c>
       <c r="DX100" t="n">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="EC100" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="ED100" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EE100" t="inlineStr"/>
-      <c r="EF100" t="inlineStr"/>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EK100" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EM100" t="inlineStr"/>
-      <c r="EN100" t="inlineStr"/>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EN100" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.72</t>
         </is>
       </c>
     </row>
@@ -49757,10 +49757,10 @@
         <v>22</v>
       </c>
       <c r="Y103" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z103" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
@@ -50230,13 +50230,13 @@
         <v>4</v>
       </c>
       <c r="T104" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U104" t="n">
         <v>6</v>
       </c>
       <c r="V104" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W104" t="n">
         <v>10</v>
@@ -50411,10 +50411,10 @@
         <v>0.71</v>
       </c>
       <c r="CA104" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="CB104" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="CC104" t="n">
         <v>0</v>
@@ -52157,10 +52157,10 @@
         <v>11</v>
       </c>
       <c r="Y108" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z108" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
@@ -52552,6 +52552,466 @@
       <c r="EP108" t="inlineStr">
         <is>
           <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>45992.84375</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>4</v>
+      </c>
+      <c r="I109" t="n">
+        <v>4</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>6</v>
+      </c>
+      <c r="L109" t="n">
+        <v>6</v>
+      </c>
+      <c r="M109" t="n">
+        <v>3</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6</v>
+      </c>
+      <c r="S109" t="n">
+        <v>2</v>
+      </c>
+      <c r="T109" t="n">
+        <v>12</v>
+      </c>
+      <c r="U109" t="n">
+        <v>3</v>
+      </c>
+      <c r="V109" t="n">
+        <v>18</v>
+      </c>
+      <c r="W109" t="n">
+        <v>11</v>
+      </c>
+      <c r="X109" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>84</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Estádio Municipal de Arouca</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>Afonso Pinto Magalhães Valdasna, Arouca</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>92</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL109" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DM109" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DN109" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DO109" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW109" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="DX109" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="DY109" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="ED109" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EE109" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EF109" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr"/>
+      <c r="EI109" t="inlineStr"/>
+      <c r="EJ109" t="inlineStr"/>
+      <c r="EK109" t="inlineStr"/>
+      <c r="EL109" t="inlineStr"/>
+      <c r="EM109" t="inlineStr"/>
+      <c r="EN109" t="inlineStr"/>
+      <c r="EO109" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EP109" t="inlineStr">
+        <is>
+          <t>1.88</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP109" headerRowCount="1">
-  <autoFilter ref="A1:EP109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP110" headerRowCount="1">
+  <autoFilter ref="A1:EP110"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP109"/>
+  <dimension ref="A1:EP110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>0.33</v>
       </c>
       <c r="DE2" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -10405,7 +10405,7 @@
         <v>0.5</v>
       </c>
       <c r="DE20" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10866,7 +10866,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE21" t="n">
         <v>1</v>
@@ -16799,37 +16799,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45900.8125</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L34" t="n">
         <v>8</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
         <v>2</v>
@@ -16844,108 +16844,116 @@
         <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="U34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V34" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="W34" t="n">
         <v>13</v>
       </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y34" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z34" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Estádio do Rio Ave Futebol Clube</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
+        </is>
+      </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD34" t="n">
         <v>2</v>
       </c>
       <c r="AE34" t="n">
-        <v>2</v>
+        <v>4.36</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.96</v>
+        <v>1.81</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="AJ34" t="n">
-        <v>5</v>
+        <v>3.12</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
         <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB34" t="n">
         <v>-1</v>
@@ -16969,37 +16977,37 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BM34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT34" t="n">
         <v>2</v>
@@ -17008,34 +17016,34 @@
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="BW34" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="BX34" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="BY34" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1.5</v>
+        <v>0.61</v>
       </c>
       <c r="CA34" t="n">
-        <v>0.35</v>
+        <v>2.55</v>
       </c>
       <c r="CB34" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="CC34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD34" t="n">
         <v>0</v>
       </c>
       <c r="CE34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF34" t="n">
         <v>0</v>
@@ -17059,7 +17067,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -17074,10 +17082,10 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="CS34" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
@@ -17092,70 +17100,70 @@
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="CY34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CZ34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB34" t="n">
         <v>50</v>
-      </c>
-      <c r="DB34" t="n">
-        <v>0</v>
       </c>
       <c r="DC34" t="n">
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DF34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI34" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
       <c r="DJ34" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.49</v>
+        <v>3.64</v>
       </c>
       <c r="DO34" t="n">
         <v>12</v>
       </c>
       <c r="DP34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT34" t="b">
         <v>0</v>
@@ -17164,86 +17172,102 @@
         <v>0</v>
       </c>
       <c r="DV34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW34" t="n">
-        <v>21.4</v>
+        <v>19.24</v>
       </c>
       <c r="DX34" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>6.16</t>
-        </is>
-      </c>
-      <c r="EK34" t="inlineStr"/>
-      <c r="EL34" t="inlineStr"/>
-      <c r="EM34" t="inlineStr"/>
-      <c r="EN34" t="inlineStr"/>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EL34" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EM34" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EN34" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
       <c r="EO34" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EP34" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -17263,37 +17287,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>45900.8125</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>8</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
         <v>2</v>
@@ -17308,116 +17332,108 @@
         <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V35" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
         <v>13</v>
       </c>
       <c r="X35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y35" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Z35" t="n">
-        <v>72</v>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Estádio do Rio Ave Futebol Clube</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
         <v>2</v>
       </c>
       <c r="AE35" t="n">
-        <v>4.36</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.81</v>
+        <v>3.96</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AL35" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="AO35" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
         <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
         <v>-1</v>
@@ -17441,37 +17457,37 @@
         <v>1</v>
       </c>
       <c r="BI35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BM35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT35" t="n">
         <v>2</v>
@@ -17480,34 +17496,34 @@
         <v>1</v>
       </c>
       <c r="BV35" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="BW35" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="BX35" t="n">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="BY35" t="n">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0.61</v>
+        <v>1.5</v>
       </c>
       <c r="CA35" t="n">
-        <v>2.55</v>
+        <v>0.35</v>
       </c>
       <c r="CB35" t="n">
-        <v>3.17</v>
+        <v>1.85</v>
       </c>
       <c r="CC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD35" t="n">
         <v>0</v>
       </c>
       <c r="CE35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF35" t="n">
         <v>0</v>
@@ -17531,7 +17547,7 @@
         <v>0</v>
       </c>
       <c r="CM35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
@@ -17546,10 +17562,10 @@
         <v>1</v>
       </c>
       <c r="CR35" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="CS35" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="CT35" t="n">
         <v>1</v>
@@ -17564,70 +17580,70 @@
         <v>1</v>
       </c>
       <c r="CX35" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="CY35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA35" t="n">
         <v>50</v>
       </c>
-      <c r="DA35" t="n">
-        <v>100</v>
-      </c>
       <c r="DB35" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC35" t="n">
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DF35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DH35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI35" t="n">
-        <v>2.33</v>
+        <v>0.67</v>
       </c>
       <c r="DJ35" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK35" t="n">
         <v>50</v>
       </c>
-      <c r="DK35" t="n">
-        <v>0</v>
-      </c>
       <c r="DL35" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="DM35" t="n">
-        <v>1.54</v>
+        <v>1.12</v>
       </c>
       <c r="DN35" t="n">
-        <v>3.64</v>
+        <v>2.49</v>
       </c>
       <c r="DO35" t="n">
         <v>12</v>
       </c>
       <c r="DP35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT35" t="b">
         <v>0</v>
@@ -17636,102 +17652,86 @@
         <v>0</v>
       </c>
       <c r="DV35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW35" t="n">
-        <v>19.24</v>
+        <v>21.4</v>
       </c>
       <c r="DX35" t="n">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="DY35" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="DZ35" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="EA35" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="EB35" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="EC35" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="ED35" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EE35" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EF35" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EG35" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EH35" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EI35" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EJ35" t="inlineStr">
         <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EK35" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EL35" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EM35" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EN35" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="EK35" t="inlineStr"/>
+      <c r="EL35" t="inlineStr"/>
+      <c r="EM35" t="inlineStr"/>
+      <c r="EN35" t="inlineStr"/>
       <c r="EO35" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EP35" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -18990,7 +18990,7 @@
         <v>75</v>
       </c>
       <c r="DD38" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE38" t="n">
         <v>0.83</v>
@@ -19159,12 +19159,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -19180,19 +19180,19 @@
         <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -19201,122 +19201,122 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
         <v>4</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
       </c>
       <c r="V39" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y39" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Z39" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
+          <t>Estádio António Coimbra da Mota</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
+          <t>Rua Dom Bosco, Estoril</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.25</v>
+        <v>4.42</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AJ39" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AR39" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU39" t="n">
         <v>4</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW39" t="n">
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY39" t="n">
         <v>1</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB39" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
@@ -19337,64 +19337,64 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM39" t="n">
         <v>2</v>
       </c>
       <c r="BN39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BO39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BP39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BT39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BW39" t="n">
         <v>39</v>
       </c>
       <c r="BX39" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BY39" t="n">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="CB39" t="n">
-        <v>3.32</v>
+        <v>2.82</v>
       </c>
       <c r="CC39" t="n">
         <v>0</v>
@@ -19442,34 +19442,34 @@
         <v>1</v>
       </c>
       <c r="CR39" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CS39" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CV39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW39" t="n">
         <v>1</v>
       </c>
       <c r="CX39" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="CY39" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ39" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA39" t="n">
         <v>75</v>
-      </c>
-      <c r="DA39" t="n">
-        <v>100</v>
       </c>
       <c r="DB39" t="n">
         <v>25</v>
@@ -19478,37 +19478,37 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.17</v>
+        <v>1.33</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
       <c r="DF39" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DG39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DH39" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="DI39" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="DJ39" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK39" t="n">
         <v>25</v>
       </c>
-      <c r="DK39" t="n">
-        <v>0</v>
-      </c>
       <c r="DL39" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="DM39" t="n">
-        <v>1.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DN39" t="n">
-        <v>2.79</v>
+        <v>2.26</v>
       </c>
       <c r="DO39" t="n">
         <v>12</v>
@@ -19535,99 +19535,83 @@
         <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>22.33</v>
+        <v>20.1</v>
       </c>
       <c r="DX39" t="n">
-        <v>8.09</v>
+        <v>9.27</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="ED39" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EE39" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EF39" t="inlineStr">
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="ED39" t="inlineStr"/>
+      <c r="EE39" t="inlineStr"/>
+      <c r="EF39" t="inlineStr"/>
+      <c r="EG39" t="inlineStr"/>
+      <c r="EH39" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI39" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="EG39" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EH39" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EI39" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -19647,12 +19631,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -19668,19 +19652,19 @@
         <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -19689,122 +19673,122 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R40" t="n">
         <v>4</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U40" t="n">
         <v>15</v>
       </c>
       <c r="V40" t="n">
+        <v>15</v>
+      </c>
+      <c r="W40" t="n">
         <v>12</v>
       </c>
-      <c r="W40" t="n">
-        <v>11</v>
-      </c>
       <c r="X40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y40" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Z40" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Estádio António Coimbra da Mota</t>
+          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Rua Dom Bosco, Estoril</t>
+          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.42</v>
+        <v>3.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI40" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU40" t="n">
         <v>4</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY40" t="n">
         <v>1</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
@@ -19825,64 +19809,64 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM40" t="n">
         <v>2</v>
       </c>
       <c r="BN40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BO40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BP40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BT40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BW40" t="n">
         <v>39</v>
       </c>
       <c r="BX40" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BY40" t="n">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="CB40" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="CC40" t="n">
         <v>0</v>
@@ -19930,34 +19914,34 @@
         <v>1</v>
       </c>
       <c r="CR40" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS40" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU40" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX40" t="n">
         <v>10</v>
       </c>
-      <c r="CS40" t="n">
-        <v>31</v>
-      </c>
-      <c r="CT40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU40" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV40" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX40" t="n">
-        <v>17</v>
-      </c>
       <c r="CY40" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CZ40" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DA40" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB40" t="n">
         <v>25</v>
@@ -19966,37 +19950,37 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.33</v>
+        <v>2.17</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.17</v>
+        <v>1.17</v>
       </c>
       <c r="DF40" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DG40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DH40" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="DI40" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="DJ40" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK40" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL40" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="DM40" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="DN40" t="n">
-        <v>2.26</v>
+        <v>2.79</v>
       </c>
       <c r="DO40" t="n">
         <v>12</v>
@@ -20023,83 +20007,99 @@
         <v>1</v>
       </c>
       <c r="DW40" t="n">
-        <v>20.1</v>
+        <v>22.33</v>
       </c>
       <c r="DX40" t="n">
-        <v>9.27</v>
+        <v>8.09</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="ED40" t="inlineStr"/>
-      <c r="EE40" t="inlineStr"/>
-      <c r="EF40" t="inlineStr"/>
-      <c r="EG40" t="inlineStr"/>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="ED40" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EE40" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EF40" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG40" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -20905,7 +20905,7 @@
         <v>1.33</v>
       </c>
       <c r="DE42" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="DF42" t="n">
         <v>2</v>
@@ -27106,7 +27106,7 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE55" t="n">
         <v>1.17</v>
@@ -27578,7 +27578,7 @@
         <v>50</v>
       </c>
       <c r="DD56" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE56" t="n">
         <v>1.83</v>
@@ -29493,7 +29493,7 @@
         <v>1.33</v>
       </c>
       <c r="DE60" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="DF60" t="n">
         <v>1.33</v>
@@ -37602,7 +37602,7 @@
         <v>59</v>
       </c>
       <c r="DD77" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DE77" t="n">
         <v>0.8</v>
@@ -37763,141 +37763,149 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45956.64583333334</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
         <v>2</v>
       </c>
       <c r="J78" t="n">
+        <v>6</v>
+      </c>
+      <c r="K78" t="n">
         <v>5</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
+        <v>11</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
         <v>4</v>
       </c>
-      <c r="L78" t="n">
+      <c r="R78" t="n">
+        <v>4</v>
+      </c>
+      <c r="S78" t="n">
         <v>9</v>
       </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" t="n">
-        <v>2</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>10</v>
-      </c>
-      <c r="R78" t="n">
-        <v>3</v>
-      </c>
-      <c r="S78" t="n">
+      <c r="T78" t="n">
         <v>5</v>
       </c>
-      <c r="T78" t="n">
-        <v>10</v>
-      </c>
       <c r="U78" t="n">
+        <v>13</v>
+      </c>
+      <c r="V78" t="n">
+        <v>9</v>
+      </c>
+      <c r="W78" t="n">
+        <v>13</v>
+      </c>
+      <c r="X78" t="n">
         <v>15</v>
       </c>
-      <c r="V78" t="n">
-        <v>13</v>
-      </c>
-      <c r="W78" t="n">
-        <v>20</v>
-      </c>
-      <c r="X78" t="n">
-        <v>14</v>
-      </c>
       <c r="Y78" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Z78" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Estádio António Coimbra da Mota</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Rua Dom Bosco, Estoril</t>
+        </is>
+      </c>
       <c r="AC78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE78" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP78" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF78" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH78" t="n">
+      <c r="AQ78" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI78" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AR78" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AS78" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AU78" t="n">
         <v>2</v>
       </c>
       <c r="AV78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX78" t="n">
         <v>1</v>
@@ -37912,13 +37920,13 @@
         <v>1</v>
       </c>
       <c r="BB78" t="n">
-        <v>1033</v>
+        <v>-1</v>
       </c>
       <c r="BC78" t="n">
         <v>0</v>
       </c>
       <c r="BD78" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37939,67 +37947,67 @@
         <v>2</v>
       </c>
       <c r="BK78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM78" t="n">
         <v>5</v>
       </c>
       <c r="BN78" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT78" t="n">
         <v>4</v>
       </c>
-      <c r="BO78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS78" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT78" t="n">
-        <v>1</v>
-      </c>
       <c r="BU78" t="n">
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="BW78" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="BX78" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="BY78" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="CB78" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="CC78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD78" t="n">
         <v>0</v>
       </c>
       <c r="CE78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF78" t="n">
         <v>0</v>
@@ -38023,7 +38031,7 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
@@ -38038,10 +38046,10 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CS78" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="CT78" t="n">
         <v>1</v>
@@ -38050,61 +38058,61 @@
         <v>14</v>
       </c>
       <c r="CV78" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CW78" t="n">
         <v>1</v>
       </c>
       <c r="CX78" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CY78" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CZ78" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="DA78" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB78" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DC78" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DD78" t="n">
         <v>1.33</v>
       </c>
       <c r="DE78" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DF78" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI78" t="n">
         <v>1.25</v>
       </c>
-      <c r="DG78" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DH78" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DI78" t="n">
-        <v>1.38</v>
-      </c>
       <c r="DJ78" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DK78" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL78" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="DM78" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="DN78" t="n">
-        <v>2.87</v>
+        <v>2.38</v>
       </c>
       <c r="DO78" t="n">
         <v>12</v>
@@ -38128,102 +38136,102 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW78" t="n">
-        <v>19.55</v>
+        <v>19.34</v>
       </c>
       <c r="DX78" t="n">
-        <v>3.46</v>
+        <v>4.82</v>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EC78" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="ED78" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EE78" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EG78" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EJ78" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EK78" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EL78" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EM78" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EN78" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EO78" t="inlineStr">
+        <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="ED78" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EE78" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EF78" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EG78" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EH78" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EI78" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EJ78" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="EK78" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="EL78" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EM78" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN78" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EO78" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
       <c r="EP78" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -38243,170 +38251,162 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45956.64583333334</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K79" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" t="n">
+        <v>9</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>10</v>
+      </c>
+      <c r="R79" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" t="n">
         <v>5</v>
       </c>
-      <c r="L79" t="n">
-        <v>11</v>
-      </c>
-      <c r="M79" t="n">
-        <v>3</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>4</v>
-      </c>
-      <c r="R79" t="n">
-        <v>4</v>
-      </c>
-      <c r="S79" t="n">
-        <v>9</v>
-      </c>
       <c r="T79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U79" t="n">
+        <v>15</v>
+      </c>
+      <c r="V79" t="n">
         <v>13</v>
       </c>
-      <c r="V79" t="n">
-        <v>9</v>
-      </c>
       <c r="W79" t="n">
+        <v>20</v>
+      </c>
+      <c r="X79" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1033</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
         <v>13</v>
-      </c>
-      <c r="X79" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Estádio António Coimbra da Mota</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Rua Dom Bosco, Estoril</t>
-        </is>
-      </c>
-      <c r="AC79" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB79" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD79" t="n">
-        <v>38</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38427,25 +38427,25 @@
         <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
         <v>5</v>
       </c>
       <c r="BN79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR79" t="n">
         <v>1</v>
@@ -38454,40 +38454,40 @@
         <v>2</v>
       </c>
       <c r="BT79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="BW79" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="BX79" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="BY79" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="CC79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD79" t="n">
         <v>0</v>
       </c>
       <c r="CE79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF79" t="n">
         <v>0</v>
@@ -38511,7 +38511,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38526,10 +38526,10 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CS79" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
@@ -38538,61 +38538,61 @@
         <v>14</v>
       </c>
       <c r="CV79" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CY79" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="CZ79" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="DA79" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DB79" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DC79" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DD79" t="n">
         <v>1.33</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DF79" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG79" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.75</v>
+        <v>1.63</v>
       </c>
       <c r="DI79" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DJ79" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DK79" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.38</v>
+        <v>2.87</v>
       </c>
       <c r="DO79" t="n">
         <v>12</v>
@@ -38616,102 +38616,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>19.34</v>
+        <v>19.55</v>
       </c>
       <c r="DX79" t="n">
-        <v>4.82</v>
+        <v>3.46</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
         <v>0.4</v>
       </c>
       <c r="DE80" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="DF80" t="n">
         <v>0.67</v>
@@ -41119,170 +41119,170 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
         <v>45962.75</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" t="n">
+        <v>8</v>
+      </c>
+      <c r="J85" t="n">
+        <v>5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" t="n">
+        <v>7</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
         <v>4</v>
-      </c>
-      <c r="I85" t="n">
-        <v>4</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>6</v>
-      </c>
-      <c r="L85" t="n">
-        <v>6</v>
-      </c>
-      <c r="M85" t="n">
-        <v>2</v>
-      </c>
-      <c r="N85" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>6</v>
       </c>
       <c r="S85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T85" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="U85" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V85" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="X85" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y85" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="Z85" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Estádio do Rio Ave Futebol Clube</t>
+          <t>Campo do Cevadeiro</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
+          <t>Estrada Nacional 10, Vila Franca de Xira</t>
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE85" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AF85" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AG85" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH85" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT85" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI85" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR85" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS85" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AT85" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AU85" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW85" t="n">
         <v>2</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BA85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB85" t="n">
-        <v>164</v>
+        <v>15804</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -41297,76 +41297,76 @@
         <v>1</v>
       </c>
       <c r="BI85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ85" t="n">
         <v>2</v>
       </c>
       <c r="BR85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU85" t="n">
         <v>1</v>
       </c>
       <c r="BV85" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BW85" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="BX85" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="BY85" t="n">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="BZ85" t="n">
-        <v>0.22</v>
+        <v>1.2</v>
       </c>
       <c r="CA85" t="n">
-        <v>2.37</v>
+        <v>1.32</v>
       </c>
       <c r="CB85" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="CC85" t="n">
         <v>0</v>
       </c>
       <c r="CD85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE85" t="n">
         <v>0</v>
       </c>
       <c r="CF85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CG85" t="n">
         <v>0</v>
@@ -41387,10 +41387,10 @@
         <v>0</v>
       </c>
       <c r="CM85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CN85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO85" t="n">
         <v>0</v>
@@ -41402,73 +41402,73 @@
         <v>1</v>
       </c>
       <c r="CR85" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY85" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ85" t="n">
         <v>13</v>
       </c>
-      <c r="CS85" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU85" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV85" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX85" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CZ85" t="n">
+      <c r="DA85" t="n">
         <v>75</v>
       </c>
-      <c r="DA85" t="n">
-        <v>100</v>
-      </c>
       <c r="DB85" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC85" t="n">
         <v>63</v>
       </c>
-      <c r="DC85" t="n">
-        <v>100</v>
-      </c>
       <c r="DD85" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="DF85" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="DG85" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="DH85" t="n">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="DI85" t="n">
         <v>0.78</v>
       </c>
       <c r="DJ85" t="n">
+        <v>88</v>
+      </c>
+      <c r="DK85" t="n">
         <v>25</v>
       </c>
-      <c r="DK85" t="n">
-        <v>0</v>
-      </c>
       <c r="DL85" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="DN85" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="DO85" t="n">
         <v>12</v>
@@ -41486,23 +41486,23 @@
         <v>1</v>
       </c>
       <c r="DT85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW85" t="n">
-        <v>15.06</v>
+        <v>20.42</v>
       </c>
       <c r="DX85" t="n">
-        <v>4.25</v>
+        <v>8.41</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
@@ -41512,82 +41512,74 @@
       </c>
       <c r="EA85" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EB85" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EC85" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="ED85" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EE85" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EF85" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EG85" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EH85" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI85" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EJ85" t="inlineStr">
         <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EK85" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EL85" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr"/>
+      <c r="EL85" t="inlineStr"/>
       <c r="EM85" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EN85" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EO85" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EP85" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -41607,170 +41599,170 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
         <v>45962.75</v>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M86" t="n">
         <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>6</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T86" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="U86" t="n">
+        <v>2</v>
+      </c>
+      <c r="V86" t="n">
+        <v>24</v>
+      </c>
+      <c r="W86" t="n">
         <v>10</v>
       </c>
-      <c r="V86" t="n">
-        <v>12</v>
-      </c>
-      <c r="W86" t="n">
-        <v>20</v>
-      </c>
       <c r="X86" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y86" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="Z86" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Campo do Cevadeiro</t>
+          <t>Estádio do Rio Ave Futebol Clube</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Estrada Nacional 10, Vila Franca de Xira</t>
+          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE86" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AG86" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AI86" t="n">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="AJ86" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="AK86" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AL86" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AM86" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AN86" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AO86" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AR86" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AS86" t="n">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="AT86" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AU86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW86" t="n">
         <v>2</v>
       </c>
       <c r="AX86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BA86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB86" t="n">
-        <v>15804</v>
+        <v>164</v>
       </c>
       <c r="BC86" t="n">
         <v>0</v>
       </c>
       <c r="BD86" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="BE86" t="n">
         <v>0</v>
@@ -41785,76 +41777,76 @@
         <v>1</v>
       </c>
       <c r="BI86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ86" t="n">
         <v>2</v>
       </c>
       <c r="BR86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU86" t="n">
         <v>1</v>
       </c>
       <c r="BV86" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="BW86" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="BX86" t="n">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="BY86" t="n">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="BZ86" t="n">
-        <v>1.2</v>
+        <v>0.22</v>
       </c>
       <c r="CA86" t="n">
-        <v>1.32</v>
+        <v>2.37</v>
       </c>
       <c r="CB86" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="CC86" t="n">
         <v>0</v>
       </c>
       <c r="CD86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CE86" t="n">
         <v>0</v>
       </c>
       <c r="CF86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CG86" t="n">
         <v>0</v>
@@ -41875,10 +41867,10 @@
         <v>0</v>
       </c>
       <c r="CM86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CN86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO86" t="n">
         <v>0</v>
@@ -41890,73 +41882,73 @@
         <v>1</v>
       </c>
       <c r="CR86" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CS86" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CT86" t="n">
         <v>1</v>
       </c>
       <c r="CU86" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CV86" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CW86" t="n">
         <v>1</v>
       </c>
       <c r="CX86" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CY86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CZ86" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="DA86" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB86" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DC86" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="DD86" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DE86" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG86" t="n">
         <v>0.5</v>
       </c>
-      <c r="DG86" t="n">
-        <v>0.75</v>
-      </c>
       <c r="DH86" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="DI86" t="n">
         <v>0.78</v>
       </c>
       <c r="DJ86" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="DK86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL86" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="DM86" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="DN86" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="DO86" t="n">
         <v>12</v>
@@ -41974,23 +41966,23 @@
         <v>1</v>
       </c>
       <c r="DT86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW86" t="n">
-        <v>20.42</v>
+        <v>15.06</v>
       </c>
       <c r="DX86" t="n">
-        <v>8.41</v>
+        <v>4.25</v>
       </c>
       <c r="DY86" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="DZ86" t="inlineStr">
@@ -42000,74 +41992,82 @@
       </c>
       <c r="EA86" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EB86" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EC86" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="ED86" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EE86" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EF86" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EG86" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH86" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI86" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EJ86" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EK86" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EL86" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EM86" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EN86" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EO86" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EP86" t="inlineStr">
+        <is>
           <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED86" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EE86" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF86" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EG86" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH86" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI86" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EJ86" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
-      </c>
-      <c r="EK86" t="inlineStr"/>
-      <c r="EL86" t="inlineStr"/>
-      <c r="EM86" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EN86" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="EO86" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EP86" t="inlineStr">
-        <is>
-          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -46265,7 +46265,7 @@
         <v>1.17</v>
       </c>
       <c r="DE95" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="DF95" t="n">
         <v>1.4</v>
@@ -46399,12 +46399,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
@@ -46420,111 +46420,119 @@
         <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L96" t="n">
+        <v>5</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
         <v>8</v>
       </c>
-      <c r="M96" t="n">
-        <v>3</v>
-      </c>
-      <c r="N96" t="n">
-        <v>4</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>4</v>
-      </c>
       <c r="R96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T96" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U96" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V96" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="W96" t="n">
         <v>12</v>
       </c>
       <c r="X96" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y96" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="Z96" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Estádio Clube Desportivo das Aves</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
+        </is>
+      </c>
       <c r="AC96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.42</v>
+        <v>5.75</v>
       </c>
       <c r="AF96" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.96</v>
+        <v>1.63</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI96" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AJ96" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AK96" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AL96" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AM96" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AN96" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AO96" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR96" t="n">
         <v>3.22</v>
       </c>
       <c r="AS96" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AT96" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU96" t="n">
         <v>2</v>
@@ -46554,7 +46562,7 @@
         <v>0</v>
       </c>
       <c r="BD96" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE96" t="n">
         <v>0</v>
@@ -46572,175 +46580,175 @@
         <v>1</v>
       </c>
       <c r="BJ96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM96" t="n">
         <v>5</v>
       </c>
-      <c r="BK96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM96" t="n">
+      <c r="BN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
         <v>6</v>
       </c>
-      <c r="BN96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT96" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV96" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW96" t="n">
-        <v>44</v>
-      </c>
-      <c r="BX96" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY96" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ96" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CA96" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB96" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="CC96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR96" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS96" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU96" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV96" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX96" t="n">
-        <v>7</v>
-      </c>
       <c r="CY96" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CZ96" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DA96" t="n">
         <v>70</v>
       </c>
       <c r="DB96" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DC96" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="DF96" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="DG96" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DH96" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DI96" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="DJ96" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="DK96" t="n">
         <v>30</v>
       </c>
       <c r="DL96" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="DM96" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="DN96" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="DO96" t="n">
         <v>12</v>
@@ -46767,67 +46775,87 @@
         <v>1</v>
       </c>
       <c r="DW96" t="n">
-        <v>16.49</v>
+        <v>16.28</v>
       </c>
       <c r="DX96" t="n">
-        <v>2.95</v>
+        <v>1.64</v>
       </c>
       <c r="DY96" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ96" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA96" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EB96" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="EC96" t="inlineStr">
         <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG96" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH96" t="inlineStr"/>
+      <c r="EI96" t="inlineStr"/>
+      <c r="EJ96" t="inlineStr"/>
+      <c r="EK96" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM96" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EO96" t="inlineStr">
+        <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="ED96" t="inlineStr"/>
-      <c r="EE96" t="inlineStr"/>
-      <c r="EF96" t="inlineStr"/>
-      <c r="EG96" t="inlineStr"/>
-      <c r="EH96" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EI96" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EJ96" t="inlineStr">
-        <is>
-          <t>4.24</t>
-        </is>
-      </c>
-      <c r="EK96" t="inlineStr"/>
-      <c r="EL96" t="inlineStr"/>
-      <c r="EM96" t="inlineStr"/>
-      <c r="EN96" t="inlineStr"/>
-      <c r="EO96" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
       <c r="EP96" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
@@ -46847,12 +46875,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
@@ -46868,20 +46896,20 @@
         <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
+        <v>6</v>
+      </c>
+      <c r="L97" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3</v>
+      </c>
+      <c r="N97" t="n">
         <v>4</v>
       </c>
-      <c r="L97" t="n">
-        <v>5</v>
-      </c>
-      <c r="M97" t="n">
-        <v>1</v>
-      </c>
-      <c r="N97" t="n">
-        <v>5</v>
-      </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
@@ -46889,98 +46917,90 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T97" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U97" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V97" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W97" t="n">
         <v>12</v>
       </c>
       <c r="X97" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y97" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="Z97" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Estádio Clube Desportivo das Aves</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE97" t="n">
-        <v>5.75</v>
+        <v>2.42</v>
       </c>
       <c r="AF97" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI97" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AJ97" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AK97" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AL97" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AN97" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AO97" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AR97" t="n">
         <v>3.22</v>
       </c>
       <c r="AS97" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AT97" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU97" t="n">
         <v>2</v>
@@ -47010,7 +47030,7 @@
         <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE97" t="n">
         <v>0</v>
@@ -47028,70 +47048,70 @@
         <v>1</v>
       </c>
       <c r="BJ97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT97" t="n">
         <v>4</v>
       </c>
-      <c r="BK97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM97" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR97" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT97" t="n">
-        <v>5</v>
-      </c>
       <c r="BU97" t="n">
         <v>1</v>
       </c>
       <c r="BV97" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW97" t="n">
         <v>44</v>
       </c>
-      <c r="BW97" t="n">
-        <v>47</v>
-      </c>
       <c r="BX97" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BY97" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="BZ97" t="n">
-        <v>1.88</v>
+        <v>1.37</v>
       </c>
       <c r="CA97" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="CC97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD97" t="n">
         <v>0</v>
       </c>
       <c r="CE97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF97" t="n">
         <v>0</v>
@@ -47112,13 +47132,13 @@
         <v>0</v>
       </c>
       <c r="CL97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM97" t="n">
         <v>0</v>
       </c>
       <c r="CN97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CO97" t="n">
         <v>0</v>
@@ -47130,73 +47150,73 @@
         <v>1</v>
       </c>
       <c r="CR97" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CS97" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CT97" t="n">
         <v>1</v>
       </c>
       <c r="CU97" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV97" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX97" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY97" t="n">
         <v>11</v>
       </c>
-      <c r="CW97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX97" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY97" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ97" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DA97" t="n">
         <v>70</v>
       </c>
       <c r="DB97" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DC97" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD97" t="n">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="DF97" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG97" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="DH97" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="DI97" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="DJ97" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="DK97" t="n">
         <v>30</v>
       </c>
       <c r="DL97" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="DM97" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="DN97" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="DO97" t="n">
         <v>12</v>
@@ -47223,87 +47243,67 @@
         <v>1</v>
       </c>
       <c r="DW97" t="n">
-        <v>16.28</v>
+        <v>16.49</v>
       </c>
       <c r="DX97" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="DY97" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="DZ97" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA97" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EB97" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EC97" t="inlineStr">
         <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="ED97" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EE97" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EF97" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG97" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EH97" t="inlineStr"/>
-      <c r="EI97" t="inlineStr"/>
-      <c r="EJ97" t="inlineStr"/>
-      <c r="EK97" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EL97" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EM97" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EN97" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr"/>
+      <c r="EE97" t="inlineStr"/>
+      <c r="EF97" t="inlineStr"/>
+      <c r="EG97" t="inlineStr"/>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EK97" t="inlineStr"/>
+      <c r="EL97" t="inlineStr"/>
+      <c r="EM97" t="inlineStr"/>
+      <c r="EN97" t="inlineStr"/>
       <c r="EO97" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EP97" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -47803,12 +47803,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
@@ -47818,16 +47818,16 @@
         <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L99" t="n">
         <v>8</v>
@@ -47845,34 +47845,34 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S99" t="n">
+        <v>8</v>
+      </c>
+      <c r="T99" t="n">
+        <v>10</v>
+      </c>
+      <c r="U99" t="n">
+        <v>11</v>
+      </c>
+      <c r="V99" t="n">
+        <v>11</v>
+      </c>
+      <c r="W99" t="n">
         <v>13</v>
       </c>
-      <c r="T99" t="n">
-        <v>3</v>
-      </c>
-      <c r="U99" t="n">
-        <v>19</v>
-      </c>
-      <c r="V99" t="n">
-        <v>7</v>
-      </c>
-      <c r="W99" t="n">
-        <v>8</v>
-      </c>
       <c r="X99" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y99" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="Z99" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -47883,55 +47883,55 @@
         <v>2</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AF99" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG99" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AI99" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM99" t="n">
         <v>1.62</v>
       </c>
-      <c r="AJ99" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AN99" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AU99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV99" t="n">
         <v>1</v>
@@ -47943,22 +47943,22 @@
         <v>1</v>
       </c>
       <c r="AY99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA99" t="n">
         <v>1</v>
       </c>
       <c r="BB99" t="n">
-        <v>-1</v>
+        <v>172</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47973,178 +47973,178 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ99" t="n">
         <v>2</v>
       </c>
       <c r="BK99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN99" t="n">
         <v>5</v>
       </c>
-      <c r="BN99" t="n">
-        <v>3</v>
-      </c>
       <c r="BO99" t="n">
         <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ99" t="n">
         <v>3</v>
       </c>
       <c r="BR99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="BW99" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
         <v>19</v>
       </c>
-      <c r="BX99" t="n">
-        <v>144</v>
-      </c>
-      <c r="BY99" t="n">
-        <v>55</v>
-      </c>
-      <c r="BZ99" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CA99" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="CB99" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CC99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>21</v>
-      </c>
       <c r="CS99" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="CT99" t="n">
         <v>1</v>
       </c>
       <c r="CU99" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
         <v>7</v>
       </c>
-      <c r="CV99" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX99" t="n">
-        <v>1</v>
-      </c>
       <c r="CY99" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="CZ99" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DA99" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="DB99" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DC99" t="n">
         <v>80</v>
       </c>
       <c r="DD99" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF99" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG99" t="n">
         <v>1.2</v>
       </c>
       <c r="DH99" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="DI99" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="DJ99" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DK99" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DL99" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DN99" t="n">
-        <v>3.17</v>
+        <v>2.42</v>
       </c>
       <c r="DO99" t="n">
         <v>12</v>
@@ -48159,7 +48159,7 @@
         <v>1</v>
       </c>
       <c r="DS99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT99" t="b">
         <v>0</v>
@@ -48171,83 +48171,99 @@
         <v>1</v>
       </c>
       <c r="DW99" t="n">
-        <v>17.32</v>
+        <v>16.36</v>
       </c>
       <c r="DX99" t="n">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EE99" t="inlineStr"/>
-      <c r="EF99" t="inlineStr"/>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI99" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EJ99" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EM99" t="inlineStr"/>
-      <c r="EN99" t="inlineStr"/>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EN99" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
       <c r="EO99" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EP99" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.72</t>
         </is>
       </c>
     </row>
@@ -48267,12 +48283,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
@@ -48282,16 +48298,16 @@
         <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L100" t="n">
         <v>8</v>
@@ -48309,34 +48325,34 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S100" t="n">
+        <v>13</v>
+      </c>
+      <c r="T100" t="n">
+        <v>3</v>
+      </c>
+      <c r="U100" t="n">
+        <v>19</v>
+      </c>
+      <c r="V100" t="n">
+        <v>7</v>
+      </c>
+      <c r="W100" t="n">
         <v>8</v>
       </c>
-      <c r="T100" t="n">
-        <v>10</v>
-      </c>
-      <c r="U100" t="n">
-        <v>11</v>
-      </c>
-      <c r="V100" t="n">
-        <v>11</v>
-      </c>
-      <c r="W100" t="n">
-        <v>13</v>
-      </c>
       <c r="X100" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y100" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="Z100" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -48347,55 +48363,55 @@
         <v>2</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AF100" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AG100" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AJ100" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AK100" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AL100" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AN100" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AS100" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AU100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV100" t="n">
         <v>1</v>
@@ -48407,22 +48423,22 @@
         <v>1</v>
       </c>
       <c r="AY100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA100" t="n">
         <v>1</v>
       </c>
       <c r="BB100" t="n">
-        <v>172</v>
+        <v>-1</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48437,64 +48453,64 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ100" t="n">
         <v>2</v>
       </c>
       <c r="BK100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT100" t="n">
         <v>4</v>
       </c>
-      <c r="BL100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN100" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT100" t="n">
-        <v>5</v>
-      </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="BW100" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="BX100" t="n">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="BY100" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="BZ100" t="n">
-        <v>1.23</v>
+        <v>2.19</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="CB100" t="n">
-        <v>2.28</v>
+        <v>3.06</v>
       </c>
       <c r="CC100" t="n">
         <v>1</v>
@@ -48542,73 +48558,73 @@
         <v>1</v>
       </c>
       <c r="CR100" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CS100" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="CT100" t="n">
         <v>1</v>
       </c>
       <c r="CU100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="CV100" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CW100" t="n">
         <v>1</v>
       </c>
       <c r="CX100" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CY100" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="CZ100" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DA100" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="DB100" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DC100" t="n">
         <v>80</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE100" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DF100" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="DG100" t="n">
         <v>1.2</v>
       </c>
       <c r="DH100" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="DI100" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="DJ100" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DK100" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="DM100" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="DN100" t="n">
-        <v>2.42</v>
+        <v>3.17</v>
       </c>
       <c r="DO100" t="n">
         <v>12</v>
@@ -48623,7 +48639,7 @@
         <v>1</v>
       </c>
       <c r="DS100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT100" t="b">
         <v>0</v>
@@ -48635,99 +48651,83 @@
         <v>1</v>
       </c>
       <c r="DW100" t="n">
-        <v>16.36</v>
+        <v>17.32</v>
       </c>
       <c r="DX100" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="EC100" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="ED100" t="inlineStr">
         <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EE100" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF100" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr"/>
+      <c r="EF100" t="inlineStr"/>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EK100" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EM100" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EN100" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr"/>
+      <c r="EN100" t="inlineStr"/>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
@@ -53015,6 +53015,470 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>13</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>45996.84375</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2</v>
+      </c>
+      <c r="J110" t="n">
+        <v>3</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2</v>
+      </c>
+      <c r="L110" t="n">
+        <v>5</v>
+      </c>
+      <c r="M110" t="n">
+        <v>2</v>
+      </c>
+      <c r="N110" t="n">
+        <v>5</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>4</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" t="n">
+        <v>6</v>
+      </c>
+      <c r="T110" t="n">
+        <v>3</v>
+      </c>
+      <c r="U110" t="n">
+        <v>10</v>
+      </c>
+      <c r="V110" t="n">
+        <v>5</v>
+      </c>
+      <c r="W110" t="n">
+        <v>15</v>
+      </c>
+      <c r="X110" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD110" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE110" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL110" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DM110" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DN110" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="DO110" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW110" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="DX110" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="DY110" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="EA110" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EB110" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EC110" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="ED110" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE110" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF110" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EG110" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EH110" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EI110" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EJ110" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EK110" t="inlineStr"/>
+      <c r="EL110" t="inlineStr"/>
+      <c r="EM110" t="inlineStr"/>
+      <c r="EN110" t="inlineStr"/>
+      <c r="EO110" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP110" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP117" headerRowCount="1">
-  <autoFilter ref="A1:EP117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP118" headerRowCount="1">
+  <autoFilter ref="A1:EP118"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP117"/>
+  <dimension ref="A1:EP118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2293,7 +2293,7 @@
         <v>0.5</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DE12" t="n">
         <v>0.83</v>
@@ -6651,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -9475,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9963,7 +9963,7 @@
         <v>2.11</v>
       </c>
       <c r="DO19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -11821,7 +11821,7 @@
         <v>1.14</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11851,7 +11851,7 @@
         <v>1.87</v>
       </c>
       <c r="DO23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP23" t="b">
         <v>0</v>
@@ -13771,7 +13771,7 @@
         <v>1.94</v>
       </c>
       <c r="DO27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14694,7 +14694,7 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DE29" t="n">
         <v>0.67</v>
@@ -14727,7 +14727,7 @@
         <v>2.4</v>
       </c>
       <c r="DO29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -18222,147 +18222,155 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>4</v>
       </c>
-      <c r="K37" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>9</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>7</v>
-      </c>
       <c r="R37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8</v>
+      </c>
+      <c r="U37" t="n">
         <v>12</v>
       </c>
-      <c r="T37" t="n">
-        <v>4</v>
-      </c>
-      <c r="U37" t="n">
-        <v>19</v>
-      </c>
       <c r="V37" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W37" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="X37" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y37" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="Z37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Complexo Desportivo FC Alverca</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
+        </is>
+      </c>
       <c r="AC37" t="n">
         <v>1</v>
       </c>
       <c r="AD37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.3</v>
+        <v>2.23</v>
       </c>
       <c r="AF37" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW37" t="n">
         <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB37" t="n">
-        <v>-1</v>
+        <v>10708</v>
       </c>
       <c r="BC37" t="n">
         <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE37" t="n">
         <v>0</v>
@@ -18371,184 +18379,184 @@
         <v>-1</v>
       </c>
       <c r="BG37" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH37" t="n">
         <v>1</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BJ37" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BK37" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BL37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BM37" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BN37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>74</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR37" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>34</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY37" t="n">
         <v>5</v>
       </c>
-      <c r="BO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP37" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS37" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU37" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV37" t="n">
-        <v>115</v>
-      </c>
-      <c r="BW37" t="n">
-        <v>17</v>
-      </c>
-      <c r="BX37" t="n">
-        <v>182</v>
-      </c>
-      <c r="BY37" t="n">
-        <v>48</v>
-      </c>
-      <c r="BZ37" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="CA37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB37" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="CC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>25</v>
-      </c>
-      <c r="CS37" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU37" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV37" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX37" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY37" t="n">
-        <v>14</v>
-      </c>
       <c r="CZ37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DA37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DC37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="DF37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH37" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="DI37" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="DJ37" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DK37" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL37" t="n">
-        <v>2.61</v>
+        <v>1.41</v>
       </c>
       <c r="DM37" t="n">
-        <v>1.16</v>
+        <v>0.98</v>
       </c>
       <c r="DN37" t="n">
-        <v>3.77</v>
+        <v>2.39</v>
       </c>
       <c r="DO37" t="n">
         <v>13</v>
@@ -18557,7 +18565,7 @@
         <v>1</v>
       </c>
       <c r="DQ37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR37" t="b">
         <v>0</v>
@@ -18572,102 +18580,86 @@
         <v>0</v>
       </c>
       <c r="DV37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW37" t="n">
-        <v>27.44</v>
+        <v>25.94</v>
       </c>
       <c r="DX37" t="n">
-        <v>6.53</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DY37" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ37" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="EA37" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EB37" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EC37" t="inlineStr">
         <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="ED37" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EE37" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EF37" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EG37" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="ED37" t="inlineStr"/>
+      <c r="EE37" t="inlineStr"/>
+      <c r="EF37" t="inlineStr"/>
+      <c r="EG37" t="inlineStr"/>
       <c r="EH37" t="inlineStr">
         <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="EK37" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EL37" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="EI37" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EJ37" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="EK37" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EL37" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
       <c r="EM37" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EN37" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EO37" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EP37" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.94</t>
         </is>
       </c>
     </row>
@@ -18687,12 +18679,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -18702,155 +18694,147 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" t="n">
         <v>5</v>
       </c>
-      <c r="K38" t="n">
-        <v>6</v>
-      </c>
       <c r="L38" t="n">
+        <v>9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>7</v>
+      </c>
+      <c r="R38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>12</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>19</v>
+      </c>
+      <c r="V38" t="n">
+        <v>9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>8</v>
+      </c>
+      <c r="X38" t="n">
         <v>11</v>
       </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6</v>
-      </c>
-      <c r="S38" t="n">
-        <v>8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>8</v>
-      </c>
-      <c r="U38" t="n">
-        <v>12</v>
-      </c>
-      <c r="V38" t="n">
-        <v>14</v>
-      </c>
-      <c r="W38" t="n">
-        <v>13</v>
-      </c>
-      <c r="X38" t="n">
-        <v>15</v>
-      </c>
       <c r="Y38" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="Z38" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Complexo Desportivo FC Alverca</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
         <v>1</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="AG38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR38" t="n">
         <v>2.9</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AS38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT38" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AU38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
         <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>10708</v>
+        <v>-1</v>
       </c>
       <c r="BC38" t="n">
         <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
         <v>0</v>
@@ -18859,70 +18843,70 @@
         <v>-1</v>
       </c>
       <c r="BG38" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH38" t="n">
         <v>1</v>
       </c>
       <c r="BI38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BJ38" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BK38" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BL38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BM38" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BN38" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO38" t="n">
         <v>0</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ38" t="n">
         <v>1</v>
       </c>
       <c r="BR38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU38" t="n">
         <v>1</v>
       </c>
       <c r="BV38" t="n">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="BW38" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="BX38" t="n">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="BY38" t="n">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1.26</v>
+        <v>2.53</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.71</v>
+        <v>1.04</v>
       </c>
       <c r="CB38" t="n">
-        <v>2.97</v>
+        <v>3.57</v>
       </c>
       <c r="CC38" t="n">
         <v>0</v>
@@ -18955,10 +18939,10 @@
         <v>0</v>
       </c>
       <c r="CM38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO38" t="n">
         <v>0</v>
@@ -18970,73 +18954,73 @@
         <v>1</v>
       </c>
       <c r="CR38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS38" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="CT38" t="n">
         <v>1</v>
       </c>
       <c r="CU38" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CV38" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW38" t="n">
         <v>1</v>
       </c>
       <c r="CX38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="CY38" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CZ38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DA38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DC38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="DE38" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH38" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="DI38" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="DJ38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DK38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL38" t="n">
-        <v>1.41</v>
+        <v>2.61</v>
       </c>
       <c r="DM38" t="n">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="DN38" t="n">
-        <v>2.39</v>
+        <v>3.77</v>
       </c>
       <c r="DO38" t="n">
         <v>13</v>
@@ -19045,7 +19029,7 @@
         <v>1</v>
       </c>
       <c r="DQ38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR38" t="b">
         <v>0</v>
@@ -19060,86 +19044,102 @@
         <v>0</v>
       </c>
       <c r="DV38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW38" t="n">
-        <v>25.94</v>
+        <v>27.44</v>
       </c>
       <c r="DX38" t="n">
-        <v>8.640000000000001</v>
+        <v>6.53</v>
       </c>
       <c r="DY38" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ38" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="EA38" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="EB38" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="EC38" t="inlineStr">
         <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="ED38" t="inlineStr"/>
-      <c r="EE38" t="inlineStr"/>
-      <c r="EF38" t="inlineStr"/>
-      <c r="EG38" t="inlineStr"/>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="ED38" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EE38" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF38" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG38" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="EH38" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI38" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EJ38" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="EK38" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EL38" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EM38" t="inlineStr">
+        <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="EI38" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EJ38" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="EK38" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EL38" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EM38" t="inlineStr">
+      <c r="EN38" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EO38" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EP38" t="inlineStr">
         <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN38" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="EO38" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EP38" t="inlineStr">
-        <is>
-          <t>1.94</t>
         </is>
       </c>
     </row>
@@ -21363,7 +21363,7 @@
         <v>2.74</v>
       </c>
       <c r="DO43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22301,7 +22301,7 @@
         <v>1.67</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -22331,7 +22331,7 @@
         <v>3.35</v>
       </c>
       <c r="DO45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22955,46 +22955,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.60416666666</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>6</v>
@@ -23003,89 +23003,81 @@
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="X47" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Z47" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD47" t="n">
         <v>4</v>
       </c>
-      <c r="AD47" t="n">
-        <v>2</v>
-      </c>
       <c r="AE47" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.72</v>
+        <v>5.05</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AL47" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AO47" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS47" t="n">
         <v>2.47</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.48</v>
       </c>
       <c r="AT47" t="n">
         <v>1.3</v>
@@ -23094,25 +23086,25 @@
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX47" t="n">
         <v>1</v>
       </c>
       <c r="AY47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB47" t="n">
-        <v>167</v>
+        <v>1028</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
@@ -23127,70 +23119,70 @@
         <v>-1</v>
       </c>
       <c r="BG47" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH47" t="n">
         <v>1</v>
       </c>
       <c r="BI47" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS47" t="n">
         <v>4</v>
       </c>
-      <c r="BM47" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN47" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS47" t="n">
-        <v>1</v>
-      </c>
       <c r="BT47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU47" t="n">
         <v>1</v>
       </c>
       <c r="BV47" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="BW47" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="BX47" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="BY47" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="CC47" t="n">
         <v>1</v>
@@ -23217,94 +23209,94 @@
         <v>1</v>
       </c>
       <c r="CK47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL47" t="n">
         <v>0</v>
       </c>
       <c r="CM47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ47" t="n">
         <v>1</v>
       </c>
       <c r="CR47" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="CS47" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV47" t="n">
         <v>16</v>
       </c>
-      <c r="CT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU47" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV47" t="n">
-        <v>10</v>
-      </c>
       <c r="CW47" t="n">
         <v>1</v>
       </c>
       <c r="CX47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ47" t="n">
         <v>50</v>
       </c>
       <c r="DA47" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB47" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC47" t="n">
         <v>75</v>
       </c>
-      <c r="DC47" t="n">
-        <v>100</v>
-      </c>
       <c r="DD47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF47" t="n">
         <v>0.5</v>
-      </c>
-      <c r="DE47" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DF47" t="n">
-        <v>0</v>
       </c>
       <c r="DG47" t="n">
         <v>0.5</v>
       </c>
       <c r="DH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI47" t="n">
         <v>0.8</v>
-      </c>
-      <c r="DI47" t="n">
-        <v>1</v>
       </c>
       <c r="DJ47" t="n">
         <v>50</v>
       </c>
       <c r="DK47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="DM47" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DN47" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="DO47" t="n">
         <v>13</v>
@@ -23331,99 +23323,83 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>25.21</v>
+        <v>20.04</v>
       </c>
       <c r="DX47" t="n">
-        <v>6.42</v>
+        <v>5.58</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EC47" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EE47" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG47" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="EK47" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EL47" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EM47" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN47" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="EK47" t="inlineStr"/>
+      <c r="EL47" t="inlineStr"/>
+      <c r="EM47" t="inlineStr"/>
+      <c r="EN47" t="inlineStr"/>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
@@ -23443,46 +23419,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>45920.60416666666</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>6</v>
@@ -23491,81 +23467,89 @@
         <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W48" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="X48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Z48" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
       <c r="AC48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="AF48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR48" t="n">
         <v>3.15</v>
       </c>
-      <c r="AG48" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AS48" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AT48" t="n">
         <v>1.3</v>
@@ -23574,25 +23558,25 @@
         <v>3</v>
       </c>
       <c r="AV48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
         <v>1</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1028</v>
+        <v>167</v>
       </c>
       <c r="BC48" t="n">
         <v>0</v>
@@ -23607,184 +23591,184 @@
         <v>-1</v>
       </c>
       <c r="BG48" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH48" t="n">
         <v>1</v>
       </c>
       <c r="BI48" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BJ48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL48" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BM48" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN48" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO48" t="n">
         <v>1</v>
       </c>
       <c r="BP48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>59</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR48" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX48" t="n">
         <v>5</v>
       </c>
-      <c r="BR48" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS48" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT48" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU48" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV48" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW48" t="n">
-        <v>27</v>
-      </c>
-      <c r="BX48" t="n">
-        <v>93</v>
-      </c>
-      <c r="BY48" t="n">
-        <v>70</v>
-      </c>
-      <c r="BZ48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CA48" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="CB48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CC48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS48" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU48" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV48" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX48" t="n">
-        <v>1</v>
-      </c>
       <c r="CY48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ48" t="n">
         <v>50</v>
       </c>
       <c r="DA48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB48" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DC48" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="DF48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DG48" t="n">
         <v>0.5</v>
       </c>
       <c r="DH48" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DI48" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DJ48" t="n">
         <v>50</v>
       </c>
       <c r="DK48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL48" t="n">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DM48" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="DN48" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="DO48" t="n">
         <v>13</v>
@@ -23811,83 +23795,99 @@
         <v>1</v>
       </c>
       <c r="DW48" t="n">
-        <v>20.04</v>
+        <v>25.21</v>
       </c>
       <c r="DX48" t="n">
-        <v>5.58</v>
+        <v>6.42</v>
       </c>
       <c r="DY48" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="DZ48" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA48" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="EB48" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EC48" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="ED48" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EE48" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EF48" t="inlineStr">
         <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EG48" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH48" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EI48" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EJ48" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EK48" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EL48" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EM48" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN48" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EO48" t="inlineStr">
+        <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="EG48" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EH48" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EI48" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EJ48" t="inlineStr">
-        <is>
-          <t>5.09</t>
-        </is>
-      </c>
-      <c r="EK48" t="inlineStr"/>
-      <c r="EL48" t="inlineStr"/>
-      <c r="EM48" t="inlineStr"/>
-      <c r="EN48" t="inlineStr"/>
-      <c r="EO48" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
       <c r="EP48" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -24706,7 +24706,7 @@
         <v>100</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DE50" t="n">
         <v>1.71</v>
@@ -24739,7 +24739,7 @@
         <v>3.53</v>
       </c>
       <c r="DO50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25715,7 +25715,7 @@
         <v>3.03</v>
       </c>
       <c r="DO52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -27581,7 +27581,7 @@
         <v>1.86</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DF56" t="n">
         <v>1.67</v>
@@ -27611,7 +27611,7 @@
         <v>3.98</v>
       </c>
       <c r="DO56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -30003,7 +30003,7 @@
         <v>2.65</v>
       </c>
       <c r="DO61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -32015,170 +32015,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L66" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
         <v>7</v>
       </c>
       <c r="R66" t="n">
+        <v>4</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="n">
+        <v>6</v>
+      </c>
+      <c r="U66" t="n">
+        <v>17</v>
+      </c>
+      <c r="V66" t="n">
+        <v>10</v>
+      </c>
+      <c r="W66" t="n">
+        <v>12</v>
+      </c>
+      <c r="X66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="n">
         <v>5</v>
       </c>
-      <c r="S66" t="n">
-        <v>8</v>
-      </c>
-      <c r="T66" t="n">
-        <v>10</v>
-      </c>
-      <c r="U66" t="n">
-        <v>15</v>
-      </c>
-      <c r="V66" t="n">
-        <v>15</v>
-      </c>
-      <c r="W66" t="n">
-        <v>13</v>
-      </c>
-      <c r="X66" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Estádio Cidade de Barcelos</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>strada Nacional 103, Vila Boa, Barcelos</t>
-        </is>
-      </c>
-      <c r="AC66" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>3</v>
-      </c>
       <c r="AE66" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="AF66" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AG66" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI66" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AK66" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AN66" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AO66" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR66" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AU66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
         <v>2</v>
       </c>
       <c r="BB66" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32193,181 +32193,181 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM66" t="n">
         <v>4</v>
       </c>
-      <c r="BJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL66" t="n">
+      <c r="BN66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS66" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU66" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV66" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX66" t="n">
         <v>6</v>
-      </c>
-      <c r="BM66" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN66" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT66" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV66" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW66" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>83</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CB66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CC66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS66" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX66" t="n">
-        <v>8</v>
       </c>
       <c r="CY66" t="n">
         <v>8</v>
       </c>
       <c r="CZ66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA66" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DB66" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DC66" t="n">
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DE66" t="n">
         <v>1</v>
       </c>
       <c r="DF66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DG66" t="n">
         <v>1</v>
       </c>
       <c r="DH66" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="DI66" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DJ66" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK66" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="DO66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32376,69 +32376,69 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU66" t="b">
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW66" t="n">
-        <v>25.52</v>
+        <v>24.96</v>
       </c>
       <c r="DX66" t="n">
-        <v>6.19</v>
+        <v>6.88</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EE66" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF66" t="inlineStr">
+        <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="EE66" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EF66" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
@@ -32448,42 +32448,42 @@
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -32503,170 +32503,170 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
         <v>5</v>
       </c>
-      <c r="J67" t="n">
-        <v>2</v>
-      </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L67" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>7</v>
       </c>
       <c r="R67" t="n">
+        <v>5</v>
+      </c>
+      <c r="S67" t="n">
+        <v>8</v>
+      </c>
+      <c r="T67" t="n">
+        <v>10</v>
+      </c>
+      <c r="U67" t="n">
+        <v>15</v>
+      </c>
+      <c r="V67" t="n">
+        <v>15</v>
+      </c>
+      <c r="W67" t="n">
+        <v>13</v>
+      </c>
+      <c r="X67" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Estádio Cidade de Barcelos</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>strada Nacional 103, Vila Boa, Barcelos</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
         <v>4</v>
       </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="n">
-        <v>6</v>
-      </c>
-      <c r="U67" t="n">
-        <v>17</v>
-      </c>
-      <c r="V67" t="n">
-        <v>10</v>
-      </c>
-      <c r="W67" t="n">
-        <v>12</v>
-      </c>
-      <c r="X67" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
-      <c r="AC67" t="n">
-        <v>1</v>
-      </c>
       <c r="AD67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="AF67" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AG67" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AI67" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ67" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AL67" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AN67" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AO67" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AR67" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AS67" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AU67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
       </c>
       <c r="BB67" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32681,73 +32681,73 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM67" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT67" t="n">
         <v>4</v>
       </c>
-      <c r="BN67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT67" t="n">
-        <v>3</v>
-      </c>
       <c r="BU67" t="n">
         <v>1</v>
       </c>
       <c r="BV67" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BW67" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="BX67" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="BY67" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BZ67" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="CA67" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="CB67" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="CC67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD67" t="n">
         <v>0</v>
       </c>
       <c r="CE67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF67" t="n">
         <v>0</v>
@@ -32768,10 +32768,10 @@
         <v>0</v>
       </c>
       <c r="CL67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN67" t="n">
         <v>0</v>
@@ -32786,73 +32786,73 @@
         <v>1</v>
       </c>
       <c r="CR67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS67" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT67" t="n">
         <v>1</v>
       </c>
       <c r="CU67" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW67" t="n">
         <v>1</v>
       </c>
       <c r="CX67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY67" t="n">
         <v>8</v>
       </c>
       <c r="CZ67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA67" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DB67" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DC67" t="n">
         <v>50</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DE67" t="n">
         <v>1</v>
       </c>
       <c r="DF67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DG67" t="n">
         <v>1</v>
       </c>
       <c r="DH67" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="DI67" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="DJ67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK67" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="DM67" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="DN67" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="DO67" t="n">
         <v>13</v>
@@ -32864,114 +32864,114 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU67" t="b">
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW67" t="n">
-        <v>24.96</v>
+        <v>25.52</v>
       </c>
       <c r="DX67" t="n">
-        <v>6.88</v>
+        <v>6.19</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA67" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="EB67" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EC67" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="ED67" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EE67" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EH67" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI67" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ67" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EK67" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EL67" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM67" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN67" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EO67" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP67" t="inlineStr">
+        <is>
           <t>1.72</t>
-        </is>
-      </c>
-      <c r="EH67" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI67" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ67" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="EK67" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="EL67" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EM67" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EN67" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EO67" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EP67" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -33770,7 +33770,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DE69" t="n">
         <v>0.83</v>
@@ -33803,7 +33803,7 @@
         <v>2.48</v>
       </c>
       <c r="DO69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -36173,7 +36173,7 @@
         <v>1.43</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DF74" t="n">
         <v>1.5</v>
@@ -36203,7 +36203,7 @@
         <v>2.87</v>
       </c>
       <c r="DO74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -38107,7 +38107,7 @@
         <v>2.87</v>
       </c>
       <c r="DO78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -41119,170 +41119,170 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
         <v>45962.75</v>
       </c>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I85" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M85" t="n">
         <v>2</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>6</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T85" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="U85" t="n">
+        <v>2</v>
+      </c>
+      <c r="V85" t="n">
+        <v>24</v>
+      </c>
+      <c r="W85" t="n">
         <v>10</v>
       </c>
-      <c r="V85" t="n">
-        <v>12</v>
-      </c>
-      <c r="W85" t="n">
-        <v>20</v>
-      </c>
       <c r="X85" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y85" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="Z85" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Campo do Cevadeiro</t>
+          <t>Estádio do Rio Ave Futebol Clube</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Estrada Nacional 10, Vila Franca de Xira</t>
+          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE85" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AG85" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AI85" t="n">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="AJ85" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="AK85" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AL85" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AM85" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AN85" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AO85" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AR85" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AS85" t="n">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AU85" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW85" t="n">
         <v>2</v>
       </c>
       <c r="AX85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BA85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB85" t="n">
-        <v>15804</v>
+        <v>164</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -41297,76 +41297,76 @@
         <v>1</v>
       </c>
       <c r="BI85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ85" t="n">
         <v>2</v>
       </c>
       <c r="BR85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU85" t="n">
         <v>1</v>
       </c>
       <c r="BV85" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="BW85" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="BX85" t="n">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="BY85" t="n">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="BZ85" t="n">
-        <v>1.2</v>
+        <v>0.22</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.32</v>
+        <v>2.37</v>
       </c>
       <c r="CB85" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="CC85" t="n">
         <v>0</v>
       </c>
       <c r="CD85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CE85" t="n">
         <v>0</v>
       </c>
       <c r="CF85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CG85" t="n">
         <v>0</v>
@@ -41387,10 +41387,10 @@
         <v>0</v>
       </c>
       <c r="CM85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CN85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO85" t="n">
         <v>0</v>
@@ -41402,73 +41402,73 @@
         <v>1</v>
       </c>
       <c r="CR85" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CS85" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CT85" t="n">
         <v>1</v>
       </c>
       <c r="CU85" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CV85" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CW85" t="n">
         <v>1</v>
       </c>
       <c r="CX85" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="CY85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CZ85" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="DA85" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB85" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DC85" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="DD85" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DE85" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG85" t="n">
         <v>0.5</v>
       </c>
-      <c r="DG85" t="n">
-        <v>0.75</v>
-      </c>
       <c r="DH85" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="DI85" t="n">
         <v>0.78</v>
       </c>
       <c r="DJ85" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="DK85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL85" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="DN85" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="DO85" t="n">
         <v>13</v>
@@ -41486,23 +41486,23 @@
         <v>1</v>
       </c>
       <c r="DT85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW85" t="n">
-        <v>20.42</v>
+        <v>15.06</v>
       </c>
       <c r="DX85" t="n">
-        <v>8.41</v>
+        <v>4.25</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
@@ -41512,74 +41512,82 @@
       </c>
       <c r="EA85" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EB85" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EC85" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EG85" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH85" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EM85" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EN85" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EO85" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EP85" t="inlineStr">
+        <is>
           <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED85" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EE85" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF85" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EG85" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EH85" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI85" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EJ85" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
-      </c>
-      <c r="EK85" t="inlineStr"/>
-      <c r="EL85" t="inlineStr"/>
-      <c r="EM85" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EN85" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="EO85" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EP85" t="inlineStr">
-        <is>
-          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -41599,170 +41607,170 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
         <v>45962.75</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H86" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>8</v>
+      </c>
+      <c r="J86" t="n">
+        <v>5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>2</v>
+      </c>
+      <c r="L86" t="n">
+        <v>7</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
         <v>4</v>
-      </c>
-      <c r="I86" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>6</v>
-      </c>
-      <c r="L86" t="n">
-        <v>6</v>
-      </c>
-      <c r="M86" t="n">
-        <v>2</v>
-      </c>
-      <c r="N86" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>6</v>
       </c>
       <c r="S86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V86" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="W86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="X86" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y86" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="Z86" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Estádio do Rio Ave Futebol Clube</t>
+          <t>Campo do Cevadeiro</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
+          <t>Estrada Nacional 10, Vila Franca de Xira</t>
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE86" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AF86" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AG86" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH86" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT86" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI86" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ86" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AK86" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL86" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM86" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AN86" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO86" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AP86" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ86" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR86" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS86" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AT86" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AU86" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW86" t="n">
         <v>2</v>
       </c>
       <c r="AX86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BA86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB86" t="n">
-        <v>164</v>
+        <v>15804</v>
       </c>
       <c r="BC86" t="n">
         <v>0</v>
       </c>
       <c r="BD86" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="BE86" t="n">
         <v>0</v>
@@ -41777,76 +41785,76 @@
         <v>1</v>
       </c>
       <c r="BI86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ86" t="n">
         <v>2</v>
       </c>
       <c r="BR86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU86" t="n">
         <v>1</v>
       </c>
       <c r="BV86" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BW86" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="BX86" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="BY86" t="n">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="BZ86" t="n">
-        <v>0.22</v>
+        <v>1.2</v>
       </c>
       <c r="CA86" t="n">
-        <v>2.37</v>
+        <v>1.32</v>
       </c>
       <c r="CB86" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="CC86" t="n">
         <v>0</v>
       </c>
       <c r="CD86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE86" t="n">
         <v>0</v>
       </c>
       <c r="CF86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CG86" t="n">
         <v>0</v>
@@ -41867,10 +41875,10 @@
         <v>0</v>
       </c>
       <c r="CM86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CN86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO86" t="n">
         <v>0</v>
@@ -41882,73 +41890,73 @@
         <v>1</v>
       </c>
       <c r="CR86" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS86" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU86" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV86" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX86" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY86" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ86" t="n">
         <v>13</v>
       </c>
-      <c r="CS86" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU86" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV86" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX86" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY86" t="n">
-        <v>1</v>
-      </c>
-      <c r="CZ86" t="n">
+      <c r="DA86" t="n">
         <v>75</v>
       </c>
-      <c r="DA86" t="n">
-        <v>100</v>
-      </c>
       <c r="DB86" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC86" t="n">
         <v>63</v>
       </c>
-      <c r="DC86" t="n">
-        <v>100</v>
-      </c>
       <c r="DD86" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="DE86" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="DF86" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="DG86" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="DH86" t="n">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="DI86" t="n">
         <v>0.78</v>
       </c>
       <c r="DJ86" t="n">
+        <v>88</v>
+      </c>
+      <c r="DK86" t="n">
         <v>25</v>
       </c>
-      <c r="DK86" t="n">
-        <v>0</v>
-      </c>
       <c r="DL86" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="DM86" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="DN86" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="DO86" t="n">
         <v>13</v>
@@ -41966,23 +41974,23 @@
         <v>1</v>
       </c>
       <c r="DT86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW86" t="n">
-        <v>15.06</v>
+        <v>20.42</v>
       </c>
       <c r="DX86" t="n">
-        <v>4.25</v>
+        <v>8.41</v>
       </c>
       <c r="DY86" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="DZ86" t="inlineStr">
@@ -41992,82 +42000,74 @@
       </c>
       <c r="EA86" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EB86" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EC86" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="ED86" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EE86" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EF86" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EG86" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EH86" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI86" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EJ86" t="inlineStr">
         <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EK86" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EL86" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="EK86" t="inlineStr"/>
+      <c r="EL86" t="inlineStr"/>
       <c r="EM86" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EN86" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EO86" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EP86" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.74</t>
         </is>
       </c>
     </row>
@@ -42406,7 +42406,7 @@
         <v>75</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DE87" t="n">
         <v>2.67</v>
@@ -42439,7 +42439,7 @@
         <v>2.67</v>
       </c>
       <c r="DO87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -44391,7 +44391,7 @@
         <v>2.73</v>
       </c>
       <c r="DO91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -45831,7 +45831,7 @@
         <v>2.92</v>
       </c>
       <c r="DO94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46399,12 +46399,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
@@ -46420,111 +46420,119 @@
         <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L96" t="n">
+        <v>5</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
         <v>8</v>
       </c>
-      <c r="M96" t="n">
-        <v>3</v>
-      </c>
-      <c r="N96" t="n">
-        <v>4</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>4</v>
-      </c>
       <c r="R96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T96" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U96" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V96" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="W96" t="n">
         <v>12</v>
       </c>
       <c r="X96" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y96" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="Z96" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Estádio Clube Desportivo das Aves</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
+        </is>
+      </c>
       <c r="AC96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.42</v>
+        <v>5.75</v>
       </c>
       <c r="AF96" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.96</v>
+        <v>1.63</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI96" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AJ96" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AK96" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AL96" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AM96" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AN96" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AO96" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR96" t="n">
         <v>3.22</v>
       </c>
       <c r="AS96" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AT96" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU96" t="n">
         <v>2</v>
@@ -46554,7 +46562,7 @@
         <v>0</v>
       </c>
       <c r="BD96" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE96" t="n">
         <v>0</v>
@@ -46572,175 +46580,175 @@
         <v>1</v>
       </c>
       <c r="BJ96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM96" t="n">
         <v>5</v>
       </c>
-      <c r="BK96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM96" t="n">
+      <c r="BN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
         <v>6</v>
       </c>
-      <c r="BN96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT96" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV96" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW96" t="n">
-        <v>44</v>
-      </c>
-      <c r="BX96" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY96" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ96" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CA96" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB96" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="CC96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR96" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS96" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU96" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV96" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX96" t="n">
-        <v>7</v>
-      </c>
       <c r="CY96" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CZ96" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DA96" t="n">
         <v>70</v>
       </c>
       <c r="DB96" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DC96" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.14</v>
+        <v>0.29</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="DF96" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="DG96" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DH96" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DI96" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="DJ96" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="DK96" t="n">
         <v>30</v>
       </c>
       <c r="DL96" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="DM96" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="DN96" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="DO96" t="n">
         <v>13</v>
@@ -46767,67 +46775,87 @@
         <v>1</v>
       </c>
       <c r="DW96" t="n">
-        <v>16.49</v>
+        <v>16.28</v>
       </c>
       <c r="DX96" t="n">
-        <v>2.95</v>
+        <v>1.64</v>
       </c>
       <c r="DY96" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ96" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA96" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EB96" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="EC96" t="inlineStr">
         <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG96" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH96" t="inlineStr"/>
+      <c r="EI96" t="inlineStr"/>
+      <c r="EJ96" t="inlineStr"/>
+      <c r="EK96" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM96" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EO96" t="inlineStr">
+        <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="ED96" t="inlineStr"/>
-      <c r="EE96" t="inlineStr"/>
-      <c r="EF96" t="inlineStr"/>
-      <c r="EG96" t="inlineStr"/>
-      <c r="EH96" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EI96" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EJ96" t="inlineStr">
-        <is>
-          <t>4.24</t>
-        </is>
-      </c>
-      <c r="EK96" t="inlineStr"/>
-      <c r="EL96" t="inlineStr"/>
-      <c r="EM96" t="inlineStr"/>
-      <c r="EN96" t="inlineStr"/>
-      <c r="EO96" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
       <c r="EP96" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
@@ -46847,12 +46875,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
@@ -46868,20 +46896,20 @@
         <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
+        <v>6</v>
+      </c>
+      <c r="L97" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3</v>
+      </c>
+      <c r="N97" t="n">
         <v>4</v>
       </c>
-      <c r="L97" t="n">
-        <v>5</v>
-      </c>
-      <c r="M97" t="n">
-        <v>1</v>
-      </c>
-      <c r="N97" t="n">
-        <v>5</v>
-      </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
@@ -46889,98 +46917,90 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T97" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U97" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V97" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W97" t="n">
         <v>12</v>
       </c>
       <c r="X97" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y97" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="Z97" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Estádio Clube Desportivo das Aves</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE97" t="n">
-        <v>5.75</v>
+        <v>2.42</v>
       </c>
       <c r="AF97" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI97" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AJ97" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AK97" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AL97" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AN97" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AO97" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AR97" t="n">
         <v>3.22</v>
       </c>
       <c r="AS97" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AT97" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU97" t="n">
         <v>2</v>
@@ -47010,7 +47030,7 @@
         <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE97" t="n">
         <v>0</v>
@@ -47028,70 +47048,70 @@
         <v>1</v>
       </c>
       <c r="BJ97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT97" t="n">
         <v>4</v>
       </c>
-      <c r="BK97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM97" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR97" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT97" t="n">
-        <v>5</v>
-      </c>
       <c r="BU97" t="n">
         <v>1</v>
       </c>
       <c r="BV97" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW97" t="n">
         <v>44</v>
       </c>
-      <c r="BW97" t="n">
-        <v>47</v>
-      </c>
       <c r="BX97" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BY97" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="BZ97" t="n">
-        <v>1.88</v>
+        <v>1.37</v>
       </c>
       <c r="CA97" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="CC97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD97" t="n">
         <v>0</v>
       </c>
       <c r="CE97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF97" t="n">
         <v>0</v>
@@ -47112,13 +47132,13 @@
         <v>0</v>
       </c>
       <c r="CL97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM97" t="n">
         <v>0</v>
       </c>
       <c r="CN97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CO97" t="n">
         <v>0</v>
@@ -47130,76 +47150,76 @@
         <v>1</v>
       </c>
       <c r="CR97" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CS97" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CT97" t="n">
         <v>1</v>
       </c>
       <c r="CU97" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV97" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX97" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY97" t="n">
         <v>11</v>
       </c>
-      <c r="CW97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX97" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY97" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ97" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DA97" t="n">
         <v>70</v>
       </c>
       <c r="DB97" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DC97" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD97" t="n">
-        <v>0.29</v>
+        <v>1.14</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="DF97" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG97" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="DH97" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="DI97" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="DJ97" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="DK97" t="n">
         <v>30</v>
       </c>
       <c r="DL97" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="DM97" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="DN97" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="DO97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47223,87 +47243,67 @@
         <v>1</v>
       </c>
       <c r="DW97" t="n">
-        <v>16.28</v>
+        <v>16.49</v>
       </c>
       <c r="DX97" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="DY97" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="DZ97" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA97" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EB97" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EC97" t="inlineStr">
         <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="ED97" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EE97" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EF97" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG97" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EH97" t="inlineStr"/>
-      <c r="EI97" t="inlineStr"/>
-      <c r="EJ97" t="inlineStr"/>
-      <c r="EK97" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EL97" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EM97" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EN97" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr"/>
+      <c r="EE97" t="inlineStr"/>
+      <c r="EF97" t="inlineStr"/>
+      <c r="EG97" t="inlineStr"/>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EK97" t="inlineStr"/>
+      <c r="EL97" t="inlineStr"/>
+      <c r="EM97" t="inlineStr"/>
+      <c r="EN97" t="inlineStr"/>
       <c r="EO97" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EP97" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -47803,12 +47803,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
@@ -47818,16 +47818,16 @@
         <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L99" t="n">
         <v>8</v>
@@ -47845,34 +47845,34 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S99" t="n">
+        <v>8</v>
+      </c>
+      <c r="T99" t="n">
+        <v>10</v>
+      </c>
+      <c r="U99" t="n">
+        <v>11</v>
+      </c>
+      <c r="V99" t="n">
+        <v>11</v>
+      </c>
+      <c r="W99" t="n">
         <v>13</v>
       </c>
-      <c r="T99" t="n">
-        <v>3</v>
-      </c>
-      <c r="U99" t="n">
-        <v>19</v>
-      </c>
-      <c r="V99" t="n">
-        <v>7</v>
-      </c>
-      <c r="W99" t="n">
-        <v>8</v>
-      </c>
       <c r="X99" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y99" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="Z99" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -47883,55 +47883,55 @@
         <v>2</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AF99" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG99" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AI99" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM99" t="n">
         <v>1.62</v>
       </c>
-      <c r="AJ99" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AN99" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AU99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV99" t="n">
         <v>1</v>
@@ -47943,22 +47943,22 @@
         <v>1</v>
       </c>
       <c r="AY99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA99" t="n">
         <v>1</v>
       </c>
       <c r="BB99" t="n">
-        <v>-1</v>
+        <v>172</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47973,178 +47973,178 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ99" t="n">
         <v>2</v>
       </c>
       <c r="BK99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN99" t="n">
         <v>5</v>
       </c>
-      <c r="BN99" t="n">
-        <v>3</v>
-      </c>
       <c r="BO99" t="n">
         <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ99" t="n">
         <v>3</v>
       </c>
       <c r="BR99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="BW99" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
         <v>19</v>
       </c>
-      <c r="BX99" t="n">
-        <v>144</v>
-      </c>
-      <c r="BY99" t="n">
-        <v>55</v>
-      </c>
-      <c r="BZ99" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CA99" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="CB99" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CC99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>21</v>
-      </c>
       <c r="CS99" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="CT99" t="n">
         <v>1</v>
       </c>
       <c r="CU99" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
         <v>7</v>
       </c>
-      <c r="CV99" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX99" t="n">
-        <v>1</v>
-      </c>
       <c r="CY99" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="CZ99" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DA99" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="DB99" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DC99" t="n">
         <v>80</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="DE99" t="n">
         <v>1</v>
       </c>
       <c r="DF99" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG99" t="n">
         <v>1.2</v>
       </c>
       <c r="DH99" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="DI99" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="DJ99" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DK99" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DL99" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DN99" t="n">
-        <v>3.17</v>
+        <v>2.42</v>
       </c>
       <c r="DO99" t="n">
         <v>13</v>
@@ -48159,7 +48159,7 @@
         <v>1</v>
       </c>
       <c r="DS99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT99" t="b">
         <v>0</v>
@@ -48171,83 +48171,99 @@
         <v>1</v>
       </c>
       <c r="DW99" t="n">
-        <v>17.32</v>
+        <v>16.36</v>
       </c>
       <c r="DX99" t="n">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EE99" t="inlineStr"/>
-      <c r="EF99" t="inlineStr"/>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI99" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EJ99" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EM99" t="inlineStr"/>
-      <c r="EN99" t="inlineStr"/>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EN99" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
       <c r="EO99" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EP99" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.72</t>
         </is>
       </c>
     </row>
@@ -48267,12 +48283,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
@@ -48282,16 +48298,16 @@
         <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L100" t="n">
         <v>8</v>
@@ -48309,34 +48325,34 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S100" t="n">
+        <v>13</v>
+      </c>
+      <c r="T100" t="n">
+        <v>3</v>
+      </c>
+      <c r="U100" t="n">
+        <v>19</v>
+      </c>
+      <c r="V100" t="n">
+        <v>7</v>
+      </c>
+      <c r="W100" t="n">
         <v>8</v>
       </c>
-      <c r="T100" t="n">
-        <v>10</v>
-      </c>
-      <c r="U100" t="n">
-        <v>11</v>
-      </c>
-      <c r="V100" t="n">
-        <v>11</v>
-      </c>
-      <c r="W100" t="n">
-        <v>13</v>
-      </c>
       <c r="X100" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y100" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="Z100" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -48347,55 +48363,55 @@
         <v>2</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AF100" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AG100" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AJ100" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AK100" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AL100" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AN100" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AS100" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AU100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV100" t="n">
         <v>1</v>
@@ -48407,22 +48423,22 @@
         <v>1</v>
       </c>
       <c r="AY100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA100" t="n">
         <v>1</v>
       </c>
       <c r="BB100" t="n">
-        <v>172</v>
+        <v>-1</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48437,64 +48453,64 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ100" t="n">
         <v>2</v>
       </c>
       <c r="BK100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT100" t="n">
         <v>4</v>
       </c>
-      <c r="BL100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN100" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT100" t="n">
-        <v>5</v>
-      </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="BW100" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="BX100" t="n">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="BY100" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="BZ100" t="n">
-        <v>1.23</v>
+        <v>2.19</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="CB100" t="n">
-        <v>2.28</v>
+        <v>3.06</v>
       </c>
       <c r="CC100" t="n">
         <v>1</v>
@@ -48542,73 +48558,73 @@
         <v>1</v>
       </c>
       <c r="CR100" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CS100" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="CT100" t="n">
         <v>1</v>
       </c>
       <c r="CU100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="CV100" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CW100" t="n">
         <v>1</v>
       </c>
       <c r="CX100" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CY100" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="CZ100" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DA100" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="DB100" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DC100" t="n">
         <v>80</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE100" t="n">
         <v>1</v>
       </c>
       <c r="DF100" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="DG100" t="n">
         <v>1.2</v>
       </c>
       <c r="DH100" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="DI100" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="DJ100" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DK100" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="DM100" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="DN100" t="n">
-        <v>2.42</v>
+        <v>3.17</v>
       </c>
       <c r="DO100" t="n">
         <v>13</v>
@@ -48623,7 +48639,7 @@
         <v>1</v>
       </c>
       <c r="DS100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT100" t="b">
         <v>0</v>
@@ -48635,99 +48651,83 @@
         <v>1</v>
       </c>
       <c r="DW100" t="n">
-        <v>16.36</v>
+        <v>17.32</v>
       </c>
       <c r="DX100" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="EC100" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="ED100" t="inlineStr">
         <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EE100" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF100" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr"/>
+      <c r="EF100" t="inlineStr"/>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EK100" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EM100" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EN100" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr"/>
+      <c r="EN100" t="inlineStr"/>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
@@ -49066,7 +49066,7 @@
         <v>80</v>
       </c>
       <c r="DD101" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="DE101" t="n">
         <v>0.17</v>
@@ -49099,7 +49099,7 @@
         <v>2.41</v>
       </c>
       <c r="DO101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -51003,7 +51003,7 @@
         <v>2.67</v>
       </c>
       <c r="DO105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -53571,10 +53571,10 @@
         <v>5</v>
       </c>
       <c r="W111" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y111" t="n">
         <v>43</v>
@@ -54516,7 +54516,7 @@
         <v>4</v>
       </c>
       <c r="R113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S113" t="n">
         <v>3</v>
@@ -54528,7 +54528,7 @@
         <v>7</v>
       </c>
       <c r="V113" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W113" t="n">
         <v>10</v>
@@ -54695,10 +54695,10 @@
         <v>0.98</v>
       </c>
       <c r="CA113" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="CB113" t="n">
-        <v>3.16</v>
+        <v>3.29</v>
       </c>
       <c r="CC113" t="n">
         <v>0</v>
@@ -55017,10 +55017,10 @@
         <v>14</v>
       </c>
       <c r="Y114" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z114" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
@@ -55423,146 +55423,138 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L115" t="n">
+        <v>8</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
         <v>4</v>
       </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1</v>
-      </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q115" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T115" t="n">
+        <v>7</v>
+      </c>
+      <c r="U115" t="n">
+        <v>24</v>
+      </c>
+      <c r="V115" t="n">
+        <v>9</v>
+      </c>
+      <c r="W115" t="n">
+        <v>11</v>
+      </c>
+      <c r="X115" t="n">
         <v>14</v>
       </c>
-      <c r="U115" t="n">
-        <v>10</v>
-      </c>
-      <c r="V115" t="n">
-        <v>17</v>
-      </c>
-      <c r="W115" t="n">
-        <v>10</v>
-      </c>
-      <c r="X115" t="n">
-        <v>19</v>
-      </c>
       <c r="Y115" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="Z115" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Complexo Desportivo FC Alverca</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AG115" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AJ115" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL115" t="n">
         <v>1.92</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW115" t="n">
         <v>0</v>
@@ -55571,22 +55563,22 @@
         <v>1</v>
       </c>
       <c r="AY115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB115" t="n">
-        <v>10708</v>
+        <v>15804</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55601,64 +55593,64 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BW115" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="BX115" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="BY115" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="BZ115" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="CA115" t="n">
-        <v>1.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB115" t="n">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
@@ -55691,10 +55683,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55709,70 +55701,70 @@
         <v>21</v>
       </c>
       <c r="CS115" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV115" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
       </c>
       <c r="CX115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY115" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CZ115" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="DA115" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="DB115" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="DC115" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="DF115" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="DG115" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="DH115" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="DI115" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DJ115" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="DK115" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DM115" t="n">
-        <v>1.21</v>
+        <v>0.87</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="DO115" t="n">
         <v>13</v>
@@ -55781,13 +55773,13 @@
         <v>1</v>
       </c>
       <c r="DQ115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT115" t="b">
         <v>0</v>
@@ -55796,17 +55788,17 @@
         <v>0</v>
       </c>
       <c r="DV115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW115" t="n">
-        <v>16.34</v>
+        <v>16.07</v>
       </c>
       <c r="DX115" t="n">
-        <v>5.53</v>
+        <v>5.47</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
@@ -55816,39 +55808,23 @@
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="ED115" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EE115" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EF115" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EG115" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr"/>
+      <c r="EF115" t="inlineStr"/>
+      <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -55856,26 +55832,42 @@
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="EK115" t="inlineStr"/>
-      <c r="EL115" t="inlineStr"/>
-      <c r="EM115" t="inlineStr"/>
-      <c r="EN115" t="inlineStr"/>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EM115" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN115" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
       <c r="EO115" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -55895,138 +55887,146 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" t="n">
         <v>4</v>
       </c>
-      <c r="J116" t="n">
-        <v>5</v>
-      </c>
-      <c r="K116" t="n">
-        <v>3</v>
-      </c>
-      <c r="L116" t="n">
-        <v>8</v>
-      </c>
       <c r="M116" t="n">
         <v>1</v>
       </c>
       <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
         <v>4</v>
       </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>9</v>
-      </c>
       <c r="R116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T116" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U116" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V116" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X116" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y116" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="Z116" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Complexo Desportivo FC Alverca</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
+        </is>
+      </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AG116" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI116" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AJ116" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL116" t="n">
         <v>1.92</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AN116" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AU116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW116" t="n">
         <v>0</v>
@@ -56035,22 +56035,22 @@
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>15804</v>
+        <v>10708</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -56065,64 +56065,64 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR116" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU116" t="n">
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="BW116" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="BX116" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="BY116" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="BZ116" t="n">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="CA116" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="CB116" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
@@ -56155,10 +56155,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -56173,70 +56173,70 @@
         <v>21</v>
       </c>
       <c r="CS116" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CV116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CW116" t="n">
         <v>1</v>
       </c>
       <c r="CX116" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY116" t="n">
         <v>6</v>
       </c>
-      <c r="CY116" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ116" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="DA116" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="DB116" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="DC116" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="DF116" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG116" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="DH116" t="n">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="DI116" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DJ116" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="DK116" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DM116" t="n">
-        <v>0.87</v>
+        <v>1.21</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="DO116" t="n">
         <v>13</v>
@@ -56245,13 +56245,13 @@
         <v>1</v>
       </c>
       <c r="DQ116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT116" t="b">
         <v>0</v>
@@ -56260,17 +56260,17 @@
         <v>0</v>
       </c>
       <c r="DV116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>16.07</v>
+        <v>16.34</v>
       </c>
       <c r="DX116" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
@@ -56280,23 +56280,39 @@
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="ED116" t="inlineStr"/>
-      <c r="EE116" t="inlineStr"/>
-      <c r="EF116" t="inlineStr"/>
-      <c r="EG116" t="inlineStr"/>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
       <c r="EH116" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -56304,42 +56320,26 @@
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="EK116" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="EL116" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EM116" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN116" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr"/>
+      <c r="EL116" t="inlineStr"/>
+      <c r="EM116" t="inlineStr"/>
+      <c r="EN116" t="inlineStr"/>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -56425,10 +56425,10 @@
         <v>10</v>
       </c>
       <c r="Y117" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z117" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
@@ -56828,6 +56828,486 @@
       <c r="EP117" t="inlineStr">
         <is>
           <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>13</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Vitória Guimarães</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>45999.85416666666</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>8</v>
+      </c>
+      <c r="K118" t="n">
+        <v>4</v>
+      </c>
+      <c r="L118" t="n">
+        <v>12</v>
+      </c>
+      <c r="M118" t="n">
+        <v>4</v>
+      </c>
+      <c r="N118" t="n">
+        <v>5</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>3</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>7</v>
+      </c>
+      <c r="T118" t="n">
+        <v>5</v>
+      </c>
+      <c r="U118" t="n">
+        <v>10</v>
+      </c>
+      <c r="V118" t="n">
+        <v>6</v>
+      </c>
+      <c r="W118" t="n">
+        <v>15</v>
+      </c>
+      <c r="X118" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>Estádio Dom Afonso Henriques</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Rua de São Gonçalo 505, Guimarães</t>
+        </is>
+      </c>
+      <c r="AC118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU118" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV118" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX118" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY118" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ118" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA118" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB118" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC118" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD118" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE118" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DF118" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DG118" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DH118" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DI118" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DJ118" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK118" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL118" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM118" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN118" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DO118" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW118" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="DX118" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="DY118" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="DZ118" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA118" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EB118" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EC118" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="ED118" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EE118" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EF118" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG118" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EH118" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EI118" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EJ118" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="EK118" t="inlineStr"/>
+      <c r="EL118" t="inlineStr"/>
+      <c r="EM118" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EN118" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EO118" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP118" t="inlineStr">
+        <is>
+          <t>1.72</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -55483,7 +55483,7 @@
         <v>9</v>
       </c>
       <c r="W115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X115" t="n">
         <v>14</v>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP124" headerRowCount="1">
-  <autoFilter ref="A1:EP124"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP127" headerRowCount="1">
+  <autoFilter ref="A1:EP127"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP124"/>
+  <dimension ref="A1:EP127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE3" t="n">
         <v>1.63</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         <v>1.38</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>1.29</v>
       </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE9" t="n">
         <v>1.29</v>
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6163,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8051,7 +8051,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9475,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10402,7 +10402,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE20" t="n">
         <v>2.71</v>
@@ -10435,7 +10435,7 @@
         <v>4.35</v>
       </c>
       <c r="DO20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10869,7 +10869,7 @@
         <v>1.86</v>
       </c>
       <c r="DE21" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10899,7 +10899,7 @@
         <v>0.87</v>
       </c>
       <c r="DO21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -12298,7 +12298,7 @@
         <v>100</v>
       </c>
       <c r="DD24" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE24" t="n">
         <v>1</v>
@@ -12331,7 +12331,7 @@
         <v>3.21</v>
       </c>
       <c r="DO24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12770,7 +12770,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE25" t="n">
         <v>0.14</v>
@@ -12803,7 +12803,7 @@
         <v>2.56</v>
       </c>
       <c r="DO25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13283,7 +13283,7 @@
         <v>2.05</v>
       </c>
       <c r="DO26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14239,7 +14239,7 @@
         <v>2.43</v>
       </c>
       <c r="DO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -15703,7 +15703,7 @@
         <v>3.82</v>
       </c>
       <c r="DO31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16191,7 +16191,7 @@
         <v>3.04</v>
       </c>
       <c r="DO32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16799,37 +16799,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45900.8125</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>8</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
         <v>2</v>
@@ -16844,116 +16844,108 @@
         <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T34" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V34" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="W34" t="n">
         <v>13</v>
       </c>
       <c r="X34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Z34" t="n">
-        <v>72</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Estádio do Rio Ave Futebol Clube</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
         <v>2</v>
       </c>
       <c r="AE34" t="n">
-        <v>4.36</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.81</v>
+        <v>3.96</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AL34" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AU34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
         <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
         <v>-1</v>
@@ -16977,37 +16969,37 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BM34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT34" t="n">
         <v>2</v>
@@ -17016,34 +17008,34 @@
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="BW34" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="BX34" t="n">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="BY34" t="n">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0.61</v>
+        <v>1.5</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.55</v>
+        <v>0.35</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.17</v>
+        <v>1.85</v>
       </c>
       <c r="CC34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD34" t="n">
         <v>0</v>
       </c>
       <c r="CE34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF34" t="n">
         <v>0</v>
@@ -17067,7 +17059,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -17082,10 +17074,10 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="CS34" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
@@ -17100,70 +17092,70 @@
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="CY34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA34" t="n">
         <v>50</v>
       </c>
-      <c r="DA34" t="n">
-        <v>100</v>
-      </c>
       <c r="DB34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC34" t="n">
         <v>100</v>
       </c>
       <c r="DD34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE34" t="n">
         <v>0.86</v>
       </c>
-      <c r="DE34" t="n">
-        <v>1.71</v>
-      </c>
       <c r="DF34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DH34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI34" t="n">
-        <v>2.33</v>
+        <v>0.67</v>
       </c>
       <c r="DJ34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK34" t="n">
         <v>50</v>
       </c>
-      <c r="DK34" t="n">
-        <v>0</v>
-      </c>
       <c r="DL34" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.54</v>
+        <v>1.12</v>
       </c>
       <c r="DN34" t="n">
-        <v>3.64</v>
+        <v>2.49</v>
       </c>
       <c r="DO34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT34" t="b">
         <v>0</v>
@@ -17172,102 +17164,86 @@
         <v>0</v>
       </c>
       <c r="DV34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW34" t="n">
-        <v>19.24</v>
+        <v>21.4</v>
       </c>
       <c r="DX34" t="n">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EK34" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="EL34" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EM34" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EN34" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr"/>
+      <c r="EL34" t="inlineStr"/>
+      <c r="EM34" t="inlineStr"/>
+      <c r="EN34" t="inlineStr"/>
       <c r="EO34" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EP34" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -17287,37 +17263,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>45900.8125</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L35" t="n">
         <v>8</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
         <v>2</v>
@@ -17332,108 +17308,116 @@
         <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="U35" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="W35" t="n">
         <v>13</v>
       </c>
       <c r="X35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y35" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z35" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Estádio do Rio Ave Futebol Clube</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Rua Dona Maria Pães Ribeiro, Vila do Conde</t>
+        </is>
+      </c>
       <c r="AC35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD35" t="n">
         <v>2</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>4.36</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.96</v>
+        <v>1.81</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="AJ35" t="n">
-        <v>5</v>
+        <v>3.12</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX35" t="n">
         <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB35" t="n">
         <v>-1</v>
@@ -17457,37 +17441,37 @@
         <v>1</v>
       </c>
       <c r="BI35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BM35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT35" t="n">
         <v>2</v>
@@ -17496,34 +17480,34 @@
         <v>1</v>
       </c>
       <c r="BV35" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="BW35" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="BX35" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="BY35" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1.5</v>
+        <v>0.61</v>
       </c>
       <c r="CA35" t="n">
-        <v>0.35</v>
+        <v>2.55</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="CC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD35" t="n">
         <v>0</v>
       </c>
       <c r="CE35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF35" t="n">
         <v>0</v>
@@ -17547,7 +17531,7 @@
         <v>0</v>
       </c>
       <c r="CM35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
@@ -17562,10 +17546,10 @@
         <v>1</v>
       </c>
       <c r="CR35" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="CS35" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="CT35" t="n">
         <v>1</v>
@@ -17580,70 +17564,70 @@
         <v>1</v>
       </c>
       <c r="CX35" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="CY35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CZ35" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA35" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB35" t="n">
         <v>50</v>
-      </c>
-      <c r="DB35" t="n">
-        <v>0</v>
       </c>
       <c r="DC35" t="n">
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.43</v>
+        <v>0.86</v>
       </c>
       <c r="DE35" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="DF35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI35" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
       <c r="DJ35" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK35" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL35" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="DM35" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="DN35" t="n">
-        <v>2.49</v>
+        <v>3.64</v>
       </c>
       <c r="DO35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT35" t="b">
         <v>0</v>
@@ -17652,86 +17636,102 @@
         <v>0</v>
       </c>
       <c r="DV35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW35" t="n">
-        <v>21.4</v>
+        <v>19.24</v>
       </c>
       <c r="DX35" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="DY35" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="DZ35" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA35" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EB35" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EC35" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="ED35" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EE35" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EF35" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EG35" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EH35" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI35" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EJ35" t="inlineStr">
         <is>
-          <t>6.16</t>
-        </is>
-      </c>
-      <c r="EK35" t="inlineStr"/>
-      <c r="EL35" t="inlineStr"/>
-      <c r="EM35" t="inlineStr"/>
-      <c r="EN35" t="inlineStr"/>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EK35" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EL35" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EM35" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EN35" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
       <c r="EO35" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EP35" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
         <v>1.29</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF36" t="n">
         <v>1</v>
@@ -18103,7 +18103,7 @@
         <v>1.84</v>
       </c>
       <c r="DO36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18529,7 +18529,7 @@
         <v>1.43</v>
       </c>
       <c r="DE37" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -18559,7 +18559,7 @@
         <v>2.39</v>
       </c>
       <c r="DO37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18993,7 +18993,7 @@
         <v>1.86</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF38" t="n">
         <v>3</v>
@@ -19023,7 +19023,7 @@
         <v>3.77</v>
       </c>
       <c r="DO38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19159,12 +19159,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -19180,19 +19180,19 @@
         <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -19201,122 +19201,122 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R39" t="n">
         <v>4</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
       </c>
       <c r="V39" t="n">
+        <v>15</v>
+      </c>
+      <c r="W39" t="n">
         <v>12</v>
       </c>
-      <c r="W39" t="n">
-        <v>11</v>
-      </c>
       <c r="X39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Z39" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Estádio António Coimbra da Mota</t>
+          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Rua Dom Bosco, Estoril</t>
+          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.42</v>
+        <v>3.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI39" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU39" t="n">
         <v>4</v>
       </c>
       <c r="AV39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY39" t="n">
         <v>1</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
@@ -19337,64 +19337,64 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM39" t="n">
         <v>2</v>
       </c>
       <c r="BN39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BO39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BP39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BT39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BW39" t="n">
         <v>39</v>
       </c>
       <c r="BX39" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BY39" t="n">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="CB39" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="CC39" t="n">
         <v>0</v>
@@ -19442,34 +19442,34 @@
         <v>1</v>
       </c>
       <c r="CR39" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS39" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU39" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX39" t="n">
         <v>10</v>
       </c>
-      <c r="CS39" t="n">
-        <v>31</v>
-      </c>
-      <c r="CT39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU39" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV39" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX39" t="n">
-        <v>17</v>
-      </c>
       <c r="CY39" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CZ39" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DA39" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB39" t="n">
         <v>25</v>
@@ -19478,37 +19478,37 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.14</v>
+        <v>1.43</v>
       </c>
       <c r="DF39" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DG39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DH39" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="DI39" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="DJ39" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK39" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL39" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="DM39" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="DN39" t="n">
-        <v>2.26</v>
+        <v>2.79</v>
       </c>
       <c r="DO39" t="n">
         <v>14</v>
@@ -19535,83 +19535,99 @@
         <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>20.1</v>
+        <v>22.33</v>
       </c>
       <c r="DX39" t="n">
-        <v>9.27</v>
+        <v>8.09</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="ED39" t="inlineStr"/>
-      <c r="EE39" t="inlineStr"/>
-      <c r="EF39" t="inlineStr"/>
-      <c r="EG39" t="inlineStr"/>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="ED39" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EE39" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EF39" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG39" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EI39" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -19631,12 +19647,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -19652,19 +19668,19 @@
         <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -19673,122 +19689,122 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
         <v>4</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U40" t="n">
         <v>15</v>
       </c>
       <c r="V40" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y40" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Z40" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
+          <t>Estádio António Coimbra da Mota</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
+          <t>Rua Dom Bosco, Estoril</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.25</v>
+        <v>4.42</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AR40" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU40" t="n">
         <v>4</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY40" t="n">
         <v>1</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB40" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
@@ -19809,64 +19825,64 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM40" t="n">
         <v>2</v>
       </c>
       <c r="BN40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BO40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BP40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BT40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BW40" t="n">
         <v>39</v>
       </c>
       <c r="BX40" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BY40" t="n">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="CB40" t="n">
-        <v>3.32</v>
+        <v>2.82</v>
       </c>
       <c r="CC40" t="n">
         <v>0</v>
@@ -19914,34 +19930,34 @@
         <v>1</v>
       </c>
       <c r="CR40" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CS40" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CV40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW40" t="n">
         <v>1</v>
       </c>
       <c r="CX40" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="CY40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ40" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA40" t="n">
         <v>75</v>
-      </c>
-      <c r="DA40" t="n">
-        <v>100</v>
       </c>
       <c r="DB40" t="n">
         <v>25</v>
@@ -19950,37 +19966,37 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.86</v>
+        <v>1.29</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.43</v>
+        <v>0.14</v>
       </c>
       <c r="DF40" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DG40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DH40" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="DI40" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="DJ40" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK40" t="n">
         <v>25</v>
       </c>
-      <c r="DK40" t="n">
-        <v>0</v>
-      </c>
       <c r="DL40" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="DM40" t="n">
-        <v>1.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DN40" t="n">
-        <v>2.79</v>
+        <v>2.26</v>
       </c>
       <c r="DO40" t="n">
         <v>14</v>
@@ -20007,99 +20023,83 @@
         <v>1</v>
       </c>
       <c r="DW40" t="n">
-        <v>22.33</v>
+        <v>20.1</v>
       </c>
       <c r="DX40" t="n">
-        <v>8.09</v>
+        <v>9.27</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="ED40" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EE40" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EF40" t="inlineStr">
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="ED40" t="inlineStr"/>
+      <c r="EE40" t="inlineStr"/>
+      <c r="EF40" t="inlineStr"/>
+      <c r="EG40" t="inlineStr"/>
+      <c r="EH40" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI40" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="EG40" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EH40" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EI40" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -20438,7 +20438,7 @@
         <v>100</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE41" t="n">
         <v>1.29</v>
@@ -20471,7 +20471,7 @@
         <v>3.36</v>
       </c>
       <c r="DO41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21363,7 +21363,7 @@
         <v>2.74</v>
       </c>
       <c r="DO43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22298,7 +22298,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE45" t="n">
         <v>1.63</v>
@@ -22331,7 +22331,7 @@
         <v>3.35</v>
       </c>
       <c r="DO45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22819,7 +22819,7 @@
         <v>2.94</v>
       </c>
       <c r="DO46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22955,46 +22955,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.60416666666</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>6</v>
@@ -23003,89 +23003,81 @@
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="X47" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Z47" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD47" t="n">
         <v>4</v>
       </c>
-      <c r="AD47" t="n">
-        <v>2</v>
-      </c>
       <c r="AE47" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.72</v>
+        <v>5.05</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AL47" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AO47" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS47" t="n">
         <v>2.47</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.48</v>
       </c>
       <c r="AT47" t="n">
         <v>1.3</v>
@@ -23094,25 +23086,25 @@
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX47" t="n">
         <v>1</v>
       </c>
       <c r="AY47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB47" t="n">
-        <v>167</v>
+        <v>1028</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
@@ -23127,70 +23119,70 @@
         <v>-1</v>
       </c>
       <c r="BG47" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH47" t="n">
         <v>1</v>
       </c>
       <c r="BI47" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS47" t="n">
         <v>4</v>
       </c>
-      <c r="BM47" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN47" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS47" t="n">
-        <v>1</v>
-      </c>
       <c r="BT47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU47" t="n">
         <v>1</v>
       </c>
       <c r="BV47" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="BW47" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="BX47" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="BY47" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="CC47" t="n">
         <v>1</v>
@@ -23217,97 +23209,97 @@
         <v>1</v>
       </c>
       <c r="CK47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL47" t="n">
         <v>0</v>
       </c>
       <c r="CM47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ47" t="n">
         <v>1</v>
       </c>
       <c r="CR47" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="CS47" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV47" t="n">
         <v>16</v>
       </c>
-      <c r="CT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU47" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV47" t="n">
-        <v>10</v>
-      </c>
       <c r="CW47" t="n">
         <v>1</v>
       </c>
       <c r="CX47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ47" t="n">
         <v>50</v>
       </c>
       <c r="DA47" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB47" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC47" t="n">
         <v>75</v>
       </c>
-      <c r="DC47" t="n">
-        <v>100</v>
-      </c>
       <c r="DD47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF47" t="n">
         <v>0.5</v>
-      </c>
-      <c r="DE47" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DF47" t="n">
-        <v>0</v>
       </c>
       <c r="DG47" t="n">
         <v>0.5</v>
       </c>
       <c r="DH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI47" t="n">
         <v>0.8</v>
-      </c>
-      <c r="DI47" t="n">
-        <v>1</v>
       </c>
       <c r="DJ47" t="n">
         <v>50</v>
       </c>
       <c r="DK47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="DM47" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DN47" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="DO47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23331,99 +23323,83 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>25.21</v>
+        <v>20.04</v>
       </c>
       <c r="DX47" t="n">
-        <v>6.42</v>
+        <v>5.58</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EC47" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EE47" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG47" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="EK47" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EL47" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EM47" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN47" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="EK47" t="inlineStr"/>
+      <c r="EL47" t="inlineStr"/>
+      <c r="EM47" t="inlineStr"/>
+      <c r="EN47" t="inlineStr"/>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
@@ -23443,46 +23419,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>45920.60416666666</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>6</v>
@@ -23491,81 +23467,89 @@
         <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W48" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="X48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Z48" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
       <c r="AC48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="AF48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR48" t="n">
         <v>3.15</v>
       </c>
-      <c r="AG48" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AS48" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AT48" t="n">
         <v>1.3</v>
@@ -23574,25 +23558,25 @@
         <v>3</v>
       </c>
       <c r="AV48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
         <v>1</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1028</v>
+        <v>167</v>
       </c>
       <c r="BC48" t="n">
         <v>0</v>
@@ -23607,187 +23591,187 @@
         <v>-1</v>
       </c>
       <c r="BG48" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH48" t="n">
         <v>1</v>
       </c>
       <c r="BI48" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BJ48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL48" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BM48" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN48" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO48" t="n">
         <v>1</v>
       </c>
       <c r="BP48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>59</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR48" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX48" t="n">
         <v>5</v>
       </c>
-      <c r="BR48" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS48" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT48" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU48" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV48" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW48" t="n">
-        <v>27</v>
-      </c>
-      <c r="BX48" t="n">
-        <v>93</v>
-      </c>
-      <c r="BY48" t="n">
-        <v>70</v>
-      </c>
-      <c r="BZ48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CA48" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="CB48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CC48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS48" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU48" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV48" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX48" t="n">
-        <v>1</v>
-      </c>
       <c r="CY48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ48" t="n">
         <v>50</v>
       </c>
       <c r="DA48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB48" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DC48" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.43</v>
+        <v>0.86</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DF48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DG48" t="n">
         <v>0.5</v>
       </c>
       <c r="DH48" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DI48" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DJ48" t="n">
         <v>50</v>
       </c>
       <c r="DK48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL48" t="n">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DM48" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="DN48" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="DO48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23811,83 +23795,99 @@
         <v>1</v>
       </c>
       <c r="DW48" t="n">
-        <v>20.04</v>
+        <v>25.21</v>
       </c>
       <c r="DX48" t="n">
-        <v>5.58</v>
+        <v>6.42</v>
       </c>
       <c r="DY48" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="DZ48" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA48" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="EB48" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EC48" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="ED48" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EE48" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EF48" t="inlineStr">
         <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EG48" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH48" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EI48" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EJ48" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EK48" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EL48" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EM48" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN48" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EO48" t="inlineStr">
+        <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="EG48" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EH48" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EI48" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EJ48" t="inlineStr">
-        <is>
-          <t>5.09</t>
-        </is>
-      </c>
-      <c r="EK48" t="inlineStr"/>
-      <c r="EL48" t="inlineStr"/>
-      <c r="EM48" t="inlineStr"/>
-      <c r="EN48" t="inlineStr"/>
-      <c r="EO48" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
       <c r="EP48" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -24739,7 +24739,7 @@
         <v>3.53</v>
       </c>
       <c r="DO50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25197,7 +25197,7 @@
         <v>0.33</v>
       </c>
       <c r="DE51" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF51" t="n">
         <v>0.5</v>
@@ -25227,7 +25227,7 @@
         <v>2.25</v>
       </c>
       <c r="DO51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -28541,7 +28541,7 @@
         <v>1.43</v>
       </c>
       <c r="DE58" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF58" t="n">
         <v>1.33</v>
@@ -28571,7 +28571,7 @@
         <v>2.71</v>
       </c>
       <c r="DO58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29051,7 +29051,7 @@
         <v>2.43</v>
       </c>
       <c r="DO59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -30450,7 +30450,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE62" t="n">
         <v>1.29</v>
@@ -30483,7 +30483,7 @@
         <v>2.74</v>
       </c>
       <c r="DO62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31435,7 +31435,7 @@
         <v>2.94</v>
       </c>
       <c r="DO64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32015,170 +32015,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L66" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
         <v>7</v>
       </c>
       <c r="R66" t="n">
+        <v>4</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="n">
+        <v>6</v>
+      </c>
+      <c r="U66" t="n">
+        <v>17</v>
+      </c>
+      <c r="V66" t="n">
+        <v>10</v>
+      </c>
+      <c r="W66" t="n">
+        <v>12</v>
+      </c>
+      <c r="X66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="n">
         <v>5</v>
       </c>
-      <c r="S66" t="n">
-        <v>8</v>
-      </c>
-      <c r="T66" t="n">
-        <v>10</v>
-      </c>
-      <c r="U66" t="n">
-        <v>15</v>
-      </c>
-      <c r="V66" t="n">
-        <v>15</v>
-      </c>
-      <c r="W66" t="n">
-        <v>13</v>
-      </c>
-      <c r="X66" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Estádio Cidade de Barcelos</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>strada Nacional 103, Vila Boa, Barcelos</t>
-        </is>
-      </c>
-      <c r="AC66" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>3</v>
-      </c>
       <c r="AE66" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="AF66" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AG66" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI66" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AK66" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AN66" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AO66" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR66" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AU66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
         <v>2</v>
       </c>
       <c r="BB66" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32193,181 +32193,181 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM66" t="n">
         <v>4</v>
       </c>
-      <c r="BJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL66" t="n">
+      <c r="BN66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS66" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU66" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV66" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX66" t="n">
         <v>6</v>
-      </c>
-      <c r="BM66" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN66" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT66" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV66" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW66" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>83</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CB66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CC66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS66" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX66" t="n">
-        <v>8</v>
       </c>
       <c r="CY66" t="n">
         <v>8</v>
       </c>
       <c r="CZ66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA66" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DB66" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DC66" t="n">
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>2</v>
+        <v>0.86</v>
       </c>
       <c r="DE66" t="n">
         <v>1</v>
       </c>
       <c r="DF66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DG66" t="n">
         <v>1</v>
       </c>
       <c r="DH66" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="DI66" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DJ66" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK66" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="DO66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32376,69 +32376,69 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU66" t="b">
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW66" t="n">
-        <v>25.52</v>
+        <v>24.96</v>
       </c>
       <c r="DX66" t="n">
-        <v>6.19</v>
+        <v>6.88</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EE66" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF66" t="inlineStr">
+        <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="EE66" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EF66" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
@@ -32448,42 +32448,42 @@
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -32503,170 +32503,170 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
         <v>5</v>
       </c>
-      <c r="J67" t="n">
-        <v>2</v>
-      </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L67" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>7</v>
       </c>
       <c r="R67" t="n">
+        <v>5</v>
+      </c>
+      <c r="S67" t="n">
+        <v>8</v>
+      </c>
+      <c r="T67" t="n">
+        <v>10</v>
+      </c>
+      <c r="U67" t="n">
+        <v>15</v>
+      </c>
+      <c r="V67" t="n">
+        <v>15</v>
+      </c>
+      <c r="W67" t="n">
+        <v>13</v>
+      </c>
+      <c r="X67" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Estádio Cidade de Barcelos</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>strada Nacional 103, Vila Boa, Barcelos</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
         <v>4</v>
       </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="n">
-        <v>6</v>
-      </c>
-      <c r="U67" t="n">
-        <v>17</v>
-      </c>
-      <c r="V67" t="n">
-        <v>10</v>
-      </c>
-      <c r="W67" t="n">
-        <v>12</v>
-      </c>
-      <c r="X67" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
-      <c r="AC67" t="n">
-        <v>1</v>
-      </c>
       <c r="AD67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="AF67" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AG67" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AI67" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ67" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AL67" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AN67" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AO67" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AR67" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AS67" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AU67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
       </c>
       <c r="BB67" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32681,73 +32681,73 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM67" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT67" t="n">
         <v>4</v>
       </c>
-      <c r="BN67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT67" t="n">
-        <v>3</v>
-      </c>
       <c r="BU67" t="n">
         <v>1</v>
       </c>
       <c r="BV67" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BW67" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="BX67" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="BY67" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BZ67" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="CA67" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="CB67" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="CC67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD67" t="n">
         <v>0</v>
       </c>
       <c r="CE67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF67" t="n">
         <v>0</v>
@@ -32768,10 +32768,10 @@
         <v>0</v>
       </c>
       <c r="CL67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN67" t="n">
         <v>0</v>
@@ -32786,76 +32786,76 @@
         <v>1</v>
       </c>
       <c r="CR67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS67" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT67" t="n">
         <v>1</v>
       </c>
       <c r="CU67" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW67" t="n">
         <v>1</v>
       </c>
       <c r="CX67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY67" t="n">
         <v>8</v>
       </c>
       <c r="CZ67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA67" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DB67" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DC67" t="n">
         <v>50</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DE67" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DG67" t="n">
         <v>1</v>
       </c>
       <c r="DH67" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="DI67" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="DJ67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK67" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="DM67" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="DN67" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="DO67" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32864,114 +32864,114 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU67" t="b">
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW67" t="n">
-        <v>24.96</v>
+        <v>25.52</v>
       </c>
       <c r="DX67" t="n">
-        <v>6.88</v>
+        <v>6.19</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA67" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="EB67" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EC67" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="ED67" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EE67" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EH67" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI67" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ67" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EK67" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EL67" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM67" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN67" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EO67" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP67" t="inlineStr">
+        <is>
           <t>1.72</t>
-        </is>
-      </c>
-      <c r="EH67" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI67" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ67" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="EK67" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="EL67" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EM67" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EN67" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EO67" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EP67" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -33773,7 +33773,7 @@
         <v>1.71</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF69" t="n">
         <v>1.67</v>
@@ -33803,7 +33803,7 @@
         <v>2.48</v>
       </c>
       <c r="DO69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34741,7 +34741,7 @@
         <v>0.86</v>
       </c>
       <c r="DE71" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF71" t="n">
         <v>0.67</v>
@@ -34771,7 +34771,7 @@
         <v>2.4</v>
       </c>
       <c r="DO71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35227,7 +35227,7 @@
         <v>4.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35682,7 +35682,7 @@
         <v>84</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE73" t="n">
         <v>2.71</v>
@@ -35715,7 +35715,7 @@
         <v>3.37</v>
       </c>
       <c r="DO73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36675,7 +36675,7 @@
         <v>2.53</v>
       </c>
       <c r="DO75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37627,7 +37627,7 @@
         <v>2.46</v>
       </c>
       <c r="DO77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38115,7 +38115,7 @@
         <v>2.38</v>
       </c>
       <c r="DO78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -39083,7 +39083,7 @@
         <v>3.65</v>
       </c>
       <c r="DO80" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39522,7 +39522,7 @@
         <v>100</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE81" t="n">
         <v>1</v>
@@ -39555,7 +39555,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40043,7 +40043,7 @@
         <v>3.06</v>
       </c>
       <c r="DO82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40958,7 +40958,7 @@
         <v>38</v>
       </c>
       <c r="DD84" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE84" t="n">
         <v>2</v>
@@ -40991,7 +40991,7 @@
         <v>2.85</v>
       </c>
       <c r="DO84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41929,7 +41929,7 @@
         <v>0.43</v>
       </c>
       <c r="DE86" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF86" t="n">
         <v>0.5</v>
@@ -41959,7 +41959,7 @@
         <v>2.12</v>
       </c>
       <c r="DO86" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42897,7 +42897,7 @@
         <v>0.29</v>
       </c>
       <c r="DE88" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF88" t="n">
         <v>0</v>
@@ -42927,7 +42927,7 @@
         <v>2.27</v>
       </c>
       <c r="DO88" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43870,7 +43870,7 @@
         <v>88</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE90" t="n">
         <v>1.71</v>
@@ -43903,7 +43903,7 @@
         <v>3.54</v>
       </c>
       <c r="DO90" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44361,7 +44361,7 @@
         <v>2</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF91" t="n">
         <v>2.25</v>
@@ -44391,7 +44391,7 @@
         <v>2.73</v>
       </c>
       <c r="DO91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -45831,7 +45831,7 @@
         <v>2.92</v>
       </c>
       <c r="DO94" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46295,7 +46295,7 @@
         <v>3.79</v>
       </c>
       <c r="DO95" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46743,7 +46743,7 @@
         <v>2.53</v>
       </c>
       <c r="DO96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47667,7 +47667,7 @@
         <v>3.3</v>
       </c>
       <c r="DO98" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48578,7 +48578,7 @@
         <v>80</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE100" t="n">
         <v>1</v>
@@ -48611,7 +48611,7 @@
         <v>2.42</v>
       </c>
       <c r="DO100" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -50498,7 +50498,7 @@
         <v>60</v>
       </c>
       <c r="DD104" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE104" t="n">
         <v>2.71</v>
@@ -50531,7 +50531,7 @@
         <v>2.81</v>
       </c>
       <c r="DO104" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50973,7 +50973,7 @@
         <v>2</v>
       </c>
       <c r="DE105" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF105" t="n">
         <v>2.4</v>
@@ -51003,7 +51003,7 @@
         <v>2.67</v>
       </c>
       <c r="DO105" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51461,7 +51461,7 @@
         <v>0.86</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF106" t="n">
         <v>1</v>
@@ -51491,7 +51491,7 @@
         <v>2.31</v>
       </c>
       <c r="DO106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51941,7 +51941,7 @@
         <v>2.29</v>
       </c>
       <c r="DE107" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF107" t="n">
         <v>2</v>
@@ -51971,7 +51971,7 @@
         <v>3.36</v>
       </c>
       <c r="DO107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52410,7 +52410,7 @@
         <v>90</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE108" t="n">
         <v>0.71</v>
@@ -52443,7 +52443,7 @@
         <v>3.13</v>
       </c>
       <c r="DO108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52923,7 +52923,7 @@
         <v>2.9</v>
       </c>
       <c r="DO109" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53855,7 +53855,7 @@
         <v>2.39</v>
       </c>
       <c r="DO111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54815,7 +54815,7 @@
         <v>3.14</v>
       </c>
       <c r="DO113" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55423,138 +55423,146 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K115" t="n">
+        <v>2</v>
+      </c>
+      <c r="L115" t="n">
         <v>4</v>
       </c>
-      <c r="J115" t="n">
-        <v>5</v>
-      </c>
-      <c r="K115" t="n">
-        <v>3</v>
-      </c>
-      <c r="L115" t="n">
-        <v>8</v>
-      </c>
       <c r="M115" t="n">
         <v>1</v>
       </c>
       <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
         <v>4</v>
       </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>9</v>
-      </c>
       <c r="R115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T115" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U115" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V115" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W115" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X115" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y115" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="Z115" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA115" t="inlineStr"/>
-      <c r="AB115" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Complexo Desportivo FC Alverca</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
+        </is>
+      </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE115" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AG115" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AJ115" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL115" t="n">
         <v>1.92</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AU115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW115" t="n">
         <v>0</v>
@@ -55563,22 +55571,22 @@
         <v>1</v>
       </c>
       <c r="AY115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>15804</v>
+        <v>10708</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55593,64 +55601,64 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR115" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT115" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="BW115" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="BX115" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="BY115" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="BZ115" t="n">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="CA115" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="CB115" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
@@ -55683,10 +55691,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55701,85 +55709,85 @@
         <v>21</v>
       </c>
       <c r="CS115" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM115" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN115" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DO115" t="n">
         <v>14</v>
       </c>
-      <c r="CV115" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX115" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY115" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ115" t="n">
-        <v>65</v>
-      </c>
-      <c r="DA115" t="n">
-        <v>92</v>
-      </c>
-      <c r="DB115" t="n">
-        <v>57</v>
-      </c>
-      <c r="DC115" t="n">
-        <v>82</v>
-      </c>
-      <c r="DD115" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DE115" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DF115" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="DG115" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DH115" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI115" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DJ115" t="n">
-        <v>35</v>
-      </c>
-      <c r="DK115" t="n">
-        <v>9</v>
-      </c>
-      <c r="DL115" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DM115" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="DN115" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="DO115" t="n">
-        <v>13</v>
-      </c>
       <c r="DP115" t="b">
         <v>1</v>
       </c>
       <c r="DQ115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT115" t="b">
         <v>0</v>
@@ -55788,17 +55796,17 @@
         <v>0</v>
       </c>
       <c r="DV115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW115" t="n">
-        <v>16.07</v>
+        <v>16.34</v>
       </c>
       <c r="DX115" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
@@ -55808,23 +55816,39 @@
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="ED115" t="inlineStr"/>
-      <c r="EE115" t="inlineStr"/>
-      <c r="EF115" t="inlineStr"/>
-      <c r="EG115" t="inlineStr"/>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="ED115" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE115" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF115" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EG115" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
       <c r="EH115" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -55832,42 +55856,26 @@
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="EK115" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="EL115" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EM115" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN115" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr"/>
+      <c r="EL115" t="inlineStr"/>
+      <c r="EM115" t="inlineStr"/>
+      <c r="EN115" t="inlineStr"/>
       <c r="EO115" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -55887,146 +55895,138 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L116" t="n">
+        <v>8</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
         <v>4</v>
       </c>
-      <c r="M116" t="n">
-        <v>1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>1</v>
-      </c>
       <c r="O116" t="n">
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S116" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T116" t="n">
+        <v>7</v>
+      </c>
+      <c r="U116" t="n">
+        <v>24</v>
+      </c>
+      <c r="V116" t="n">
+        <v>9</v>
+      </c>
+      <c r="W116" t="n">
+        <v>12</v>
+      </c>
+      <c r="X116" t="n">
         <v>14</v>
       </c>
-      <c r="U116" t="n">
-        <v>10</v>
-      </c>
-      <c r="V116" t="n">
-        <v>17</v>
-      </c>
-      <c r="W116" t="n">
-        <v>10</v>
-      </c>
-      <c r="X116" t="n">
-        <v>19</v>
-      </c>
       <c r="Y116" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="Z116" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>Complexo Desportivo FC Alverca</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE116" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AG116" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI116" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AJ116" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL116" t="n">
         <v>1.92</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AN116" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW116" t="n">
         <v>0</v>
@@ -56035,22 +56035,22 @@
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB116" t="n">
-        <v>10708</v>
+        <v>15804</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -56065,64 +56065,64 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU116" t="n">
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BW116" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="BX116" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="BY116" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="BZ116" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="CA116" t="n">
-        <v>1.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB116" t="n">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
@@ -56155,10 +56155,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -56173,85 +56173,85 @@
         <v>21</v>
       </c>
       <c r="CS116" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV116" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CW116" t="n">
         <v>1</v>
       </c>
       <c r="CX116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY116" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CZ116" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="DA116" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="DB116" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="DC116" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="DF116" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="DG116" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="DH116" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="DI116" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DJ116" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="DK116" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.21</v>
+        <v>0.87</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="DO116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
       </c>
       <c r="DQ116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT116" t="b">
         <v>0</v>
@@ -56260,17 +56260,17 @@
         <v>0</v>
       </c>
       <c r="DV116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW116" t="n">
-        <v>16.34</v>
+        <v>16.07</v>
       </c>
       <c r="DX116" t="n">
-        <v>5.53</v>
+        <v>5.47</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
@@ -56280,39 +56280,23 @@
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="ED116" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EE116" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EF116" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EG116" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr"/>
+      <c r="EE116" t="inlineStr"/>
+      <c r="EF116" t="inlineStr"/>
+      <c r="EG116" t="inlineStr"/>
       <c r="EH116" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -56320,26 +56304,42 @@
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="EK116" t="inlineStr"/>
-      <c r="EL116" t="inlineStr"/>
-      <c r="EM116" t="inlineStr"/>
-      <c r="EN116" t="inlineStr"/>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EL116" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EM116" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN116" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -56711,7 +56711,7 @@
         <v>3.31</v>
       </c>
       <c r="DO117" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -58822,7 +58822,7 @@
         <v>10</v>
       </c>
       <c r="X122" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y122" t="n">
         <v>54</v>
@@ -59034,7 +59034,7 @@
         <v>1</v>
       </c>
       <c r="CR122" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CS122" t="n">
         <v>14</v>
@@ -59043,7 +59043,7 @@
         <v>1</v>
       </c>
       <c r="CU122" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CV122" t="n">
         <v>10</v>
@@ -59632,77 +59632,77 @@
       </c>
       <c r="EA123" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr">
+        <is>
+          <t>8.70</t>
+        </is>
+      </c>
+      <c r="ED123" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EE123" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EF123" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EG123" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EL123" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EM123" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="EB123" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="EC123" t="inlineStr">
-        <is>
-          <t>8.80</t>
-        </is>
-      </c>
-      <c r="ED123" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="EE123" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EF123" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EG123" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EH123" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EI123" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EJ123" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="EK123" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="EL123" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EM123" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
       <c r="EN123" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EO123" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EP123" t="inlineStr">
@@ -60120,82 +60120,1490 @@
       </c>
       <c r="EA124" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EB124" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EC124" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="ED124" t="inlineStr">
         <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EE124" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EF124" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EG124" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EH124" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EL124" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM124" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN124" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EO124" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EP124" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>14</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CD Nacional</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>CD Tondela</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>46006.72916666666</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="n">
+        <v>4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>3</v>
+      </c>
+      <c r="K125" t="n">
+        <v>10</v>
+      </c>
+      <c r="L125" t="n">
+        <v>13</v>
+      </c>
+      <c r="M125" t="n">
+        <v>5</v>
+      </c>
+      <c r="N125" t="n">
+        <v>6</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>4</v>
+      </c>
+      <c r="R125" t="n">
+        <v>5</v>
+      </c>
+      <c r="S125" t="n">
+        <v>4</v>
+      </c>
+      <c r="T125" t="n">
+        <v>16</v>
+      </c>
+      <c r="U125" t="n">
+        <v>8</v>
+      </c>
+      <c r="V125" t="n">
+        <v>21</v>
+      </c>
+      <c r="W125" t="n">
+        <v>11</v>
+      </c>
+      <c r="X125" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>163</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>69</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>31</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DM125" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DN125" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DO125" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW125" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="DX125" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="DZ125" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="EA125" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EB125" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC125" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="ED125" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EE125" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EF125" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EG125" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI125" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EJ125" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EK125" t="inlineStr"/>
+      <c r="EL125" t="inlineStr"/>
+      <c r="EM125" t="inlineStr"/>
+      <c r="EN125" t="inlineStr"/>
+      <c r="EO125" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP125" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>14</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>46006.78125</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>5</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" t="n">
+        <v>6</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>3</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2</v>
+      </c>
+      <c r="S126" t="n">
+        <v>3</v>
+      </c>
+      <c r="T126" t="n">
+        <v>3</v>
+      </c>
+      <c r="U126" t="n">
+        <v>6</v>
+      </c>
+      <c r="V126" t="n">
+        <v>5</v>
+      </c>
+      <c r="W126" t="n">
+        <v>10</v>
+      </c>
+      <c r="X126" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK126" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DO126" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW126" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="DX126" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="DY126" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="DZ126" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA126" t="inlineStr">
+        <is>
+          <t>8.42</t>
+        </is>
+      </c>
+      <c r="EB126" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="EC126" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="ED126" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EE126" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EF126" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG126" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EH126" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EJ126" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr"/>
+      <c r="EL126" t="inlineStr"/>
+      <c r="EM126" t="inlineStr"/>
+      <c r="EN126" t="inlineStr"/>
+      <c r="EO126" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EP126" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>14</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>46006.86458333334</v>
+      </c>
+      <c r="G127" t="n">
+        <v>3</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="n">
+        <v>4</v>
+      </c>
+      <c r="J127" t="n">
+        <v>4</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>4</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" t="n">
+        <v>5</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>6</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1</v>
+      </c>
+      <c r="S127" t="n">
+        <v>14</v>
+      </c>
+      <c r="T127" t="n">
+        <v>5</v>
+      </c>
+      <c r="U127" t="n">
+        <v>20</v>
+      </c>
+      <c r="V127" t="n">
+        <v>6</v>
+      </c>
+      <c r="W127" t="n">
+        <v>13</v>
+      </c>
+      <c r="X127" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Estádio Do Dragão</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>Via Futebol Clube do Porto, Porto</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>82</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW127" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="DX127" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>17.50</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>7.62</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="ED127" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE127" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF127" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EG127" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EH127" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EI127" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EJ127" t="inlineStr">
+        <is>
           <t>2.37</t>
         </is>
       </c>
-      <c r="EE124" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EF124" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EG124" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EH124" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI124" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EJ124" t="inlineStr">
-        <is>
-          <t>4.32</t>
-        </is>
-      </c>
-      <c r="EK124" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="EL124" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EM124" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN124" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="EO124" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EP124" t="inlineStr">
-        <is>
-          <t>1.91</t>
+      <c r="EK127" t="inlineStr"/>
+      <c r="EL127" t="inlineStr"/>
+      <c r="EM127" t="inlineStr"/>
+      <c r="EN127" t="inlineStr"/>
+      <c r="EO127" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EP127" t="inlineStr">
+        <is>
+          <t>1.52</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -60753,10 +60753,10 @@
         <v>15</v>
       </c>
       <c r="Y126" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Z126" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr"/>
@@ -61193,7 +61193,7 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R127" t="n">
         <v>1</v>
@@ -61205,7 +61205,7 @@
         <v>5</v>
       </c>
       <c r="U127" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V127" t="n">
         <v>6</v>
@@ -61380,13 +61380,13 @@
         <v>79</v>
       </c>
       <c r="BZ127" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="CA127" t="n">
         <v>0.53</v>
       </c>
       <c r="CB127" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="CC127" t="n">
         <v>1</v>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP136" headerRowCount="1">
-  <autoFilter ref="A1:EP136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP138" headerRowCount="1">
+  <autoFilter ref="A1:EP138"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP136"/>
+  <dimension ref="A1:EP138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE5" t="n">
         <v>0.71</v>
@@ -4213,7 +4213,7 @@
         <v>1.86</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4698,10 +4698,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE23" t="n">
         <v>1.63</v>
@@ -13253,7 +13253,7 @@
         <v>1.13</v>
       </c>
       <c r="DE26" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -13283,7 +13283,7 @@
         <v>2.05</v>
       </c>
       <c r="DO26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14375,37 +14375,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
         <v>45899.70833333334</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
         <v>4</v>
@@ -14414,7 +14414,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
@@ -14423,122 +14423,122 @@
         <v>3</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y29" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Z29" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Estádio Clube Desportivo das Aves</t>
+          <t>Estádio Dom Afonso Henriques</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
+          <t>Rua de São Gonçalo 505, Guimarães</t>
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>4.05</v>
+        <v>1.78</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.79</v>
+        <v>4.15</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AO29" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB29" t="n">
-        <v>1033</v>
+        <v>-1</v>
       </c>
       <c r="BC29" t="n">
         <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE29" t="n">
         <v>0</v>
@@ -14547,70 +14547,70 @@
         <v>-1</v>
       </c>
       <c r="BG29" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH29" t="n">
         <v>1</v>
       </c>
       <c r="BI29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BK29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL29" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BN29" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO29" t="n">
         <v>0</v>
       </c>
       <c r="BP29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR29" t="n">
         <v>4</v>
       </c>
       <c r="BS29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BU29" t="n">
         <v>1</v>
       </c>
       <c r="BV29" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="BW29" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="BX29" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="BY29" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.35</v>
+        <v>0.93</v>
       </c>
       <c r="CB29" t="n">
-        <v>2.69</v>
+        <v>2.12</v>
       </c>
       <c r="CC29" t="n">
         <v>0</v>
@@ -14643,10 +14643,10 @@
         <v>0</v>
       </c>
       <c r="CM29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO29" t="n">
         <v>0</v>
@@ -14658,73 +14658,73 @@
         <v>1</v>
       </c>
       <c r="CR29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CS29" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="CT29" t="n">
         <v>1</v>
       </c>
       <c r="CU29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW29" t="n">
         <v>1</v>
       </c>
       <c r="CX29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CY29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CZ29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DA29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DC29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>0.38</v>
+        <v>1.5</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.71</v>
+        <v>0.71</v>
       </c>
       <c r="DF29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH29" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DI29" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="DJ29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL29" t="n">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="DM29" t="n">
-        <v>1.71</v>
+        <v>0.64</v>
       </c>
       <c r="DN29" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="DO29" t="n">
         <v>15</v>
@@ -14733,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="DQ29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR29" t="b">
         <v>0</v>
@@ -14748,13 +14748,13 @@
         <v>0</v>
       </c>
       <c r="DV29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW29" t="n">
-        <v>26.39</v>
+        <v>25.71</v>
       </c>
       <c r="DX29" t="n">
-        <v>5.3</v>
+        <v>5.57</v>
       </c>
       <c r="DY29" t="inlineStr">
         <is>
@@ -14763,32 +14763,32 @@
       </c>
       <c r="DZ29" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="EA29" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EB29" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EC29" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="ED29" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EE29" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EF29" t="inlineStr">
@@ -14798,52 +14798,52 @@
       </c>
       <c r="EG29" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EH29" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EI29" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ29" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK29" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EL29" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EM29" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EN29" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EO29" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EP29" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -14863,37 +14863,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>45899.70833333334</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -14902,7 +14902,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>3</v>
@@ -14911,122 +14911,122 @@
         <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="Z30" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Estádio Dom Afonso Henriques</t>
+          <t>Estádio Clube Desportivo das Aves</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Rua de São Gonçalo 505, Guimarães</t>
+          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.78</v>
+        <v>4.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>4.15</v>
+        <v>1.79</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AO30" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>-1</v>
+        <v>1033</v>
       </c>
       <c r="BC30" t="n">
         <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
         <v>0</v>
@@ -15035,184 +15035,184 @@
         <v>-1</v>
       </c>
       <c r="BG30" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH30" t="n">
         <v>1</v>
       </c>
       <c r="BI30" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BK30" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL30" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM30" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BN30" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO30" t="n">
         <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR30" t="n">
         <v>4</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX30" t="n">
         <v>8</v>
       </c>
-      <c r="BU30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>20</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>105</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>61</v>
-      </c>
-      <c r="BZ30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CA30" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="CB30" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS30" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU30" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV30" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX30" t="n">
-        <v>9</v>
-      </c>
       <c r="CY30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ30" t="n">
         <v>100</v>
       </c>
-      <c r="DA30" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB30" t="n">
-        <v>100</v>
-      </c>
-      <c r="DC30" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE30" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DF30" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH30" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DJ30" t="n">
-        <v>0</v>
-      </c>
       <c r="DK30" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL30" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="DM30" t="n">
-        <v>0.64</v>
+        <v>1.71</v>
       </c>
       <c r="DN30" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="DO30" t="n">
         <v>15</v>
@@ -15221,7 +15221,7 @@
         <v>1</v>
       </c>
       <c r="DQ30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR30" t="b">
         <v>0</v>
@@ -15236,13 +15236,13 @@
         <v>0</v>
       </c>
       <c r="DV30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW30" t="n">
-        <v>25.71</v>
+        <v>26.39</v>
       </c>
       <c r="DX30" t="n">
-        <v>5.57</v>
+        <v>5.3</v>
       </c>
       <c r="DY30" t="inlineStr">
         <is>
@@ -15251,32 +15251,32 @@
       </c>
       <c r="DZ30" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="EA30" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EB30" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC30" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="ED30" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EE30" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EF30" t="inlineStr">
@@ -15286,52 +15286,52 @@
       </c>
       <c r="EG30" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EH30" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI30" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ30" t="inlineStr">
+        <is>
+          <t>4.56</t>
+        </is>
+      </c>
+      <c r="EK30" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EL30" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="EI30" t="inlineStr">
+      <c r="EM30" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EN30" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EO30" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="EJ30" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
-      </c>
-      <c r="EK30" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EL30" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EM30" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN30" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="EO30" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
       <c r="EP30" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -17113,7 +17113,7 @@
         <v>1.38</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -18070,7 +18070,7 @@
         <v>100</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE36" t="n">
         <v>0.71</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -18222,147 +18222,155 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>4</v>
       </c>
-      <c r="K37" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>9</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>7</v>
-      </c>
       <c r="R37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8</v>
+      </c>
+      <c r="U37" t="n">
         <v>12</v>
       </c>
-      <c r="T37" t="n">
-        <v>4</v>
-      </c>
-      <c r="U37" t="n">
-        <v>19</v>
-      </c>
       <c r="V37" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W37" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="X37" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y37" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="Z37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Complexo Desportivo FC Alverca</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
+        </is>
+      </c>
       <c r="AC37" t="n">
         <v>1</v>
       </c>
       <c r="AD37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.3</v>
+        <v>2.23</v>
       </c>
       <c r="AF37" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW37" t="n">
         <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB37" t="n">
-        <v>-1</v>
+        <v>10708</v>
       </c>
       <c r="BC37" t="n">
         <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE37" t="n">
         <v>0</v>
@@ -18371,184 +18379,184 @@
         <v>-1</v>
       </c>
       <c r="BG37" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH37" t="n">
         <v>1</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BJ37" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BK37" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BL37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BM37" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BN37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>74</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR37" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>34</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY37" t="n">
         <v>5</v>
       </c>
-      <c r="BO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP37" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS37" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU37" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV37" t="n">
-        <v>115</v>
-      </c>
-      <c r="BW37" t="n">
-        <v>17</v>
-      </c>
-      <c r="BX37" t="n">
-        <v>182</v>
-      </c>
-      <c r="BY37" t="n">
-        <v>48</v>
-      </c>
-      <c r="BZ37" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="CA37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB37" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="CC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>25</v>
-      </c>
-      <c r="CS37" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU37" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV37" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX37" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY37" t="n">
-        <v>14</v>
-      </c>
       <c r="CZ37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DA37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DC37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="DF37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DH37" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="DI37" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="DJ37" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DK37" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL37" t="n">
-        <v>2.61</v>
+        <v>1.41</v>
       </c>
       <c r="DM37" t="n">
-        <v>1.16</v>
+        <v>0.98</v>
       </c>
       <c r="DN37" t="n">
-        <v>3.77</v>
+        <v>2.39</v>
       </c>
       <c r="DO37" t="n">
         <v>15</v>
@@ -18557,7 +18565,7 @@
         <v>1</v>
       </c>
       <c r="DQ37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR37" t="b">
         <v>0</v>
@@ -18572,102 +18580,86 @@
         <v>0</v>
       </c>
       <c r="DV37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW37" t="n">
-        <v>27.44</v>
+        <v>25.94</v>
       </c>
       <c r="DX37" t="n">
-        <v>6.53</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DY37" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ37" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="EA37" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EB37" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EC37" t="inlineStr">
         <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="ED37" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EE37" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EF37" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EG37" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="ED37" t="inlineStr"/>
+      <c r="EE37" t="inlineStr"/>
+      <c r="EF37" t="inlineStr"/>
+      <c r="EG37" t="inlineStr"/>
       <c r="EH37" t="inlineStr">
         <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="EK37" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EL37" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="EI37" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EJ37" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="EK37" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EL37" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
       <c r="EM37" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EN37" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EO37" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EP37" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.94</t>
         </is>
       </c>
     </row>
@@ -18687,12 +18679,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -18702,155 +18694,147 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" t="n">
         <v>5</v>
       </c>
-      <c r="K38" t="n">
-        <v>6</v>
-      </c>
       <c r="L38" t="n">
+        <v>9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>7</v>
+      </c>
+      <c r="R38" t="n">
+        <v>5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>12</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>19</v>
+      </c>
+      <c r="V38" t="n">
+        <v>9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>8</v>
+      </c>
+      <c r="X38" t="n">
         <v>11</v>
       </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6</v>
-      </c>
-      <c r="S38" t="n">
-        <v>8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>8</v>
-      </c>
-      <c r="U38" t="n">
-        <v>12</v>
-      </c>
-      <c r="V38" t="n">
-        <v>14</v>
-      </c>
-      <c r="W38" t="n">
-        <v>13</v>
-      </c>
-      <c r="X38" t="n">
-        <v>15</v>
-      </c>
       <c r="Y38" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="Z38" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Complexo Desportivo FC Alverca</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
         <v>1</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="AG38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR38" t="n">
         <v>2.9</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AS38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT38" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AU38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
         <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>10708</v>
+        <v>-1</v>
       </c>
       <c r="BC38" t="n">
         <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
         <v>0</v>
@@ -18859,70 +18843,70 @@
         <v>-1</v>
       </c>
       <c r="BG38" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH38" t="n">
         <v>1</v>
       </c>
       <c r="BI38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BJ38" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BK38" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BL38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BM38" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BN38" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO38" t="n">
         <v>0</v>
       </c>
       <c r="BP38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ38" t="n">
         <v>1</v>
       </c>
       <c r="BR38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU38" t="n">
         <v>1</v>
       </c>
       <c r="BV38" t="n">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="BW38" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="BX38" t="n">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="BY38" t="n">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1.26</v>
+        <v>2.53</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.71</v>
+        <v>1.04</v>
       </c>
       <c r="CB38" t="n">
-        <v>2.97</v>
+        <v>3.57</v>
       </c>
       <c r="CC38" t="n">
         <v>0</v>
@@ -18955,10 +18939,10 @@
         <v>0</v>
       </c>
       <c r="CM38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO38" t="n">
         <v>0</v>
@@ -18970,73 +18954,73 @@
         <v>1</v>
       </c>
       <c r="CR38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CS38" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="CT38" t="n">
         <v>1</v>
       </c>
       <c r="CU38" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CV38" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW38" t="n">
         <v>1</v>
       </c>
       <c r="CX38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="CY38" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CZ38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DA38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DC38" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="DF38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DH38" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="DI38" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="DJ38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DK38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL38" t="n">
-        <v>1.41</v>
+        <v>2.61</v>
       </c>
       <c r="DM38" t="n">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="DN38" t="n">
-        <v>2.39</v>
+        <v>3.77</v>
       </c>
       <c r="DO38" t="n">
         <v>15</v>
@@ -19045,7 +19029,7 @@
         <v>1</v>
       </c>
       <c r="DQ38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR38" t="b">
         <v>0</v>
@@ -19060,86 +19044,102 @@
         <v>0</v>
       </c>
       <c r="DV38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW38" t="n">
-        <v>25.94</v>
+        <v>27.44</v>
       </c>
       <c r="DX38" t="n">
-        <v>8.640000000000001</v>
+        <v>6.53</v>
       </c>
       <c r="DY38" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ38" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="EA38" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="EB38" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="EC38" t="inlineStr">
         <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="ED38" t="inlineStr"/>
-      <c r="EE38" t="inlineStr"/>
-      <c r="EF38" t="inlineStr"/>
-      <c r="EG38" t="inlineStr"/>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="ED38" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EE38" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF38" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG38" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="EH38" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI38" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EJ38" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="EK38" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EL38" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EM38" t="inlineStr">
+        <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="EI38" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EJ38" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="EK38" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EL38" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EM38" t="inlineStr">
+      <c r="EN38" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EO38" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EP38" t="inlineStr">
         <is>
           <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN38" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="EO38" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EP38" t="inlineStr">
-        <is>
-          <t>1.94</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE40" t="n">
         <v>0.14</v>
@@ -20902,7 +20902,7 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE42" t="n">
         <v>2.75</v>
@@ -22955,46 +22955,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>45920.60416666666</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>6</v>
@@ -23003,89 +23003,81 @@
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="X47" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Z47" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD47" t="n">
         <v>4</v>
       </c>
-      <c r="AD47" t="n">
-        <v>2</v>
-      </c>
       <c r="AE47" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="AF47" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.72</v>
+        <v>5.05</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AL47" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AO47" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS47" t="n">
         <v>2.47</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.48</v>
       </c>
       <c r="AT47" t="n">
         <v>1.3</v>
@@ -23094,25 +23086,25 @@
         <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX47" t="n">
         <v>1</v>
       </c>
       <c r="AY47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB47" t="n">
-        <v>167</v>
+        <v>1028</v>
       </c>
       <c r="BC47" t="n">
         <v>0</v>
@@ -23127,70 +23119,70 @@
         <v>-1</v>
       </c>
       <c r="BG47" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH47" t="n">
         <v>1</v>
       </c>
       <c r="BI47" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS47" t="n">
         <v>4</v>
       </c>
-      <c r="BM47" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN47" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS47" t="n">
-        <v>1</v>
-      </c>
       <c r="BT47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU47" t="n">
         <v>1</v>
       </c>
       <c r="BV47" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="BW47" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="BX47" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="BY47" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="CB47" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="CC47" t="n">
         <v>1</v>
@@ -23217,94 +23209,94 @@
         <v>1</v>
       </c>
       <c r="CK47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL47" t="n">
         <v>0</v>
       </c>
       <c r="CM47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ47" t="n">
         <v>1</v>
       </c>
       <c r="CR47" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="CS47" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV47" t="n">
         <v>16</v>
       </c>
-      <c r="CT47" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU47" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV47" t="n">
-        <v>10</v>
-      </c>
       <c r="CW47" t="n">
         <v>1</v>
       </c>
       <c r="CX47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ47" t="n">
         <v>50</v>
       </c>
       <c r="DA47" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB47" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC47" t="n">
         <v>75</v>
       </c>
-      <c r="DC47" t="n">
-        <v>100</v>
-      </c>
       <c r="DD47" t="n">
-        <v>0.86</v>
+        <v>1.38</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="DF47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DG47" t="n">
         <v>0.5</v>
       </c>
       <c r="DH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI47" t="n">
         <v>0.8</v>
-      </c>
-      <c r="DI47" t="n">
-        <v>1</v>
       </c>
       <c r="DJ47" t="n">
         <v>50</v>
       </c>
       <c r="DK47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="DM47" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DN47" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="DO47" t="n">
         <v>15</v>
@@ -23331,99 +23323,83 @@
         <v>1</v>
       </c>
       <c r="DW47" t="n">
-        <v>25.21</v>
+        <v>20.04</v>
       </c>
       <c r="DX47" t="n">
-        <v>6.42</v>
+        <v>5.58</v>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ47" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="EA47" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="EB47" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EC47" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="ED47" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EE47" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG47" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EH47" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI47" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EJ47" t="inlineStr">
         <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="EK47" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="EL47" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EM47" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EN47" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="EK47" t="inlineStr"/>
+      <c r="EL47" t="inlineStr"/>
+      <c r="EM47" t="inlineStr"/>
+      <c r="EN47" t="inlineStr"/>
       <c r="EO47" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
@@ -23443,46 +23419,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>45920.60416666666</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>6</v>
@@ -23491,81 +23467,89 @@
         <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W48" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="X48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Z48" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
       <c r="AC48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="AF48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR48" t="n">
         <v>3.15</v>
       </c>
-      <c r="AG48" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AS48" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AT48" t="n">
         <v>1.3</v>
@@ -23574,25 +23558,25 @@
         <v>3</v>
       </c>
       <c r="AV48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
         <v>1</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1028</v>
+        <v>167</v>
       </c>
       <c r="BC48" t="n">
         <v>0</v>
@@ -23607,184 +23591,184 @@
         <v>-1</v>
       </c>
       <c r="BG48" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH48" t="n">
         <v>1</v>
       </c>
       <c r="BI48" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BJ48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL48" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BM48" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN48" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO48" t="n">
         <v>1</v>
       </c>
       <c r="BP48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>59</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR48" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX48" t="n">
         <v>5</v>
       </c>
-      <c r="BR48" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS48" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT48" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU48" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV48" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW48" t="n">
-        <v>27</v>
-      </c>
-      <c r="BX48" t="n">
-        <v>93</v>
-      </c>
-      <c r="BY48" t="n">
-        <v>70</v>
-      </c>
-      <c r="BZ48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CA48" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="CB48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CC48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS48" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU48" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV48" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX48" t="n">
-        <v>1</v>
-      </c>
       <c r="CY48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ48" t="n">
         <v>50</v>
       </c>
       <c r="DA48" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB48" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DC48" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.38</v>
+        <v>0.86</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="DF48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DG48" t="n">
         <v>0.5</v>
       </c>
       <c r="DH48" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DI48" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DJ48" t="n">
         <v>50</v>
       </c>
       <c r="DK48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL48" t="n">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DM48" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="DN48" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="DO48" t="n">
         <v>15</v>
@@ -23811,83 +23795,99 @@
         <v>1</v>
       </c>
       <c r="DW48" t="n">
-        <v>20.04</v>
+        <v>25.21</v>
       </c>
       <c r="DX48" t="n">
-        <v>5.58</v>
+        <v>6.42</v>
       </c>
       <c r="DY48" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="DZ48" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA48" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="EB48" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EC48" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="ED48" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EE48" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EF48" t="inlineStr">
         <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EG48" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH48" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EI48" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EJ48" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EK48" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EL48" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EM48" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EN48" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EO48" t="inlineStr">
+        <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="EG48" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EH48" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EI48" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EJ48" t="inlineStr">
-        <is>
-          <t>5.09</t>
-        </is>
-      </c>
-      <c r="EK48" t="inlineStr"/>
-      <c r="EL48" t="inlineStr"/>
-      <c r="EM48" t="inlineStr"/>
-      <c r="EN48" t="inlineStr"/>
-      <c r="EO48" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
       <c r="EP48" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25197,7 @@
         <v>0.29</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF51" t="n">
         <v>0.5</v>
@@ -29490,7 +29490,7 @@
         <v>84</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE60" t="n">
         <v>2.75</v>
@@ -30922,7 +30922,7 @@
         <v>50</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE63" t="n">
         <v>1.38</v>
@@ -32015,170 +32015,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="n">
         <v>5</v>
       </c>
-      <c r="J66" t="n">
-        <v>2</v>
-      </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L66" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
         <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>7</v>
       </c>
       <c r="R66" t="n">
+        <v>5</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8</v>
+      </c>
+      <c r="T66" t="n">
+        <v>10</v>
+      </c>
+      <c r="U66" t="n">
+        <v>15</v>
+      </c>
+      <c r="V66" t="n">
+        <v>15</v>
+      </c>
+      <c r="W66" t="n">
+        <v>13</v>
+      </c>
+      <c r="X66" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Estádio Cidade de Barcelos</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>strada Nacional 103, Vila Boa, Barcelos</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
         <v>4</v>
       </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="n">
-        <v>6</v>
-      </c>
-      <c r="U66" t="n">
-        <v>17</v>
-      </c>
-      <c r="V66" t="n">
-        <v>10</v>
-      </c>
-      <c r="W66" t="n">
-        <v>12</v>
-      </c>
-      <c r="X66" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
-      <c r="AC66" t="n">
-        <v>1</v>
-      </c>
       <c r="AD66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="AF66" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AG66" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AI66" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AN66" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AO66" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AR66" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AU66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
         <v>2</v>
       </c>
       <c r="BB66" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32193,73 +32193,73 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM66" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT66" t="n">
         <v>4</v>
       </c>
-      <c r="BN66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT66" t="n">
-        <v>3</v>
-      </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BW66" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="BX66" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="BY66" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BZ66" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="CB66" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="CC66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD66" t="n">
         <v>0</v>
       </c>
       <c r="CE66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF66" t="n">
         <v>0</v>
@@ -32280,10 +32280,10 @@
         <v>0</v>
       </c>
       <c r="CL66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN66" t="n">
         <v>0</v>
@@ -32298,73 +32298,73 @@
         <v>1</v>
       </c>
       <c r="CR66" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS66" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
       </c>
       <c r="CX66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY66" t="n">
         <v>8</v>
       </c>
       <c r="CZ66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA66" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DB66" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="n">
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>0.86</v>
+        <v>1.86</v>
       </c>
       <c r="DE66" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DF66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DG66" t="n">
         <v>1</v>
       </c>
       <c r="DH66" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="DI66" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="DJ66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK66" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="DN66" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="DO66" t="n">
         <v>15</v>
@@ -32376,114 +32376,114 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU66" t="b">
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>24.96</v>
+        <v>25.52</v>
       </c>
       <c r="DX66" t="n">
-        <v>6.88</v>
+        <v>6.19</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EH66" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI66" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ66" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EK66" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EL66" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM66" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN66" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EO66" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP66" t="inlineStr">
+        <is>
           <t>1.72</t>
-        </is>
-      </c>
-      <c r="EH66" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI66" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ66" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="EK66" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="EL66" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EM66" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EN66" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EO66" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EP66" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -32503,170 +32503,170 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>7</v>
       </c>
       <c r="R67" t="n">
+        <v>4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="n">
+        <v>6</v>
+      </c>
+      <c r="U67" t="n">
+        <v>17</v>
+      </c>
+      <c r="V67" t="n">
+        <v>10</v>
+      </c>
+      <c r="W67" t="n">
+        <v>12</v>
+      </c>
+      <c r="X67" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="n">
         <v>5</v>
       </c>
-      <c r="S67" t="n">
-        <v>8</v>
-      </c>
-      <c r="T67" t="n">
-        <v>10</v>
-      </c>
-      <c r="U67" t="n">
-        <v>15</v>
-      </c>
-      <c r="V67" t="n">
-        <v>15</v>
-      </c>
-      <c r="W67" t="n">
-        <v>13</v>
-      </c>
-      <c r="X67" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Estádio Cidade de Barcelos</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>strada Nacional 103, Vila Boa, Barcelos</t>
-        </is>
-      </c>
-      <c r="AC67" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>3</v>
-      </c>
       <c r="AE67" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="AF67" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AG67" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI67" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ67" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AK67" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AL67" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AN67" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AO67" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR67" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AS67" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AU67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
       </c>
       <c r="BB67" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32681,178 +32681,178 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM67" t="n">
         <v>4</v>
       </c>
-      <c r="BJ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL67" t="n">
+      <c r="BN67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC67" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE67" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX67" t="n">
         <v>6</v>
-      </c>
-      <c r="BM67" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN67" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ67" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT67" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV67" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW67" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX67" t="n">
-        <v>83</v>
-      </c>
-      <c r="BY67" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ67" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA67" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CB67" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CC67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR67" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS67" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU67" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV67" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX67" t="n">
-        <v>8</v>
       </c>
       <c r="CY67" t="n">
         <v>8</v>
       </c>
       <c r="CZ67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA67" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DB67" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DC67" t="n">
         <v>50</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.86</v>
+        <v>0.86</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DF67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DG67" t="n">
         <v>1</v>
       </c>
       <c r="DH67" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="DI67" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DJ67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK67" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="DM67" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="DN67" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="DO67" t="n">
         <v>15</v>
@@ -32864,69 +32864,69 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU67" t="b">
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW67" t="n">
-        <v>25.52</v>
+        <v>24.96</v>
       </c>
       <c r="DX67" t="n">
-        <v>6.19</v>
+        <v>6.88</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EA67" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EB67" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EC67" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="ED67" t="inlineStr">
         <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EE67" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF67" t="inlineStr">
+        <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="EE67" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EF67" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
@@ -32936,42 +32936,42 @@
       </c>
       <c r="EI67" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EJ67" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="EK67" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EL67" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM67" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EN67" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EO67" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP67" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -33313,7 +33313,7 @@
         <v>0.38</v>
       </c>
       <c r="DE68" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF68" t="n">
         <v>0</v>
@@ -37763,170 +37763,162 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45956.64583333334</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>2</v>
       </c>
       <c r="J78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L78" t="n">
+        <v>9</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>10</v>
+      </c>
+      <c r="R78" t="n">
+        <v>3</v>
+      </c>
+      <c r="S78" t="n">
         <v>5</v>
       </c>
-      <c r="L78" t="n">
-        <v>11</v>
-      </c>
-      <c r="M78" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" t="n">
-        <v>3</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>4</v>
-      </c>
-      <c r="R78" t="n">
-        <v>4</v>
-      </c>
-      <c r="S78" t="n">
-        <v>9</v>
-      </c>
       <c r="T78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U78" t="n">
+        <v>15</v>
+      </c>
+      <c r="V78" t="n">
         <v>13</v>
       </c>
-      <c r="V78" t="n">
-        <v>9</v>
-      </c>
       <c r="W78" t="n">
+        <v>20</v>
+      </c>
+      <c r="X78" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>1033</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
         <v>13</v>
-      </c>
-      <c r="X78" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Estádio António Coimbra da Mota</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>Rua Dom Bosco, Estoril</t>
-        </is>
-      </c>
-      <c r="AC78" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB78" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>38</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37947,25 +37939,25 @@
         <v>2</v>
       </c>
       <c r="BK78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM78" t="n">
         <v>5</v>
       </c>
       <c r="BN78" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR78" t="n">
         <v>1</v>
@@ -37974,40 +37966,40 @@
         <v>2</v>
       </c>
       <c r="BT78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU78" t="n">
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="BW78" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="BX78" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="BY78" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="CB78" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="CC78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD78" t="n">
         <v>0</v>
       </c>
       <c r="CE78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF78" t="n">
         <v>0</v>
@@ -38031,7 +38023,7 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
@@ -38046,10 +38038,10 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CS78" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="CT78" t="n">
         <v>1</v>
@@ -38058,61 +38050,61 @@
         <v>14</v>
       </c>
       <c r="CV78" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="CW78" t="n">
         <v>1</v>
       </c>
       <c r="CX78" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CY78" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="CZ78" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="DA78" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DB78" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK78" t="n">
         <v>25</v>
       </c>
-      <c r="DC78" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE78" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DF78" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG78" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DH78" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DI78" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DJ78" t="n">
-        <v>88</v>
-      </c>
-      <c r="DK78" t="n">
-        <v>50</v>
-      </c>
       <c r="DL78" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="DM78" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="DN78" t="n">
-        <v>2.38</v>
+        <v>2.87</v>
       </c>
       <c r="DO78" t="n">
         <v>15</v>
@@ -38136,102 +38128,102 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW78" t="n">
-        <v>19.34</v>
+        <v>19.55</v>
       </c>
       <c r="DX78" t="n">
-        <v>4.82</v>
+        <v>3.46</v>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EC78" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="ED78" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EE78" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EF78" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EG78" t="inlineStr">
         <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="EH78" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EI78" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
       <c r="EJ78" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EK78" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EL78" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EM78" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EN78" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EO78" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EP78" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -38251,141 +38243,149 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45956.64583333334</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
         <v>2</v>
       </c>
       <c r="J79" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" t="n">
         <v>5</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
+        <v>11</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
         <v>4</v>
       </c>
-      <c r="L79" t="n">
+      <c r="R79" t="n">
+        <v>4</v>
+      </c>
+      <c r="S79" t="n">
         <v>9</v>
       </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>10</v>
-      </c>
-      <c r="R79" t="n">
-        <v>3</v>
-      </c>
-      <c r="S79" t="n">
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="T79" t="n">
-        <v>10</v>
-      </c>
       <c r="U79" t="n">
+        <v>13</v>
+      </c>
+      <c r="V79" t="n">
+        <v>9</v>
+      </c>
+      <c r="W79" t="n">
+        <v>13</v>
+      </c>
+      <c r="X79" t="n">
         <v>15</v>
       </c>
-      <c r="V79" t="n">
-        <v>13</v>
-      </c>
-      <c r="W79" t="n">
-        <v>20</v>
-      </c>
-      <c r="X79" t="n">
-        <v>14</v>
-      </c>
       <c r="Y79" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Z79" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Estádio António Coimbra da Mota</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Rua Dom Bosco, Estoril</t>
+        </is>
+      </c>
       <c r="AC79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE79" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP79" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF79" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH79" t="n">
+      <c r="AQ79" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI79" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AR79" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
         <v>2</v>
       </c>
       <c r="AV79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX79" t="n">
         <v>1</v>
@@ -38400,13 +38400,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>1033</v>
+        <v>-1</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38427,67 +38427,67 @@
         <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM79" t="n">
         <v>5</v>
       </c>
       <c r="BN79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT79" t="n">
         <v>4</v>
       </c>
-      <c r="BO79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS79" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT79" t="n">
-        <v>1</v>
-      </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="BW79" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="BX79" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="BY79" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="CB79" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="CC79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD79" t="n">
         <v>0</v>
       </c>
       <c r="CE79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF79" t="n">
         <v>0</v>
@@ -38511,7 +38511,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38526,10 +38526,10 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CS79" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
@@ -38538,61 +38538,61 @@
         <v>14</v>
       </c>
       <c r="CV79" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CY79" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CZ79" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="DA79" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB79" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DC79" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI79" t="n">
         <v>1.25</v>
       </c>
-      <c r="DG79" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>1.38</v>
-      </c>
       <c r="DJ79" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DK79" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.87</v>
+        <v>2.38</v>
       </c>
       <c r="DO79" t="n">
         <v>15</v>
@@ -38616,102 +38616,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>19.55</v>
+        <v>19.34</v>
       </c>
       <c r="DX79" t="n">
-        <v>3.46</v>
+        <v>4.82</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EO79" t="inlineStr">
+        <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="ED79" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EE79" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="EK79" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN79" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EO79" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -40501,7 +40501,7 @@
         <v>2.29</v>
       </c>
       <c r="DE83" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF83" t="n">
         <v>1.75</v>
@@ -41441,7 +41441,7 @@
         <v>0.43</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF85" t="n">
         <v>0.5</v>
@@ -44838,7 +44838,7 @@
         <v>78</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE92" t="n">
         <v>0.71</v>
@@ -47634,7 +47634,7 @@
         <v>70</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE98" t="n">
         <v>3</v>
@@ -50013,7 +50013,7 @@
         <v>0.43</v>
       </c>
       <c r="DE103" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF103" t="n">
         <v>0.4</v>
@@ -51941,7 +51941,7 @@
         <v>2.29</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF107" t="n">
         <v>2</v>
@@ -54782,7 +54782,7 @@
         <v>84</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE113" t="n">
         <v>1.5</v>
@@ -55270,7 +55270,7 @@
         <v>75</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE114" t="n">
         <v>1</v>
@@ -55423,146 +55423,138 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L115" t="n">
+        <v>8</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
         <v>4</v>
       </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1</v>
-      </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q115" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T115" t="n">
+        <v>7</v>
+      </c>
+      <c r="U115" t="n">
+        <v>24</v>
+      </c>
+      <c r="V115" t="n">
+        <v>9</v>
+      </c>
+      <c r="W115" t="n">
+        <v>12</v>
+      </c>
+      <c r="X115" t="n">
         <v>14</v>
       </c>
-      <c r="U115" t="n">
-        <v>10</v>
-      </c>
-      <c r="V115" t="n">
-        <v>17</v>
-      </c>
-      <c r="W115" t="n">
-        <v>10</v>
-      </c>
-      <c r="X115" t="n">
-        <v>19</v>
-      </c>
       <c r="Y115" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="Z115" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Complexo Desportivo FC Alverca</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AG115" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AJ115" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL115" t="n">
         <v>1.92</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW115" t="n">
         <v>0</v>
@@ -55571,22 +55563,22 @@
         <v>1</v>
       </c>
       <c r="AY115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB115" t="n">
-        <v>10708</v>
+        <v>15804</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55601,64 +55593,64 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BW115" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="BX115" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="BY115" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="BZ115" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="CA115" t="n">
-        <v>1.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB115" t="n">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
@@ -55691,10 +55683,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55709,70 +55701,70 @@
         <v>21</v>
       </c>
       <c r="CS115" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV115" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
       </c>
       <c r="CX115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY115" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CZ115" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="DA115" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="DB115" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="DC115" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.25</v>
+        <v>0.71</v>
       </c>
       <c r="DF115" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="DG115" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="DH115" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="DI115" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DJ115" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="DK115" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DM115" t="n">
-        <v>1.21</v>
+        <v>0.87</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="DO115" t="n">
         <v>15</v>
@@ -55781,13 +55773,13 @@
         <v>1</v>
       </c>
       <c r="DQ115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT115" t="b">
         <v>0</v>
@@ -55796,17 +55788,17 @@
         <v>0</v>
       </c>
       <c r="DV115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW115" t="n">
-        <v>16.34</v>
+        <v>16.07</v>
       </c>
       <c r="DX115" t="n">
-        <v>5.53</v>
+        <v>5.47</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
@@ -55816,39 +55808,23 @@
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="ED115" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EE115" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EF115" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EG115" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr"/>
+      <c r="EF115" t="inlineStr"/>
+      <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -55856,26 +55832,42 @@
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="EK115" t="inlineStr"/>
-      <c r="EL115" t="inlineStr"/>
-      <c r="EM115" t="inlineStr"/>
-      <c r="EN115" t="inlineStr"/>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EM115" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN115" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
       <c r="EO115" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -55895,138 +55887,146 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" t="n">
         <v>4</v>
       </c>
-      <c r="J116" t="n">
-        <v>5</v>
-      </c>
-      <c r="K116" t="n">
-        <v>3</v>
-      </c>
-      <c r="L116" t="n">
-        <v>8</v>
-      </c>
       <c r="M116" t="n">
         <v>1</v>
       </c>
       <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
         <v>4</v>
       </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>9</v>
-      </c>
       <c r="R116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T116" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U116" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V116" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X116" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y116" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="Z116" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Complexo Desportivo FC Alverca</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
+        </is>
+      </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AG116" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI116" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AJ116" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL116" t="n">
         <v>1.92</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AN116" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AU116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW116" t="n">
         <v>0</v>
@@ -56035,22 +56035,22 @@
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>15804</v>
+        <v>10708</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -56065,64 +56065,64 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR116" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU116" t="n">
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="BW116" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="BX116" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="BY116" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="BZ116" t="n">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="CA116" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="CB116" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
@@ -56155,10 +56155,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -56173,70 +56173,70 @@
         <v>21</v>
       </c>
       <c r="CS116" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CV116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CW116" t="n">
         <v>1</v>
       </c>
       <c r="CX116" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY116" t="n">
         <v>6</v>
       </c>
-      <c r="CY116" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ116" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="DA116" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="DB116" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="DC116" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.71</v>
+        <v>1.25</v>
       </c>
       <c r="DF116" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG116" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="DH116" t="n">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="DI116" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DJ116" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="DK116" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DM116" t="n">
-        <v>0.87</v>
+        <v>1.21</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="DO116" t="n">
         <v>15</v>
@@ -56245,13 +56245,13 @@
         <v>1</v>
       </c>
       <c r="DQ116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT116" t="b">
         <v>0</v>
@@ -56260,17 +56260,17 @@
         <v>0</v>
       </c>
       <c r="DV116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>16.07</v>
+        <v>16.34</v>
       </c>
       <c r="DX116" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
@@ -56280,23 +56280,39 @@
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="ED116" t="inlineStr"/>
-      <c r="EE116" t="inlineStr"/>
-      <c r="EF116" t="inlineStr"/>
-      <c r="EG116" t="inlineStr"/>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
       <c r="EH116" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -56304,42 +56320,26 @@
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="EK116" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="EL116" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EM116" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN116" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr"/>
+      <c r="EL116" t="inlineStr"/>
+      <c r="EM116" t="inlineStr"/>
+      <c r="EN116" t="inlineStr"/>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -59070,7 +59070,7 @@
         <v>86</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE122" t="n">
         <v>0.71</v>
@@ -59103,7 +59103,7 @@
         <v>2.85</v>
       </c>
       <c r="DO122" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -60049,7 +60049,7 @@
         <v>1</v>
       </c>
       <c r="DE124" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF124" t="n">
         <v>0.71</v>
@@ -61473,7 +61473,7 @@
         <v>2.71</v>
       </c>
       <c r="DE127" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DF127" t="n">
         <v>2.67</v>
@@ -61942,7 +61942,7 @@
         <v>93</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE128" t="n">
         <v>1.5</v>
@@ -65948,6 +65948,974 @@
       <c r="EP136" t="inlineStr">
         <is>
           <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>16</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Famalicão</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>46018.75</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+      <c r="I137" t="n">
+        <v>5</v>
+      </c>
+      <c r="J137" t="n">
+        <v>9</v>
+      </c>
+      <c r="K137" t="n">
+        <v>4</v>
+      </c>
+      <c r="L137" t="n">
+        <v>13</v>
+      </c>
+      <c r="M137" t="n">
+        <v>3</v>
+      </c>
+      <c r="N137" t="n">
+        <v>5</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>5</v>
+      </c>
+      <c r="R137" t="n">
+        <v>4</v>
+      </c>
+      <c r="S137" t="n">
+        <v>17</v>
+      </c>
+      <c r="T137" t="n">
+        <v>2</v>
+      </c>
+      <c r="U137" t="n">
+        <v>22</v>
+      </c>
+      <c r="V137" t="n">
+        <v>6</v>
+      </c>
+      <c r="W137" t="n">
+        <v>18</v>
+      </c>
+      <c r="X137" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>15804</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>127</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>61</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU137" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV137" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX137" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY137" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ137" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA137" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB137" t="n">
+        <v>47</v>
+      </c>
+      <c r="DC137" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD137" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE137" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF137" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG137" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH137" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ137" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK137" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL137" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM137" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DN137" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DO137" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW137" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="DX137" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="DY137" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ137" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="EA137" t="inlineStr">
+        <is>
+          <t>7.63</t>
+        </is>
+      </c>
+      <c r="EB137" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="EC137" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="ED137" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EE137" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EF137" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EG137" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH137" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI137" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EJ137" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EK137" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EL137" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EM137" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EN137" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EO137" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EP137" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>16</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>GD Estoril Praia</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>46018.85416666666</v>
+      </c>
+      <c r="G138" t="n">
+        <v>4</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>5</v>
+      </c>
+      <c r="J138" t="n">
+        <v>3</v>
+      </c>
+      <c r="K138" t="n">
+        <v>7</v>
+      </c>
+      <c r="L138" t="n">
+        <v>10</v>
+      </c>
+      <c r="M138" t="n">
+        <v>2</v>
+      </c>
+      <c r="N138" t="n">
+        <v>3</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>4</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="n">
+        <v>4</v>
+      </c>
+      <c r="U138" t="n">
+        <v>9</v>
+      </c>
+      <c r="V138" t="n">
+        <v>11</v>
+      </c>
+      <c r="W138" t="n">
+        <v>12</v>
+      </c>
+      <c r="X138" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Estádio António Coimbra da Mota</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>Rua Dom Bosco, Estoril</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>164</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU138" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV138" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX138" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY138" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ138" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA138" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB138" t="n">
+        <v>48</v>
+      </c>
+      <c r="DC138" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD138" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE138" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF138" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG138" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH138" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI138" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ138" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK138" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL138" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM138" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DN138" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DO138" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW138" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="DX138" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="DY138" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DZ138" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="EA138" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EB138" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="EC138" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="ED138" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EE138" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF138" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EG138" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EH138" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EI138" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EJ138" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EK138" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EL138" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EM138" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EN138" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EO138" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EP138" t="inlineStr">
+        <is>
+          <t>2.21</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP138" headerRowCount="1">
-  <autoFilter ref="A1:EP138"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP143" headerRowCount="1">
+  <autoFilter ref="A1:EP143"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP138"/>
+  <dimension ref="A1:EP143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE2" t="n">
         <v>2.75</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2293,7 +2293,7 @@
         <v>0.86</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2781,7 +2781,7 @@
         <v>1</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DE6" t="n">
         <v>0.88</v>
@@ -5170,10 +5170,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6651,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7101,7 +7101,7 @@
         <v>1.13</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE17" t="n">
         <v>0.71</v>
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9475,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9933,7 +9933,7 @@
         <v>1.86</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -11341,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF22" t="n">
         <v>3</v>
@@ -11371,7 +11371,7 @@
         <v>1.05</v>
       </c>
       <c r="DO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11821,7 +11821,7 @@
         <v>1.22</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11851,7 +11851,7 @@
         <v>1.87</v>
       </c>
       <c r="DO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP23" t="b">
         <v>0</v>
@@ -12298,7 +12298,7 @@
         <v>100</v>
       </c>
       <c r="DD24" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE24" t="n">
         <v>1.25</v>
@@ -12331,7 +12331,7 @@
         <v>3.21</v>
       </c>
       <c r="DO24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12770,10 +12770,10 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12803,7 +12803,7 @@
         <v>2.56</v>
       </c>
       <c r="DO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -14206,7 +14206,7 @@
         <v>100</v>
       </c>
       <c r="DD28" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE28" t="n">
         <v>1.25</v>
@@ -14375,37 +14375,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
         <v>45899.70833333334</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>4</v>
@@ -14414,7 +14414,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
@@ -14423,122 +14423,122 @@
         <v>3</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y29" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="Z29" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Estádio Dom Afonso Henriques</t>
+          <t>Estádio Clube Desportivo das Aves</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Rua de São Gonçalo 505, Guimarães</t>
+          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.78</v>
+        <v>4.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.15</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AO29" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>-1</v>
+        <v>1033</v>
       </c>
       <c r="BC29" t="n">
         <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
         <v>0</v>
@@ -14547,193 +14547,193 @@
         <v>-1</v>
       </c>
       <c r="BG29" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH29" t="n">
         <v>1</v>
       </c>
       <c r="BI29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BK29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL29" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BN29" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO29" t="n">
         <v>0</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR29" t="n">
         <v>4</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX29" t="n">
         <v>8</v>
       </c>
-      <c r="BU29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>20</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>105</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>61</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="CB29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS29" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU29" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV29" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX29" t="n">
-        <v>9</v>
-      </c>
       <c r="CY29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ29" t="n">
         <v>100</v>
       </c>
-      <c r="DA29" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB29" t="n">
-        <v>100</v>
-      </c>
-      <c r="DC29" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE29" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DF29" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH29" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DJ29" t="n">
-        <v>0</v>
-      </c>
       <c r="DK29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL29" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="DM29" t="n">
-        <v>0.64</v>
+        <v>1.71</v>
       </c>
       <c r="DN29" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="DO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
       </c>
       <c r="DQ29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR29" t="b">
         <v>0</v>
@@ -14748,13 +14748,13 @@
         <v>0</v>
       </c>
       <c r="DV29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW29" t="n">
-        <v>25.71</v>
+        <v>26.39</v>
       </c>
       <c r="DX29" t="n">
-        <v>5.57</v>
+        <v>5.3</v>
       </c>
       <c r="DY29" t="inlineStr">
         <is>
@@ -14763,32 +14763,32 @@
       </c>
       <c r="DZ29" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="EA29" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EB29" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC29" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="ED29" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EE29" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EF29" t="inlineStr">
@@ -14798,52 +14798,52 @@
       </c>
       <c r="EG29" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EH29" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI29" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ29" t="inlineStr">
+        <is>
+          <t>4.56</t>
+        </is>
+      </c>
+      <c r="EK29" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EL29" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="EI29" t="inlineStr">
+      <c r="EM29" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EN29" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EO29" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="EJ29" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
-      </c>
-      <c r="EK29" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EL29" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EM29" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN29" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="EO29" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
       <c r="EP29" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -14863,37 +14863,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>45899.70833333334</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -14902,7 +14902,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>3</v>
@@ -14911,122 +14911,122 @@
         <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y30" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Z30" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Estádio Clube Desportivo das Aves</t>
+          <t>Estádio Dom Afonso Henriques</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
+          <t>Rua de São Gonçalo 505, Guimarães</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>4.05</v>
+        <v>1.78</v>
       </c>
       <c r="AF30" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.79</v>
+        <v>4.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AO30" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
-        <v>1033</v>
+        <v>-1</v>
       </c>
       <c r="BC30" t="n">
         <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE30" t="n">
         <v>0</v>
@@ -15035,70 +15035,70 @@
         <v>-1</v>
       </c>
       <c r="BG30" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH30" t="n">
         <v>1</v>
       </c>
       <c r="BI30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BK30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL30" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BN30" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO30" t="n">
         <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR30" t="n">
         <v>4</v>
       </c>
       <c r="BS30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BU30" t="n">
         <v>1</v>
       </c>
       <c r="BV30" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="BW30" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="BX30" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="BY30" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="BZ30" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.35</v>
+        <v>0.93</v>
       </c>
       <c r="CB30" t="n">
-        <v>2.69</v>
+        <v>2.12</v>
       </c>
       <c r="CC30" t="n">
         <v>0</v>
@@ -15131,10 +15131,10 @@
         <v>0</v>
       </c>
       <c r="CM30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO30" t="n">
         <v>0</v>
@@ -15146,82 +15146,82 @@
         <v>1</v>
       </c>
       <c r="CR30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CS30" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="CT30" t="n">
         <v>1</v>
       </c>
       <c r="CU30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV30" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY30" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DM30" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DN30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DO30" t="n">
         <v>16</v>
       </c>
-      <c r="CW30" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX30" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY30" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA30" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC30" t="n">
-        <v>50</v>
-      </c>
-      <c r="DD30" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DE30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG30" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH30" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DI30" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DJ30" t="n">
-        <v>100</v>
-      </c>
-      <c r="DK30" t="n">
-        <v>50</v>
-      </c>
-      <c r="DL30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="DM30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DN30" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="DO30" t="n">
-        <v>15</v>
-      </c>
       <c r="DP30" t="b">
         <v>1</v>
       </c>
       <c r="DQ30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR30" t="b">
         <v>0</v>
@@ -15236,13 +15236,13 @@
         <v>0</v>
       </c>
       <c r="DV30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW30" t="n">
-        <v>26.39</v>
+        <v>25.71</v>
       </c>
       <c r="DX30" t="n">
-        <v>5.3</v>
+        <v>5.57</v>
       </c>
       <c r="DY30" t="inlineStr">
         <is>
@@ -15251,32 +15251,32 @@
       </c>
       <c r="DZ30" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="EA30" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EB30" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EC30" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="ED30" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EE30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EF30" t="inlineStr">
@@ -15286,52 +15286,52 @@
       </c>
       <c r="EG30" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EH30" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EI30" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ30" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK30" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EL30" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EM30" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EN30" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EO30" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EP30" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -15670,7 +15670,7 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE31" t="n">
         <v>3</v>
@@ -15703,7 +15703,7 @@
         <v>3.82</v>
       </c>
       <c r="DO31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16649,7 +16649,7 @@
         <v>1.25</v>
       </c>
       <c r="DE33" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16679,7 +16679,7 @@
         <v>2.74</v>
       </c>
       <c r="DO33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17615,7 +17615,7 @@
         <v>3.64</v>
       </c>
       <c r="DO35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -19481,7 +19481,7 @@
         <v>1.86</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -19969,7 +19969,7 @@
         <v>1.67</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF40" t="n">
         <v>0.5</v>
@@ -19999,7 +19999,7 @@
         <v>2.26</v>
       </c>
       <c r="DO40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20438,7 +20438,7 @@
         <v>100</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE41" t="n">
         <v>1.25</v>
@@ -20935,7 +20935,7 @@
         <v>3.84</v>
       </c>
       <c r="DO42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21333,7 +21333,7 @@
         <v>1.13</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF43" t="n">
         <v>0.5</v>
@@ -21363,7 +21363,7 @@
         <v>2.74</v>
       </c>
       <c r="DO43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21851,7 +21851,7 @@
         <v>2.16</v>
       </c>
       <c r="DO44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22298,10 +22298,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -22331,7 +22331,7 @@
         <v>3.35</v>
       </c>
       <c r="DO45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22819,7 +22819,7 @@
         <v>2.94</v>
       </c>
       <c r="DO46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -24229,7 +24229,7 @@
         <v>0.38</v>
       </c>
       <c r="DE49" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DF49" t="n">
         <v>0</v>
@@ -24259,7 +24259,7 @@
         <v>2.33</v>
       </c>
       <c r="DO49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24739,7 +24739,7 @@
         <v>3.53</v>
       </c>
       <c r="DO50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25715,7 +25715,7 @@
         <v>3.03</v>
       </c>
       <c r="DO52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26170,7 +26170,7 @@
         <v>50</v>
       </c>
       <c r="DD53" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE53" t="n">
         <v>1.71</v>
@@ -26203,7 +26203,7 @@
         <v>2.5</v>
       </c>
       <c r="DO53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26642,7 +26642,7 @@
         <v>50</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE54" t="n">
         <v>1</v>
@@ -27109,7 +27109,7 @@
         <v>2</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF55" t="n">
         <v>2</v>
@@ -27139,7 +27139,7 @@
         <v>4.14</v>
       </c>
       <c r="DO55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27581,7 +27581,7 @@
         <v>2</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DF56" t="n">
         <v>1.67</v>
@@ -27611,7 +27611,7 @@
         <v>3.98</v>
       </c>
       <c r="DO56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -29021,7 +29021,7 @@
         <v>1.13</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF59" t="n">
         <v>0.33</v>
@@ -29051,7 +29051,7 @@
         <v>2.43</v>
       </c>
       <c r="DO59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29523,7 +29523,7 @@
         <v>3.63</v>
       </c>
       <c r="DO60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29973,7 +29973,7 @@
         <v>1.25</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF61" t="n">
         <v>1</v>
@@ -30003,7 +30003,7 @@
         <v>2.65</v>
       </c>
       <c r="DO61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30450,7 +30450,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DE62" t="n">
         <v>1.25</v>
@@ -30925,7 +30925,7 @@
         <v>1.22</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF63" t="n">
         <v>1.33</v>
@@ -30955,7 +30955,7 @@
         <v>2.25</v>
       </c>
       <c r="DO63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -31435,7 +31435,7 @@
         <v>2.94</v>
       </c>
       <c r="DO64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31862,7 +31862,7 @@
         <v>84</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE65" t="n">
         <v>0.71</v>
@@ -31895,7 +31895,7 @@
         <v>2.49</v>
       </c>
       <c r="DO65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32367,7 +32367,7 @@
         <v>2.29</v>
       </c>
       <c r="DO66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33343,7 +33343,7 @@
         <v>1.8</v>
       </c>
       <c r="DO68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34283,7 +34283,7 @@
         <v>2.63</v>
       </c>
       <c r="DO70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35194,7 +35194,7 @@
         <v>67</v>
       </c>
       <c r="DD72" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE72" t="n">
         <v>1.5</v>
@@ -35227,7 +35227,7 @@
         <v>4.42</v>
       </c>
       <c r="DO72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35682,10 +35682,10 @@
         <v>84</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE73" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DF73" t="n">
         <v>3</v>
@@ -35715,7 +35715,7 @@
         <v>3.37</v>
       </c>
       <c r="DO73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36173,7 +36173,7 @@
         <v>1.25</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DF74" t="n">
         <v>1.5</v>
@@ -36203,7 +36203,7 @@
         <v>2.87</v>
       </c>
       <c r="DO74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36645,7 +36645,7 @@
         <v>1.38</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF75" t="n">
         <v>1</v>
@@ -37155,7 +37155,7 @@
         <v>3.06</v>
       </c>
       <c r="DO76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37597,7 +37597,7 @@
         <v>1.13</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF77" t="n">
         <v>1</v>
@@ -37627,7 +37627,7 @@
         <v>2.46</v>
       </c>
       <c r="DO77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37763,141 +37763,149 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45956.64583333334</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
         <v>2</v>
       </c>
       <c r="J78" t="n">
+        <v>6</v>
+      </c>
+      <c r="K78" t="n">
         <v>5</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
+        <v>11</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
         <v>4</v>
       </c>
-      <c r="L78" t="n">
+      <c r="R78" t="n">
+        <v>4</v>
+      </c>
+      <c r="S78" t="n">
         <v>9</v>
       </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" t="n">
-        <v>2</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>10</v>
-      </c>
-      <c r="R78" t="n">
-        <v>3</v>
-      </c>
-      <c r="S78" t="n">
+      <c r="T78" t="n">
         <v>5</v>
       </c>
-      <c r="T78" t="n">
-        <v>10</v>
-      </c>
       <c r="U78" t="n">
+        <v>13</v>
+      </c>
+      <c r="V78" t="n">
+        <v>9</v>
+      </c>
+      <c r="W78" t="n">
+        <v>13</v>
+      </c>
+      <c r="X78" t="n">
         <v>15</v>
       </c>
-      <c r="V78" t="n">
-        <v>13</v>
-      </c>
-      <c r="W78" t="n">
-        <v>20</v>
-      </c>
-      <c r="X78" t="n">
-        <v>14</v>
-      </c>
       <c r="Y78" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Z78" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Estádio António Coimbra da Mota</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Rua Dom Bosco, Estoril</t>
+        </is>
+      </c>
       <c r="AC78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE78" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP78" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF78" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH78" t="n">
+      <c r="AQ78" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI78" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AR78" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AS78" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AU78" t="n">
         <v>2</v>
       </c>
       <c r="AV78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX78" t="n">
         <v>1</v>
@@ -37912,13 +37920,13 @@
         <v>1</v>
       </c>
       <c r="BB78" t="n">
-        <v>1033</v>
+        <v>-1</v>
       </c>
       <c r="BC78" t="n">
         <v>0</v>
       </c>
       <c r="BD78" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37939,67 +37947,67 @@
         <v>2</v>
       </c>
       <c r="BK78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM78" t="n">
         <v>5</v>
       </c>
       <c r="BN78" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT78" t="n">
         <v>4</v>
       </c>
-      <c r="BO78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS78" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT78" t="n">
-        <v>1</v>
-      </c>
       <c r="BU78" t="n">
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="BW78" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="BX78" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="BY78" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="CB78" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="CC78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD78" t="n">
         <v>0</v>
       </c>
       <c r="CE78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF78" t="n">
         <v>0</v>
@@ -38023,7 +38031,7 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
@@ -38038,10 +38046,10 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CS78" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="CT78" t="n">
         <v>1</v>
@@ -38050,61 +38058,61 @@
         <v>14</v>
       </c>
       <c r="CV78" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CW78" t="n">
         <v>1</v>
       </c>
       <c r="CX78" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CY78" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CZ78" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="DA78" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB78" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DC78" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF78" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI78" t="n">
         <v>1.25</v>
       </c>
-      <c r="DG78" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DH78" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DI78" t="n">
-        <v>1.38</v>
-      </c>
       <c r="DJ78" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DK78" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL78" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="DM78" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="DN78" t="n">
-        <v>2.87</v>
+        <v>2.38</v>
       </c>
       <c r="DO78" t="n">
         <v>15</v>
@@ -38128,102 +38136,102 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW78" t="n">
-        <v>19.55</v>
+        <v>19.34</v>
       </c>
       <c r="DX78" t="n">
-        <v>3.46</v>
+        <v>4.82</v>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EC78" t="inlineStr">
         <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="ED78" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EE78" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EG78" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EJ78" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EK78" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EL78" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EM78" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EN78" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EO78" t="inlineStr">
+        <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="ED78" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EE78" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EF78" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EG78" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EH78" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EI78" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EJ78" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="EK78" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="EL78" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EM78" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN78" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="EO78" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
       <c r="EP78" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -38243,170 +38251,162 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45956.64583333334</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K79" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" t="n">
+        <v>9</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>10</v>
+      </c>
+      <c r="R79" t="n">
+        <v>3</v>
+      </c>
+      <c r="S79" t="n">
         <v>5</v>
       </c>
-      <c r="L79" t="n">
-        <v>11</v>
-      </c>
-      <c r="M79" t="n">
-        <v>3</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>4</v>
-      </c>
-      <c r="R79" t="n">
-        <v>4</v>
-      </c>
-      <c r="S79" t="n">
-        <v>9</v>
-      </c>
       <c r="T79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U79" t="n">
+        <v>15</v>
+      </c>
+      <c r="V79" t="n">
         <v>13</v>
       </c>
-      <c r="V79" t="n">
-        <v>9</v>
-      </c>
       <c r="W79" t="n">
+        <v>20</v>
+      </c>
+      <c r="X79" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1033</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
         <v>13</v>
-      </c>
-      <c r="X79" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Estádio António Coimbra da Mota</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Rua Dom Bosco, Estoril</t>
-        </is>
-      </c>
-      <c r="AC79" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB79" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD79" t="n">
-        <v>38</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38427,25 +38427,25 @@
         <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
         <v>5</v>
       </c>
       <c r="BN79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR79" t="n">
         <v>1</v>
@@ -38454,40 +38454,40 @@
         <v>2</v>
       </c>
       <c r="BT79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="BW79" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="BX79" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="BY79" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="CC79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD79" t="n">
         <v>0</v>
       </c>
       <c r="CE79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF79" t="n">
         <v>0</v>
@@ -38511,7 +38511,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38526,10 +38526,10 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CS79" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
@@ -38538,64 +38538,64 @@
         <v>14</v>
       </c>
       <c r="CV79" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CY79" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="CZ79" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="DA79" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DB79" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DC79" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="DE79" t="n">
         <v>1.25</v>
       </c>
       <c r="DF79" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG79" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.75</v>
+        <v>1.63</v>
       </c>
       <c r="DI79" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DJ79" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DK79" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.38</v>
+        <v>2.87</v>
       </c>
       <c r="DO79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38616,102 +38616,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>19.34</v>
+        <v>19.55</v>
       </c>
       <c r="DX79" t="n">
-        <v>4.82</v>
+        <v>3.46</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -39522,7 +39522,7 @@
         <v>100</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DE81" t="n">
         <v>1.25</v>
@@ -39555,7 +39555,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40498,7 +40498,7 @@
         <v>75</v>
       </c>
       <c r="DD83" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE83" t="n">
         <v>0.88</v>
@@ -40531,7 +40531,7 @@
         <v>3.03</v>
       </c>
       <c r="DO83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41438,7 +41438,7 @@
         <v>63</v>
       </c>
       <c r="DD85" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE85" t="n">
         <v>1.13</v>
@@ -41471,7 +41471,7 @@
         <v>2.12</v>
       </c>
       <c r="DO85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41951,7 +41951,7 @@
         <v>2.63</v>
       </c>
       <c r="DO86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42409,7 +42409,7 @@
         <v>1.5</v>
       </c>
       <c r="DE87" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DF87" t="n">
         <v>2</v>
@@ -42439,7 +42439,7 @@
         <v>2.67</v>
       </c>
       <c r="DO87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -43870,7 +43870,7 @@
         <v>88</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE90" t="n">
         <v>1.5</v>
@@ -43903,7 +43903,7 @@
         <v>3.54</v>
       </c>
       <c r="DO90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44871,7 +44871,7 @@
         <v>2.11</v>
       </c>
       <c r="DO92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45329,7 +45329,7 @@
         <v>1.25</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF93" t="n">
         <v>1.2</v>
@@ -45359,7 +45359,7 @@
         <v>2.27</v>
       </c>
       <c r="DO93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45801,7 +45801,7 @@
         <v>0.29</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF94" t="n">
         <v>0.5</v>
@@ -46399,12 +46399,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
@@ -46420,20 +46420,20 @@
         <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
+        <v>6</v>
+      </c>
+      <c r="L96" t="n">
+        <v>8</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3</v>
+      </c>
+      <c r="N96" t="n">
         <v>4</v>
       </c>
-      <c r="L96" t="n">
-        <v>5</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" t="n">
-        <v>5</v>
-      </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
@@ -46441,98 +46441,90 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T96" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U96" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V96" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W96" t="n">
         <v>12</v>
       </c>
       <c r="X96" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y96" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="Z96" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>Estádio Clube Desportivo das Aves</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE96" t="n">
-        <v>5.75</v>
+        <v>2.42</v>
       </c>
       <c r="AF96" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AG96" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI96" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AJ96" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AK96" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AL96" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AM96" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AN96" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AO96" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AR96" t="n">
         <v>3.22</v>
       </c>
       <c r="AS96" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AT96" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU96" t="n">
         <v>2</v>
@@ -46562,7 +46554,7 @@
         <v>0</v>
       </c>
       <c r="BD96" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE96" t="n">
         <v>0</v>
@@ -46580,70 +46572,70 @@
         <v>1</v>
       </c>
       <c r="BJ96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT96" t="n">
         <v>4</v>
       </c>
-      <c r="BK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM96" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR96" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT96" t="n">
-        <v>5</v>
-      </c>
       <c r="BU96" t="n">
         <v>1</v>
       </c>
       <c r="BV96" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW96" t="n">
         <v>44</v>
       </c>
-      <c r="BW96" t="n">
-        <v>47</v>
-      </c>
       <c r="BX96" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BY96" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="BZ96" t="n">
-        <v>1.88</v>
+        <v>1.37</v>
       </c>
       <c r="CA96" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="CB96" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="CC96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD96" t="n">
         <v>0</v>
       </c>
       <c r="CE96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF96" t="n">
         <v>0</v>
@@ -46664,13 +46656,13 @@
         <v>0</v>
       </c>
       <c r="CL96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM96" t="n">
         <v>0</v>
       </c>
       <c r="CN96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CO96" t="n">
         <v>0</v>
@@ -46682,73 +46674,73 @@
         <v>1</v>
       </c>
       <c r="CR96" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CS96" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CT96" t="n">
         <v>1</v>
       </c>
       <c r="CU96" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV96" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY96" t="n">
         <v>11</v>
       </c>
-      <c r="CW96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX96" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY96" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ96" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DA96" t="n">
         <v>70</v>
       </c>
       <c r="DB96" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DC96" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD96" t="n">
-        <v>0.38</v>
+        <v>1.13</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="DF96" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG96" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="DH96" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="DI96" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="DJ96" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="DK96" t="n">
         <v>30</v>
       </c>
       <c r="DL96" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="DM96" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="DN96" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="DO96" t="n">
         <v>15</v>
@@ -46775,87 +46767,67 @@
         <v>1</v>
       </c>
       <c r="DW96" t="n">
-        <v>16.28</v>
+        <v>16.49</v>
       </c>
       <c r="DX96" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="DY96" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="DZ96" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA96" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EB96" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EC96" t="inlineStr">
         <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="ED96" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EE96" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EF96" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG96" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EH96" t="inlineStr"/>
-      <c r="EI96" t="inlineStr"/>
-      <c r="EJ96" t="inlineStr"/>
-      <c r="EK96" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EL96" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EM96" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EN96" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr"/>
+      <c r="EE96" t="inlineStr"/>
+      <c r="EF96" t="inlineStr"/>
+      <c r="EG96" t="inlineStr"/>
+      <c r="EH96" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI96" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ96" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EK96" t="inlineStr"/>
+      <c r="EL96" t="inlineStr"/>
+      <c r="EM96" t="inlineStr"/>
+      <c r="EN96" t="inlineStr"/>
       <c r="EO96" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EP96" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -46875,12 +46847,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
@@ -46896,111 +46868,119 @@
         <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L97" t="n">
+        <v>5</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
         <v>8</v>
       </c>
-      <c r="M97" t="n">
-        <v>3</v>
-      </c>
-      <c r="N97" t="n">
-        <v>4</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>4</v>
-      </c>
       <c r="R97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U97" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V97" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="W97" t="n">
         <v>12</v>
       </c>
       <c r="X97" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y97" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="Z97" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA97" t="inlineStr"/>
-      <c r="AB97" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Estádio Clube Desportivo das Aves</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
+        </is>
+      </c>
       <c r="AC97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE97" t="n">
-        <v>2.42</v>
+        <v>5.75</v>
       </c>
       <c r="AF97" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AG97" t="n">
-        <v>2.96</v>
+        <v>1.63</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI97" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AJ97" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AK97" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AL97" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AN97" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AO97" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR97" t="n">
         <v>3.22</v>
       </c>
       <c r="AS97" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AT97" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU97" t="n">
         <v>2</v>
@@ -47030,7 +47010,7 @@
         <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE97" t="n">
         <v>0</v>
@@ -47048,178 +47028,178 @@
         <v>1</v>
       </c>
       <c r="BJ97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM97" t="n">
         <v>5</v>
       </c>
-      <c r="BK97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM97" t="n">
+      <c r="BN97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX97" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY97" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ97" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CB97" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN97" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR97" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS97" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU97" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV97" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX97" t="n">
         <v>6</v>
       </c>
-      <c r="BN97" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO97" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR97" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS97" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT97" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV97" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW97" t="n">
-        <v>44</v>
-      </c>
-      <c r="BX97" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY97" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ97" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CA97" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB97" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="CC97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR97" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS97" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU97" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV97" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX97" t="n">
-        <v>7</v>
-      </c>
       <c r="CY97" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CZ97" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DA97" t="n">
         <v>70</v>
       </c>
       <c r="DB97" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DC97" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.13</v>
+        <v>0.38</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="DF97" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="DG97" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DH97" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DI97" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="DJ97" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="DK97" t="n">
         <v>30</v>
       </c>
       <c r="DL97" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="DM97" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="DN97" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="DO97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -47243,67 +47223,87 @@
         <v>1</v>
       </c>
       <c r="DW97" t="n">
-        <v>16.49</v>
+        <v>16.28</v>
       </c>
       <c r="DX97" t="n">
-        <v>2.95</v>
+        <v>1.64</v>
       </c>
       <c r="DY97" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ97" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA97" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EB97" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="EC97" t="inlineStr">
         <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EE97" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF97" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG97" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH97" t="inlineStr"/>
+      <c r="EI97" t="inlineStr"/>
+      <c r="EJ97" t="inlineStr"/>
+      <c r="EK97" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EL97" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM97" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EN97" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EO97" t="inlineStr">
+        <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="ED97" t="inlineStr"/>
-      <c r="EE97" t="inlineStr"/>
-      <c r="EF97" t="inlineStr"/>
-      <c r="EG97" t="inlineStr"/>
-      <c r="EH97" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EI97" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EJ97" t="inlineStr">
-        <is>
-          <t>4.24</t>
-        </is>
-      </c>
-      <c r="EK97" t="inlineStr"/>
-      <c r="EL97" t="inlineStr"/>
-      <c r="EM97" t="inlineStr"/>
-      <c r="EN97" t="inlineStr"/>
-      <c r="EO97" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
       <c r="EP97" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
@@ -47667,7 +47667,7 @@
         <v>3.3</v>
       </c>
       <c r="DO98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48114,7 +48114,7 @@
         <v>80</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DE99" t="n">
         <v>1</v>
@@ -48627,7 +48627,7 @@
         <v>3.17</v>
       </c>
       <c r="DO100" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49069,7 +49069,7 @@
         <v>1.5</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF101" t="n">
         <v>1.6</v>
@@ -49099,7 +49099,7 @@
         <v>2.41</v>
       </c>
       <c r="DO101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -50010,7 +50010,7 @@
         <v>80</v>
       </c>
       <c r="DD103" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE103" t="n">
         <v>0.88</v>
@@ -50043,7 +50043,7 @@
         <v>1.98</v>
       </c>
       <c r="DO103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50501,7 +50501,7 @@
         <v>0.86</v>
       </c>
       <c r="DE104" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DF104" t="n">
         <v>0.6</v>
@@ -51938,7 +51938,7 @@
         <v>50</v>
       </c>
       <c r="DD107" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE107" t="n">
         <v>1.13</v>
@@ -51971,7 +51971,7 @@
         <v>3.36</v>
       </c>
       <c r="DO107" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52410,7 +52410,7 @@
         <v>90</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE108" t="n">
         <v>0.71</v>
@@ -52443,7 +52443,7 @@
         <v>3.13</v>
       </c>
       <c r="DO108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -52923,7 +52923,7 @@
         <v>2.9</v>
       </c>
       <c r="DO109" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53375,7 +53375,7 @@
         <v>4.44</v>
       </c>
       <c r="DO110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -54305,7 +54305,7 @@
         <v>0.38</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF112" t="n">
         <v>0.33</v>
@@ -54335,7 +54335,7 @@
         <v>2.3</v>
       </c>
       <c r="DO112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54815,7 +54815,7 @@
         <v>3.14</v>
       </c>
       <c r="DO113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -55423,138 +55423,146 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K115" t="n">
+        <v>2</v>
+      </c>
+      <c r="L115" t="n">
         <v>4</v>
       </c>
-      <c r="J115" t="n">
-        <v>5</v>
-      </c>
-      <c r="K115" t="n">
-        <v>3</v>
-      </c>
-      <c r="L115" t="n">
-        <v>8</v>
-      </c>
       <c r="M115" t="n">
         <v>1</v>
       </c>
       <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
         <v>4</v>
       </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>9</v>
-      </c>
       <c r="R115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T115" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U115" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V115" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W115" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X115" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y115" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="Z115" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA115" t="inlineStr"/>
-      <c r="AB115" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Complexo Desportivo FC Alverca</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
+        </is>
+      </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE115" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AG115" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AJ115" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL115" t="n">
         <v>1.92</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AU115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW115" t="n">
         <v>0</v>
@@ -55563,22 +55571,22 @@
         <v>1</v>
       </c>
       <c r="AY115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>15804</v>
+        <v>10708</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55593,64 +55601,64 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR115" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT115" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="BW115" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="BX115" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="BY115" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="BZ115" t="n">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="CA115" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="CB115" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
@@ -55683,10 +55691,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55701,70 +55709,70 @@
         <v>21</v>
       </c>
       <c r="CS115" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CV115" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
       </c>
       <c r="CX115" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY115" t="n">
         <v>6</v>
       </c>
-      <c r="CY115" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ115" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="DA115" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="DB115" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="DC115" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="DE115" t="n">
-        <v>0.71</v>
+        <v>1.25</v>
       </c>
       <c r="DF115" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG115" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="DH115" t="n">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="DI115" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DJ115" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="DK115" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DM115" t="n">
-        <v>0.87</v>
+        <v>1.21</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="DO115" t="n">
         <v>15</v>
@@ -55773,13 +55781,13 @@
         <v>1</v>
       </c>
       <c r="DQ115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT115" t="b">
         <v>0</v>
@@ -55788,17 +55796,17 @@
         <v>0</v>
       </c>
       <c r="DV115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW115" t="n">
-        <v>16.07</v>
+        <v>16.34</v>
       </c>
       <c r="DX115" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
@@ -55808,23 +55816,39 @@
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="ED115" t="inlineStr"/>
-      <c r="EE115" t="inlineStr"/>
-      <c r="EF115" t="inlineStr"/>
-      <c r="EG115" t="inlineStr"/>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="ED115" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE115" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF115" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EG115" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
       <c r="EH115" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -55832,42 +55856,26 @@
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="EK115" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="EL115" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EM115" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN115" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr"/>
+      <c r="EL115" t="inlineStr"/>
+      <c r="EM115" t="inlineStr"/>
+      <c r="EN115" t="inlineStr"/>
       <c r="EO115" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -55887,146 +55895,138 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L116" t="n">
+        <v>8</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
         <v>4</v>
       </c>
-      <c r="M116" t="n">
-        <v>1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>1</v>
-      </c>
       <c r="O116" t="n">
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S116" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T116" t="n">
+        <v>7</v>
+      </c>
+      <c r="U116" t="n">
+        <v>24</v>
+      </c>
+      <c r="V116" t="n">
+        <v>9</v>
+      </c>
+      <c r="W116" t="n">
+        <v>12</v>
+      </c>
+      <c r="X116" t="n">
         <v>14</v>
       </c>
-      <c r="U116" t="n">
-        <v>10</v>
-      </c>
-      <c r="V116" t="n">
-        <v>17</v>
-      </c>
-      <c r="W116" t="n">
-        <v>10</v>
-      </c>
-      <c r="X116" t="n">
-        <v>19</v>
-      </c>
       <c r="Y116" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="Z116" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>Complexo Desportivo FC Alverca</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE116" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AG116" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI116" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AJ116" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL116" t="n">
         <v>1.92</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AN116" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW116" t="n">
         <v>0</v>
@@ -56035,22 +56035,22 @@
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB116" t="n">
-        <v>10708</v>
+        <v>15804</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -56065,64 +56065,64 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU116" t="n">
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BW116" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="BX116" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="BY116" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="BZ116" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="CA116" t="n">
-        <v>1.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB116" t="n">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
@@ -56155,10 +56155,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -56173,85 +56173,85 @@
         <v>21</v>
       </c>
       <c r="CS116" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV116" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CW116" t="n">
         <v>1</v>
       </c>
       <c r="CX116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY116" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CZ116" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="DA116" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="DB116" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="DC116" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.25</v>
+        <v>0.71</v>
       </c>
       <c r="DF116" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="DG116" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="DH116" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="DI116" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DJ116" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="DK116" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.21</v>
+        <v>0.87</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="DO116" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
       </c>
       <c r="DQ116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT116" t="b">
         <v>0</v>
@@ -56260,17 +56260,17 @@
         <v>0</v>
       </c>
       <c r="DV116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW116" t="n">
-        <v>16.34</v>
+        <v>16.07</v>
       </c>
       <c r="DX116" t="n">
-        <v>5.53</v>
+        <v>5.47</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
@@ -56280,39 +56280,23 @@
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="ED116" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EE116" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EF116" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EG116" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr"/>
+      <c r="EE116" t="inlineStr"/>
+      <c r="EF116" t="inlineStr"/>
+      <c r="EG116" t="inlineStr"/>
       <c r="EH116" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -56320,26 +56304,42 @@
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="EK116" t="inlineStr"/>
-      <c r="EL116" t="inlineStr"/>
-      <c r="EM116" t="inlineStr"/>
-      <c r="EN116" t="inlineStr"/>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EL116" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EM116" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN116" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -57169,7 +57169,7 @@
         <v>1.5</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DF118" t="n">
         <v>1.83</v>
@@ -57199,7 +57199,7 @@
         <v>2.85</v>
       </c>
       <c r="DO118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP118" t="b">
         <v>0</v>
@@ -57646,10 +57646,10 @@
         <v>69</v>
       </c>
       <c r="DD119" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DF119" t="n">
         <v>0.33</v>
@@ -57679,7 +57679,7 @@
         <v>2.43</v>
       </c>
       <c r="DO119" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -58137,7 +58137,7 @@
         <v>0.86</v>
       </c>
       <c r="DE120" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF120" t="n">
         <v>1</v>
@@ -58167,7 +58167,7 @@
         <v>2.42</v>
       </c>
       <c r="DO120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -58606,10 +58606,10 @@
         <v>67</v>
       </c>
       <c r="DD121" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="DE121" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF121" t="n">
         <v>2.17</v>
@@ -58639,7 +58639,7 @@
         <v>3.24</v>
       </c>
       <c r="DO121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -59561,7 +59561,7 @@
         <v>1.86</v>
       </c>
       <c r="DE123" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DF123" t="n">
         <v>2.17</v>
@@ -60079,7 +60079,7 @@
         <v>2.09</v>
       </c>
       <c r="DO124" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -60998,7 +60998,7 @@
         <v>84</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DE126" t="n">
         <v>0.71</v>
@@ -61470,7 +61470,7 @@
         <v>75</v>
       </c>
       <c r="DD127" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE127" t="n">
         <v>1.13</v>
@@ -61503,7 +61503,7 @@
         <v>2.55</v>
       </c>
       <c r="DO127" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61975,7 +61975,7 @@
         <v>3.22</v>
       </c>
       <c r="DO128" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -62433,7 +62433,7 @@
         <v>1.86</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DF129" t="n">
         <v>2</v>
@@ -62463,7 +62463,7 @@
         <v>2.67</v>
       </c>
       <c r="DO129" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -64871,7 +64871,7 @@
         <v>3.06</v>
       </c>
       <c r="DO134" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -65351,7 +65351,7 @@
         <v>3.64</v>
       </c>
       <c r="DO135" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65831,7 +65831,7 @@
         <v>3.38</v>
       </c>
       <c r="DO136" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -66916,6 +66916,2358 @@
       <c r="EP138" t="inlineStr">
         <is>
           <t>2.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>16</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Vitória Guimarães</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>46019.64583333334</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3</v>
+      </c>
+      <c r="L139" t="n">
+        <v>5</v>
+      </c>
+      <c r="M139" t="n">
+        <v>4</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>2</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2</v>
+      </c>
+      <c r="S139" t="n">
+        <v>3</v>
+      </c>
+      <c r="T139" t="n">
+        <v>11</v>
+      </c>
+      <c r="U139" t="n">
+        <v>5</v>
+      </c>
+      <c r="V139" t="n">
+        <v>13</v>
+      </c>
+      <c r="W139" t="n">
+        <v>23</v>
+      </c>
+      <c r="X139" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>Campo do Cevadeiro</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>Estrada Nacional 10, Vila Franca de Xira</t>
+        </is>
+      </c>
+      <c r="AC139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>56</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU139" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV139" t="n">
+        <v>23</v>
+      </c>
+      <c r="CW139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX139" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY139" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ139" t="n">
+        <v>22</v>
+      </c>
+      <c r="DA139" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB139" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC139" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD139" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE139" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF139" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DG139" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH139" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DI139" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ139" t="n">
+        <v>79</v>
+      </c>
+      <c r="DK139" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL139" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DM139" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN139" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DO139" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW139" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="DX139" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="DZ139" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EB139" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EC139" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="ED139" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EE139" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF139" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EG139" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EH139" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EI139" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EJ139" t="inlineStr">
+        <is>
+          <t>5.42</t>
+        </is>
+      </c>
+      <c r="EK139" t="inlineStr"/>
+      <c r="EL139" t="inlineStr"/>
+      <c r="EM139" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EN139" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EO139" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EP139" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>16</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>FC Arouca</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>46019.64583333334</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2</v>
+      </c>
+      <c r="I140" t="n">
+        <v>4</v>
+      </c>
+      <c r="J140" t="n">
+        <v>4</v>
+      </c>
+      <c r="K140" t="n">
+        <v>8</v>
+      </c>
+      <c r="L140" t="n">
+        <v>12</v>
+      </c>
+      <c r="M140" t="n">
+        <v>5</v>
+      </c>
+      <c r="N140" t="n">
+        <v>2</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>5</v>
+      </c>
+      <c r="R140" t="n">
+        <v>5</v>
+      </c>
+      <c r="S140" t="n">
+        <v>4</v>
+      </c>
+      <c r="T140" t="n">
+        <v>12</v>
+      </c>
+      <c r="U140" t="n">
+        <v>9</v>
+      </c>
+      <c r="V140" t="n">
+        <v>17</v>
+      </c>
+      <c r="W140" t="n">
+        <v>13</v>
+      </c>
+      <c r="X140" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Estádio Municipal de Arouca</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Afonso Pinto Magalhães Valdasna, Arouca</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW140" t="n">
+        <v>12</v>
+      </c>
+      <c r="DX140" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DY140" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="DZ140" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="EA140" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EB140" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EC140" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="ED140" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EE140" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EF140" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EG140" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EH140" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EI140" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EJ140" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="EK140" t="inlineStr"/>
+      <c r="EL140" t="inlineStr"/>
+      <c r="EM140" t="inlineStr"/>
+      <c r="EN140" t="inlineStr"/>
+      <c r="EO140" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EP140" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>16</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sporting Braga</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>46019.75</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>2</v>
+      </c>
+      <c r="I141" t="n">
+        <v>4</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>5</v>
+      </c>
+      <c r="L141" t="n">
+        <v>6</v>
+      </c>
+      <c r="M141" t="n">
+        <v>3</v>
+      </c>
+      <c r="N141" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>3</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6</v>
+      </c>
+      <c r="S141" t="n">
+        <v>8</v>
+      </c>
+      <c r="T141" t="n">
+        <v>8</v>
+      </c>
+      <c r="U141" t="n">
+        <v>11</v>
+      </c>
+      <c r="V141" t="n">
+        <v>14</v>
+      </c>
+      <c r="W141" t="n">
+        <v>14</v>
+      </c>
+      <c r="X141" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU141" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV141" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX141" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY141" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ141" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA141" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB141" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC141" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD141" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DF141" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG141" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DH141" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI141" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ141" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK141" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL141" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DM141" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN141" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DO141" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW141" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="DX141" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="DY141" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="DZ141" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA141" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EB141" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EC141" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="ED141" t="inlineStr"/>
+      <c r="EE141" t="inlineStr"/>
+      <c r="EF141" t="inlineStr"/>
+      <c r="EG141" t="inlineStr"/>
+      <c r="EH141" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI141" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EJ141" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="EK141" t="inlineStr"/>
+      <c r="EL141" t="inlineStr"/>
+      <c r="EM141" t="inlineStr"/>
+      <c r="EN141" t="inlineStr"/>
+      <c r="EO141" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EP141" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>16</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Rio Ave FC</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>46019.85416666666</v>
+      </c>
+      <c r="G142" t="n">
+        <v>4</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>4</v>
+      </c>
+      <c r="J142" t="n">
+        <v>8</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>9</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>12</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>11</v>
+      </c>
+      <c r="T142" t="n">
+        <v>5</v>
+      </c>
+      <c r="U142" t="n">
+        <v>23</v>
+      </c>
+      <c r="V142" t="n">
+        <v>5</v>
+      </c>
+      <c r="W142" t="n">
+        <v>13</v>
+      </c>
+      <c r="X142" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Estádio José Alvalade</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>Rua Professor Fernando da Fonseca, Lisboa</t>
+        </is>
+      </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>114</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>155</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>50</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DE142" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF142" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DG142" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DH142" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DI142" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ142" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK142" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL142" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DM142" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN142" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="DO142" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW142" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="DX142" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="DY142" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="DZ142" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="EA142" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="EB142" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="EC142" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="ED142" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EE142" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF142" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EG142" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EH142" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="EI142" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ142" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EK142" t="inlineStr"/>
+      <c r="EL142" t="inlineStr"/>
+      <c r="EM142" t="inlineStr"/>
+      <c r="EN142" t="inlineStr"/>
+      <c r="EO142" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EP142" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>16</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AVS</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>46020.84375</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" t="n">
+        <v>7</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>7</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>4</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1</v>
+      </c>
+      <c r="S143" t="n">
+        <v>14</v>
+      </c>
+      <c r="T143" t="n">
+        <v>6</v>
+      </c>
+      <c r="U143" t="n">
+        <v>18</v>
+      </c>
+      <c r="V143" t="n">
+        <v>7</v>
+      </c>
+      <c r="W143" t="n">
+        <v>8</v>
+      </c>
+      <c r="X143" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>Estádio Do Dragão</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>Via Futebol Clube do Porto, Porto</t>
+        </is>
+      </c>
+      <c r="AC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>82</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>143</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU143" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV143" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX143" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY143" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ143" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA143" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB143" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC143" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DE143" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF143" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DG143" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DH143" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DI143" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DJ143" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK143" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL143" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DM143" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN143" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DO143" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ143" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV143" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW143" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="DX143" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DY143" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DZ143" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="EA143" t="inlineStr">
+        <is>
+          <t>23.60</t>
+        </is>
+      </c>
+      <c r="EB143" t="inlineStr">
+        <is>
+          <t>10.61</t>
+        </is>
+      </c>
+      <c r="EC143" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="ED143" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EE143" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EF143" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EG143" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH143" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="EI143" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EJ143" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EK143" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EL143" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM143" t="inlineStr"/>
+      <c r="EN143" t="inlineStr"/>
+      <c r="EO143" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EP143" t="inlineStr">
+        <is>
+          <t>1.48</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -69456,7 +69456,7 @@
         <v>0</v>
       </c>
       <c r="BF144" t="n">
-        <v>-1</v>
+        <v>8956</v>
       </c>
       <c r="BG144" t="n">
         <v>2</v>
@@ -69944,7 +69944,7 @@
         <v>0</v>
       </c>
       <c r="BF145" t="n">
-        <v>-1</v>
+        <v>13955</v>
       </c>
       <c r="BG145" t="n">
         <v>2</v>
@@ -71745,10 +71745,10 @@
         <v>11</v>
       </c>
       <c r="Y149" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z149" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
@@ -72549,47 +72549,47 @@
       </c>
       <c r="EB150" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="EC150" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="ED150" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EE150" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EF150" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EG150" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EH150" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI150" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EJ150" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="EK150" t="inlineStr">
@@ -72614,12 +72614,12 @@
       </c>
       <c r="EO150" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EP150" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -73024,36 +73024,52 @@
       </c>
       <c r="EA151" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EB151" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="EC151" t="inlineStr">
+        <is>
+          <t>7.59</t>
+        </is>
+      </c>
+      <c r="ED151" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EE151" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EF151" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EG151" t="inlineStr">
+        <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="EB151" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
-      <c r="EC151" t="inlineStr">
-        <is>
-          <t>7.80</t>
-        </is>
-      </c>
-      <c r="ED151" t="inlineStr"/>
-      <c r="EE151" t="inlineStr"/>
-      <c r="EF151" t="inlineStr"/>
-      <c r="EG151" t="inlineStr"/>
       <c r="EH151" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EI151" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EJ151" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="EK151" t="inlineStr">
@@ -73068,17 +73084,17 @@
       </c>
       <c r="EM151" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EN151" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EO151" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EP151" t="inlineStr">
@@ -73496,82 +73512,82 @@
       </c>
       <c r="EA152" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EB152" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EC152" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="ED152" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EE152" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EF152" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EG152" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH152" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI152" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EJ152" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="EK152" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EL152" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EM152" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EN152" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EO152" t="inlineStr">
+        <is>
           <t>1.92</t>
         </is>
       </c>
-      <c r="EH152" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EI152" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EJ152" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
-      </c>
-      <c r="EK152" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
-      <c r="EL152" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EM152" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EN152" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="EO152" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="EP152" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -74145,10 +74145,10 @@
         <v>13</v>
       </c>
       <c r="Y154" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z154" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA154" t="inlineStr">
         <is>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP154" headerRowCount="1">
-  <autoFilter ref="A1:EP154"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP155" headerRowCount="1">
+  <autoFilter ref="A1:EP155"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP154"/>
+  <dimension ref="A1:EP155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -5661,7 +5661,7 @@
         <v>0.33</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE17" t="n">
         <v>0.63</v>
@@ -12301,7 +12301,7 @@
         <v>2.75</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF24" t="n">
         <v>3</v>
@@ -15670,7 +15670,7 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE31" t="n">
         <v>3</v>
@@ -21821,7 +21821,7 @@
         <v>1</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -26642,7 +26642,7 @@
         <v>50</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE54" t="n">
         <v>1.22</v>
@@ -28069,7 +28069,7 @@
         <v>2</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF57" t="n">
         <v>3</v>
@@ -32015,170 +32015,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L66" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
         <v>7</v>
       </c>
       <c r="R66" t="n">
+        <v>4</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="n">
+        <v>6</v>
+      </c>
+      <c r="U66" t="n">
+        <v>17</v>
+      </c>
+      <c r="V66" t="n">
+        <v>10</v>
+      </c>
+      <c r="W66" t="n">
+        <v>12</v>
+      </c>
+      <c r="X66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="n">
         <v>5</v>
       </c>
-      <c r="S66" t="n">
-        <v>8</v>
-      </c>
-      <c r="T66" t="n">
-        <v>10</v>
-      </c>
-      <c r="U66" t="n">
-        <v>15</v>
-      </c>
-      <c r="V66" t="n">
-        <v>15</v>
-      </c>
-      <c r="W66" t="n">
-        <v>13</v>
-      </c>
-      <c r="X66" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Estádio Cidade de Barcelos</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>strada Nacional 103, Vila Boa, Barcelos</t>
-        </is>
-      </c>
-      <c r="AC66" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>3</v>
-      </c>
       <c r="AE66" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="AF66" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AG66" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI66" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AK66" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AN66" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AO66" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR66" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AU66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
         <v>2</v>
       </c>
       <c r="BB66" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32193,178 +32193,178 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM66" t="n">
         <v>4</v>
       </c>
-      <c r="BJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL66" t="n">
+      <c r="BN66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS66" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU66" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV66" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX66" t="n">
         <v>6</v>
-      </c>
-      <c r="BM66" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN66" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT66" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV66" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW66" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>83</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CB66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CC66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS66" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX66" t="n">
-        <v>8</v>
       </c>
       <c r="CY66" t="n">
         <v>8</v>
       </c>
       <c r="CZ66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA66" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DB66" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DC66" t="n">
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.75</v>
+        <v>0.88</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="DF66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DG66" t="n">
         <v>1</v>
       </c>
       <c r="DH66" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="DI66" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DJ66" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK66" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="DO66" t="n">
         <v>17</v>
@@ -32376,69 +32376,69 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU66" t="b">
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW66" t="n">
-        <v>25.52</v>
+        <v>24.96</v>
       </c>
       <c r="DX66" t="n">
-        <v>6.19</v>
+        <v>6.88</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EE66" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF66" t="inlineStr">
+        <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="EE66" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EF66" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
@@ -32448,42 +32448,42 @@
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -32503,170 +32503,170 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
         <v>5</v>
       </c>
-      <c r="J67" t="n">
-        <v>2</v>
-      </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L67" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>7</v>
       </c>
       <c r="R67" t="n">
+        <v>5</v>
+      </c>
+      <c r="S67" t="n">
+        <v>8</v>
+      </c>
+      <c r="T67" t="n">
+        <v>10</v>
+      </c>
+      <c r="U67" t="n">
+        <v>15</v>
+      </c>
+      <c r="V67" t="n">
+        <v>15</v>
+      </c>
+      <c r="W67" t="n">
+        <v>13</v>
+      </c>
+      <c r="X67" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Estádio Cidade de Barcelos</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>strada Nacional 103, Vila Boa, Barcelos</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
         <v>4</v>
       </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="n">
-        <v>6</v>
-      </c>
-      <c r="U67" t="n">
-        <v>17</v>
-      </c>
-      <c r="V67" t="n">
-        <v>10</v>
-      </c>
-      <c r="W67" t="n">
-        <v>12</v>
-      </c>
-      <c r="X67" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
-      <c r="AC67" t="n">
-        <v>1</v>
-      </c>
       <c r="AD67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="AF67" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AG67" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AI67" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ67" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AL67" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AN67" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AO67" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AR67" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AS67" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AU67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
       </c>
       <c r="BB67" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32681,73 +32681,73 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM67" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT67" t="n">
         <v>4</v>
       </c>
-      <c r="BN67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT67" t="n">
-        <v>3</v>
-      </c>
       <c r="BU67" t="n">
         <v>1</v>
       </c>
       <c r="BV67" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BW67" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="BX67" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="BY67" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BZ67" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="CA67" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="CB67" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="CC67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD67" t="n">
         <v>0</v>
       </c>
       <c r="CE67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF67" t="n">
         <v>0</v>
@@ -32768,10 +32768,10 @@
         <v>0</v>
       </c>
       <c r="CL67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN67" t="n">
         <v>0</v>
@@ -32786,73 +32786,73 @@
         <v>1</v>
       </c>
       <c r="CR67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS67" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT67" t="n">
         <v>1</v>
       </c>
       <c r="CU67" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW67" t="n">
         <v>1</v>
       </c>
       <c r="CX67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY67" t="n">
         <v>8</v>
       </c>
       <c r="CZ67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA67" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DB67" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DC67" t="n">
         <v>50</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.88</v>
+        <v>1.75</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="DF67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DG67" t="n">
         <v>1</v>
       </c>
       <c r="DH67" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="DI67" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="DJ67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK67" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="DM67" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="DN67" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="DO67" t="n">
         <v>17</v>
@@ -32864,114 +32864,114 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU67" t="b">
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW67" t="n">
-        <v>24.96</v>
+        <v>25.52</v>
       </c>
       <c r="DX67" t="n">
-        <v>6.88</v>
+        <v>6.19</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA67" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="EB67" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EC67" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="ED67" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EE67" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EH67" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI67" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ67" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EK67" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EL67" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM67" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN67" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EO67" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP67" t="inlineStr">
+        <is>
           <t>1.72</t>
-        </is>
-      </c>
-      <c r="EH67" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI67" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ67" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="EK67" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="EL67" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EM67" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EN67" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EO67" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EP67" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -35194,7 +35194,7 @@
         <v>67</v>
       </c>
       <c r="DD72" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE72" t="n">
         <v>1.44</v>
@@ -36811,76 +36811,76 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45955.8125</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>8</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>9</v>
+      </c>
+      <c r="T76" t="n">
         <v>5</v>
       </c>
-      <c r="L76" t="n">
-        <v>9</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2</v>
-      </c>
-      <c r="N76" t="n">
+      <c r="U76" t="n">
+        <v>17</v>
+      </c>
+      <c r="V76" t="n">
         <v>5</v>
       </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>2</v>
-      </c>
-      <c r="R76" t="n">
-        <v>2</v>
-      </c>
-      <c r="S76" t="n">
-        <v>14</v>
-      </c>
-      <c r="T76" t="n">
-        <v>6</v>
-      </c>
-      <c r="U76" t="n">
-        <v>16</v>
-      </c>
-      <c r="V76" t="n">
-        <v>8</v>
-      </c>
       <c r="W76" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X76" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y76" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Z76" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
@@ -36888,85 +36888,85 @@
         <v>2</v>
       </c>
       <c r="AD76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AU76" t="n">
         <v>5</v>
       </c>
-      <c r="AE76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU76" t="n">
-        <v>3</v>
-      </c>
       <c r="AV76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW76" t="n">
         <v>0</v>
       </c>
       <c r="AX76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
         <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB76" t="n">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36981,178 +36981,178 @@
         <v>1</v>
       </c>
       <c r="BI76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN76" t="n">
         <v>6</v>
       </c>
       <c r="BO76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP76" t="n">
         <v>1</v>
       </c>
       <c r="BQ76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
         <v>5</v>
       </c>
-      <c r="BU76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV76" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW76" t="n">
-        <v>28</v>
-      </c>
-      <c r="BX76" t="n">
-        <v>94</v>
-      </c>
-      <c r="BY76" t="n">
-        <v>63</v>
-      </c>
-      <c r="BZ76" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CA76" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="CB76" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS76" t="n">
-        <v>24</v>
-      </c>
-      <c r="CT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU76" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV76" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX76" t="n">
-        <v>7</v>
-      </c>
       <c r="CY76" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CZ76" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DA76" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB76" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="DC76" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.11</v>
+        <v>2.11</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.22</v>
+        <v>0.63</v>
       </c>
       <c r="DF76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DG76" t="n">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="DH76" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL76" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DM76" t="n">
         <v>0.88</v>
       </c>
-      <c r="DI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ76" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK76" t="n">
-        <v>25</v>
-      </c>
-      <c r="DL76" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DM76" t="n">
-        <v>1.1</v>
-      </c>
       <c r="DN76" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="DO76" t="n">
         <v>17</v>
@@ -37167,111 +37167,103 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU76" t="b">
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW76" t="n">
-        <v>21.83</v>
+        <v>22.85</v>
       </c>
       <c r="DX76" t="n">
-        <v>4.62</v>
+        <v>4.75</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>13.66</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EG76" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EH76" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EI76" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ76" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EK76" t="inlineStr">
+        <is>
           <t>2.12</t>
         </is>
       </c>
-      <c r="EJ76" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="EK76" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
-      </c>
       <c r="EL76" t="inlineStr">
         <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EM76" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN76" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EM76" t="inlineStr"/>
+      <c r="EN76" t="inlineStr"/>
       <c r="EO76" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EP76" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.77</t>
         </is>
       </c>
     </row>
@@ -37291,41 +37283,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
         <v>45955.8125</v>
       </c>
       <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4</v>
+      </c>
+      <c r="K77" t="n">
         <v>5</v>
       </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
+      <c r="L77" t="n">
+        <v>9</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" t="n">
         <v>5</v>
       </c>
-      <c r="J77" t="n">
-        <v>9</v>
-      </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" t="n">
-        <v>10</v>
-      </c>
-      <c r="M77" t="n">
-        <v>2</v>
-      </c>
-      <c r="N77" t="n">
-        <v>2</v>
-      </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
@@ -37333,34 +37325,34 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
+        <v>2</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2</v>
+      </c>
+      <c r="S77" t="n">
+        <v>14</v>
+      </c>
+      <c r="T77" t="n">
+        <v>6</v>
+      </c>
+      <c r="U77" t="n">
+        <v>16</v>
+      </c>
+      <c r="V77" t="n">
         <v>8</v>
       </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>9</v>
-      </c>
-      <c r="T77" t="n">
-        <v>5</v>
-      </c>
-      <c r="U77" t="n">
-        <v>17</v>
-      </c>
-      <c r="V77" t="n">
-        <v>5</v>
-      </c>
       <c r="W77" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X77" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y77" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Z77" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
@@ -37368,85 +37360,85 @@
         <v>2</v>
       </c>
       <c r="AD77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="AF77" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="AG77" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="AJ77" t="n">
-        <v>2.08</v>
+        <v>3.54</v>
       </c>
       <c r="AK77" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL77" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AM77" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AN77" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AO77" t="n">
-        <v>2.41</v>
+        <v>2.19</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AR77" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AS77" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="AT77" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AU77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW77" t="n">
         <v>0</v>
       </c>
       <c r="AX77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ77" t="n">
         <v>2</v>
       </c>
       <c r="BA77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB77" t="n">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="BC77" t="n">
         <v>0</v>
       </c>
       <c r="BD77" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="BE77" t="n">
         <v>0</v>
@@ -37461,73 +37453,73 @@
         <v>1</v>
       </c>
       <c r="BI77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN77" t="n">
         <v>6</v>
       </c>
       <c r="BO77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP77" t="n">
         <v>1</v>
       </c>
       <c r="BQ77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU77" t="n">
         <v>1</v>
       </c>
       <c r="BV77" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="BW77" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="BX77" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="BY77" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="BZ77" t="n">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="CA77" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="CB77" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="CC77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD77" t="n">
         <v>0</v>
       </c>
       <c r="CE77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF77" t="n">
         <v>0</v>
@@ -37545,13 +37537,13 @@
         <v>1</v>
       </c>
       <c r="CK77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL77" t="n">
         <v>0</v>
       </c>
       <c r="CM77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
@@ -37560,79 +37552,79 @@
         <v>0</v>
       </c>
       <c r="CP77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ77" t="n">
         <v>1</v>
       </c>
       <c r="CR77" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="CS77" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CT77" t="n">
         <v>1</v>
       </c>
       <c r="CU77" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY77" t="n">
         <v>15</v>
       </c>
-      <c r="CV77" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX77" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY77" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ77" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DA77" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB77" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="DC77" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DD77" t="n">
-        <v>2.11</v>
+        <v>1.11</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.63</v>
+        <v>1.22</v>
       </c>
       <c r="DF77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DG77" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DH77" t="n">
-        <v>2.25</v>
+        <v>0.88</v>
       </c>
       <c r="DI77" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DJ77" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DK77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL77" t="n">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="DM77" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="DN77" t="n">
-        <v>3.06</v>
+        <v>2.46</v>
       </c>
       <c r="DO77" t="n">
         <v>17</v>
@@ -37647,103 +37639,111 @@
         <v>1</v>
       </c>
       <c r="DS77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU77" t="b">
         <v>0</v>
       </c>
       <c r="DV77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW77" t="n">
-        <v>22.85</v>
+        <v>21.83</v>
       </c>
       <c r="DX77" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>13.66</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EC77" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EF77" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EG77" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EH77" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI77" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EJ77" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="EK77" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EL77" t="inlineStr">
         <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EM77" t="inlineStr"/>
-      <c r="EN77" t="inlineStr"/>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EM77" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN77" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
       <c r="EO77" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EP77" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -39525,7 +39525,7 @@
         <v>1.75</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -40498,7 +40498,7 @@
         <v>75</v>
       </c>
       <c r="DD83" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE83" t="n">
         <v>0.88</v>
@@ -46399,12 +46399,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
@@ -46420,20 +46420,20 @@
         <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
+        <v>6</v>
+      </c>
+      <c r="L96" t="n">
+        <v>8</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3</v>
+      </c>
+      <c r="N96" t="n">
         <v>4</v>
       </c>
-      <c r="L96" t="n">
-        <v>5</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" t="n">
-        <v>5</v>
-      </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
@@ -46441,98 +46441,90 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T96" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U96" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V96" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W96" t="n">
         <v>12</v>
       </c>
       <c r="X96" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y96" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="Z96" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>Estádio Clube Desportivo das Aves</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE96" t="n">
-        <v>5.75</v>
+        <v>2.42</v>
       </c>
       <c r="AF96" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AG96" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI96" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AJ96" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AK96" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AL96" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AM96" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AN96" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AO96" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AR96" t="n">
         <v>3.22</v>
       </c>
       <c r="AS96" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AT96" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU96" t="n">
         <v>2</v>
@@ -46562,7 +46554,7 @@
         <v>0</v>
       </c>
       <c r="BD96" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE96" t="n">
         <v>0</v>
@@ -46580,70 +46572,70 @@
         <v>1</v>
       </c>
       <c r="BJ96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT96" t="n">
         <v>4</v>
       </c>
-      <c r="BK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM96" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR96" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT96" t="n">
-        <v>5</v>
-      </c>
       <c r="BU96" t="n">
         <v>1</v>
       </c>
       <c r="BV96" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW96" t="n">
         <v>44</v>
       </c>
-      <c r="BW96" t="n">
-        <v>47</v>
-      </c>
       <c r="BX96" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BY96" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="BZ96" t="n">
-        <v>1.88</v>
+        <v>1.37</v>
       </c>
       <c r="CA96" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="CB96" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="CC96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD96" t="n">
         <v>0</v>
       </c>
       <c r="CE96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF96" t="n">
         <v>0</v>
@@ -46664,13 +46656,13 @@
         <v>0</v>
       </c>
       <c r="CL96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM96" t="n">
         <v>0</v>
       </c>
       <c r="CN96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CO96" t="n">
         <v>0</v>
@@ -46682,73 +46674,73 @@
         <v>1</v>
       </c>
       <c r="CR96" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CS96" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CT96" t="n">
         <v>1</v>
       </c>
       <c r="CU96" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV96" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY96" t="n">
         <v>11</v>
       </c>
-      <c r="CW96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX96" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY96" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ96" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DA96" t="n">
         <v>70</v>
       </c>
       <c r="DB96" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DC96" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD96" t="n">
-        <v>0.33</v>
+        <v>1.11</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="DF96" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG96" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="DH96" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="DI96" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="DJ96" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="DK96" t="n">
         <v>30</v>
       </c>
       <c r="DL96" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="DM96" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="DN96" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="DO96" t="n">
         <v>17</v>
@@ -46775,87 +46767,67 @@
         <v>1</v>
       </c>
       <c r="DW96" t="n">
-        <v>16.28</v>
+        <v>16.49</v>
       </c>
       <c r="DX96" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="DY96" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="DZ96" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA96" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="EB96" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EC96" t="inlineStr">
         <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="ED96" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EE96" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EF96" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG96" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EH96" t="inlineStr"/>
-      <c r="EI96" t="inlineStr"/>
-      <c r="EJ96" t="inlineStr"/>
-      <c r="EK96" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EL96" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EM96" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EN96" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr"/>
+      <c r="EE96" t="inlineStr"/>
+      <c r="EF96" t="inlineStr"/>
+      <c r="EG96" t="inlineStr"/>
+      <c r="EH96" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI96" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ96" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EK96" t="inlineStr"/>
+      <c r="EL96" t="inlineStr"/>
+      <c r="EM96" t="inlineStr"/>
+      <c r="EN96" t="inlineStr"/>
       <c r="EO96" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EP96" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -46875,12 +46847,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
@@ -46896,111 +46868,119 @@
         <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L97" t="n">
+        <v>5</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
         <v>8</v>
       </c>
-      <c r="M97" t="n">
-        <v>3</v>
-      </c>
-      <c r="N97" t="n">
-        <v>4</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>4</v>
-      </c>
       <c r="R97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U97" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V97" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="W97" t="n">
         <v>12</v>
       </c>
       <c r="X97" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y97" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="Z97" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA97" t="inlineStr"/>
-      <c r="AB97" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Estádio Clube Desportivo das Aves</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
+        </is>
+      </c>
       <c r="AC97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE97" t="n">
-        <v>2.42</v>
+        <v>5.75</v>
       </c>
       <c r="AF97" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AG97" t="n">
-        <v>2.96</v>
+        <v>1.63</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI97" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AJ97" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AK97" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AL97" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AN97" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AO97" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR97" t="n">
         <v>3.22</v>
       </c>
       <c r="AS97" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AT97" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU97" t="n">
         <v>2</v>
@@ -47030,7 +47010,7 @@
         <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE97" t="n">
         <v>0</v>
@@ -47048,175 +47028,175 @@
         <v>1</v>
       </c>
       <c r="BJ97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM97" t="n">
         <v>5</v>
       </c>
-      <c r="BK97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM97" t="n">
+      <c r="BN97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX97" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY97" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ97" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CB97" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN97" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR97" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS97" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU97" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV97" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX97" t="n">
         <v>6</v>
       </c>
-      <c r="BN97" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO97" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR97" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS97" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT97" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV97" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW97" t="n">
-        <v>44</v>
-      </c>
-      <c r="BX97" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY97" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ97" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CA97" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB97" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="CC97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP97" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR97" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS97" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU97" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV97" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW97" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX97" t="n">
-        <v>7</v>
-      </c>
       <c r="CY97" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CZ97" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DA97" t="n">
         <v>70</v>
       </c>
       <c r="DB97" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DC97" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.11</v>
+        <v>0.33</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="DF97" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="DG97" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DH97" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DI97" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="DJ97" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="DK97" t="n">
         <v>30</v>
       </c>
       <c r="DL97" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="DM97" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="DN97" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="DO97" t="n">
         <v>17</v>
@@ -47243,67 +47223,87 @@
         <v>1</v>
       </c>
       <c r="DW97" t="n">
-        <v>16.49</v>
+        <v>16.28</v>
       </c>
       <c r="DX97" t="n">
-        <v>2.95</v>
+        <v>1.64</v>
       </c>
       <c r="DY97" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ97" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA97" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EB97" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="EC97" t="inlineStr">
         <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EE97" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF97" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG97" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EH97" t="inlineStr"/>
+      <c r="EI97" t="inlineStr"/>
+      <c r="EJ97" t="inlineStr"/>
+      <c r="EK97" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EL97" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM97" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EN97" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EO97" t="inlineStr">
+        <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="ED97" t="inlineStr"/>
-      <c r="EE97" t="inlineStr"/>
-      <c r="EF97" t="inlineStr"/>
-      <c r="EG97" t="inlineStr"/>
-      <c r="EH97" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EI97" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EJ97" t="inlineStr">
-        <is>
-          <t>4.24</t>
-        </is>
-      </c>
-      <c r="EK97" t="inlineStr"/>
-      <c r="EL97" t="inlineStr"/>
-      <c r="EM97" t="inlineStr"/>
-      <c r="EN97" t="inlineStr"/>
-      <c r="EO97" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
       <c r="EP97" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
@@ -47803,12 +47803,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
@@ -47818,16 +47818,16 @@
         <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L99" t="n">
         <v>8</v>
@@ -47845,34 +47845,34 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S99" t="n">
+        <v>13</v>
+      </c>
+      <c r="T99" t="n">
+        <v>3</v>
+      </c>
+      <c r="U99" t="n">
+        <v>19</v>
+      </c>
+      <c r="V99" t="n">
+        <v>7</v>
+      </c>
+      <c r="W99" t="n">
         <v>8</v>
       </c>
-      <c r="T99" t="n">
-        <v>10</v>
-      </c>
-      <c r="U99" t="n">
-        <v>11</v>
-      </c>
-      <c r="V99" t="n">
-        <v>11</v>
-      </c>
-      <c r="W99" t="n">
-        <v>13</v>
-      </c>
       <c r="X99" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y99" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="Z99" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -47883,55 +47883,55 @@
         <v>2</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AF99" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AJ99" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AK99" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AL99" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AN99" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AS99" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AU99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV99" t="n">
         <v>1</v>
@@ -47943,22 +47943,22 @@
         <v>1</v>
       </c>
       <c r="AY99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA99" t="n">
         <v>1</v>
       </c>
       <c r="BB99" t="n">
-        <v>172</v>
+        <v>-1</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47973,64 +47973,64 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ99" t="n">
         <v>2</v>
       </c>
       <c r="BK99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT99" t="n">
         <v>4</v>
       </c>
-      <c r="BL99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN99" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT99" t="n">
-        <v>5</v>
-      </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="BW99" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="BX99" t="n">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="BY99" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.23</v>
+        <v>2.19</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="CB99" t="n">
-        <v>2.28</v>
+        <v>3.06</v>
       </c>
       <c r="CC99" t="n">
         <v>1</v>
@@ -48078,73 +48078,73 @@
         <v>1</v>
       </c>
       <c r="CR99" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CS99" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="CT99" t="n">
         <v>1</v>
       </c>
       <c r="CU99" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="CV99" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CW99" t="n">
         <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CY99" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="CZ99" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DA99" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="DB99" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DC99" t="n">
         <v>80</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="DF99" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="DG99" t="n">
         <v>1.2</v>
       </c>
       <c r="DH99" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="DI99" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="DJ99" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DK99" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="DM99" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="DN99" t="n">
-        <v>2.42</v>
+        <v>3.17</v>
       </c>
       <c r="DO99" t="n">
         <v>17</v>
@@ -48159,7 +48159,7 @@
         <v>1</v>
       </c>
       <c r="DS99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT99" t="b">
         <v>0</v>
@@ -48171,99 +48171,83 @@
         <v>1</v>
       </c>
       <c r="DW99" t="n">
-        <v>16.36</v>
+        <v>17.32</v>
       </c>
       <c r="DX99" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EE99" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF99" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr"/>
+      <c r="EF99" t="inlineStr"/>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI99" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EJ99" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EM99" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EN99" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="inlineStr"/>
       <c r="EO99" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EP99" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.49</t>
         </is>
       </c>
     </row>
@@ -48283,12 +48267,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
@@ -48298,16 +48282,16 @@
         <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L100" t="n">
         <v>8</v>
@@ -48325,34 +48309,34 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
+        <v>8</v>
+      </c>
+      <c r="T100" t="n">
+        <v>10</v>
+      </c>
+      <c r="U100" t="n">
+        <v>11</v>
+      </c>
+      <c r="V100" t="n">
+        <v>11</v>
+      </c>
+      <c r="W100" t="n">
         <v>13</v>
       </c>
-      <c r="T100" t="n">
-        <v>3</v>
-      </c>
-      <c r="U100" t="n">
-        <v>19</v>
-      </c>
-      <c r="V100" t="n">
-        <v>7</v>
-      </c>
-      <c r="W100" t="n">
-        <v>8</v>
-      </c>
       <c r="X100" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y100" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="Z100" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -48363,55 +48347,55 @@
         <v>2</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AF100" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG100" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AI100" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM100" t="n">
         <v>1.62</v>
       </c>
-      <c r="AJ100" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AN100" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AU100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV100" t="n">
         <v>1</v>
@@ -48423,22 +48407,22 @@
         <v>1</v>
       </c>
       <c r="AY100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA100" t="n">
         <v>1</v>
       </c>
       <c r="BB100" t="n">
-        <v>-1</v>
+        <v>172</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48453,178 +48437,178 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ100" t="n">
         <v>2</v>
       </c>
       <c r="BK100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN100" t="n">
         <v>5</v>
       </c>
-      <c r="BN100" t="n">
-        <v>3</v>
-      </c>
       <c r="BO100" t="n">
         <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ100" t="n">
         <v>3</v>
       </c>
       <c r="BR100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="BW100" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
         <v>19</v>
       </c>
-      <c r="BX100" t="n">
-        <v>144</v>
-      </c>
-      <c r="BY100" t="n">
-        <v>55</v>
-      </c>
-      <c r="BZ100" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CA100" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>21</v>
-      </c>
       <c r="CS100" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="CT100" t="n">
         <v>1</v>
       </c>
       <c r="CU100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
         <v>7</v>
       </c>
-      <c r="CV100" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>1</v>
-      </c>
       <c r="CY100" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="CZ100" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DA100" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="DB100" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DC100" t="n">
         <v>80</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="DF100" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="DG100" t="n">
         <v>1.2</v>
       </c>
       <c r="DH100" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="DI100" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="DJ100" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DK100" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DL100" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DN100" t="n">
-        <v>3.17</v>
+        <v>2.42</v>
       </c>
       <c r="DO100" t="n">
         <v>17</v>
@@ -48639,7 +48623,7 @@
         <v>1</v>
       </c>
       <c r="DS100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT100" t="b">
         <v>0</v>
@@ -48651,83 +48635,99 @@
         <v>1</v>
       </c>
       <c r="DW100" t="n">
-        <v>17.32</v>
+        <v>16.36</v>
       </c>
       <c r="DX100" t="n">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="EC100" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="ED100" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EE100" t="inlineStr"/>
-      <c r="EF100" t="inlineStr"/>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EK100" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EM100" t="inlineStr"/>
-      <c r="EN100" t="inlineStr"/>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EN100" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.72</t>
         </is>
       </c>
     </row>
@@ -49203,40 +49203,40 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
         <v>45990.64583333334</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
         <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K102" t="n">
         <v>4</v>
       </c>
       <c r="L102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
@@ -49245,128 +49245,128 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
       </c>
       <c r="T102" t="n">
+        <v>9</v>
+      </c>
+      <c r="U102" t="n">
+        <v>11</v>
+      </c>
+      <c r="V102" t="n">
+        <v>17</v>
+      </c>
+      <c r="W102" t="n">
+        <v>17</v>
+      </c>
+      <c r="X102" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
+        </is>
+      </c>
+      <c r="AC102" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD102" t="n">
         <v>5</v>
       </c>
-      <c r="U102" t="n">
-        <v>5</v>
-      </c>
-      <c r="V102" t="n">
-        <v>10</v>
-      </c>
-      <c r="W102" t="n">
-        <v>9</v>
-      </c>
-      <c r="X102" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>Campo do Cevadeiro</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>Estrada Nacional 10, Vila Franca de Xira</t>
-        </is>
-      </c>
-      <c r="AC102" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD102" t="n">
+      <c r="AE102" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU102" t="n">
         <v>4</v>
       </c>
-      <c r="AE102" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH102" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI102" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AK102" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL102" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO102" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AP102" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AQ102" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR102" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS102" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT102" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AU102" t="n">
-        <v>2</v>
-      </c>
       <c r="AV102" t="n">
         <v>0</v>
       </c>
       <c r="AW102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB102" t="n">
-        <v>10708</v>
+        <v>-1</v>
       </c>
       <c r="BC102" t="n">
         <v>0</v>
       </c>
       <c r="BD102" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE102" t="n">
         <v>0</v>
@@ -49375,70 +49375,70 @@
         <v>-1</v>
       </c>
       <c r="BG102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH102" t="n">
         <v>1</v>
       </c>
       <c r="BI102" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BK102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BL102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM102" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BN102" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ102" t="n">
         <v>4</v>
-      </c>
-      <c r="BP102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ102" t="n">
-        <v>1</v>
       </c>
       <c r="BR102" t="n">
         <v>4</v>
       </c>
       <c r="BS102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BT102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BU102" t="n">
         <v>1</v>
       </c>
       <c r="BV102" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BW102" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="BX102" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="BY102" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BZ102" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="CA102" t="n">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="CB102" t="n">
-        <v>1.88</v>
+        <v>3.27</v>
       </c>
       <c r="CC102" t="n">
         <v>0</v>
@@ -49471,10 +49471,10 @@
         <v>0</v>
       </c>
       <c r="CM102" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN102" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CO102" t="n">
         <v>0</v>
@@ -49486,7 +49486,7 @@
         <v>1</v>
       </c>
       <c r="CR102" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="CS102" t="n">
         <v>15</v>
@@ -49495,64 +49495,64 @@
         <v>1</v>
       </c>
       <c r="CU102" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV102" t="n">
         <v>17</v>
       </c>
-      <c r="CV102" t="n">
-        <v>9</v>
-      </c>
       <c r="CW102" t="n">
         <v>1</v>
       </c>
       <c r="CX102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CZ102" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB102" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC102" t="n">
+        <v>40</v>
+      </c>
+      <c r="DD102" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF102" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG102" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DH102" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DI102" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DJ102" t="n">
         <v>60</v>
       </c>
-      <c r="DA102" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB102" t="n">
-        <v>70</v>
-      </c>
-      <c r="DC102" t="n">
-        <v>80</v>
-      </c>
-      <c r="DD102" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DE102" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DF102" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DG102" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DH102" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DI102" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ102" t="n">
-        <v>40</v>
-      </c>
       <c r="DK102" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DL102" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="DM102" t="n">
-        <v>0.86</v>
+        <v>1.56</v>
       </c>
       <c r="DN102" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="DO102" t="n">
         <v>17</v>
@@ -49564,10 +49564,10 @@
         <v>1</v>
       </c>
       <c r="DR102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT102" t="b">
         <v>0</v>
@@ -49576,17 +49576,17 @@
         <v>0</v>
       </c>
       <c r="DV102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW102" t="n">
-        <v>16.26</v>
+        <v>16.23</v>
       </c>
       <c r="DX102" t="n">
-        <v>5.37</v>
+        <v>6.33</v>
       </c>
       <c r="DY102" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="DZ102" t="inlineStr">
@@ -49596,82 +49596,82 @@
       </c>
       <c r="EA102" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EB102" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EC102" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="ED102" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EE102" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EF102" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EG102" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EH102" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI102" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EJ102" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="EK102" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="EL102" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EM102" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EN102" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EO102" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EP102" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -49691,170 +49691,170 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
         <v>45990.64583333334</v>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
         <v>2</v>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K103" t="n">
         <v>4</v>
       </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N103" t="n">
+        <v>4</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
         <v>5</v>
-      </c>
-      <c r="O103" t="n">
-        <v>1</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>6</v>
-      </c>
-      <c r="R103" t="n">
-        <v>8</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
       </c>
       <c r="T103" t="n">
+        <v>5</v>
+      </c>
+      <c r="U103" t="n">
+        <v>5</v>
+      </c>
+      <c r="V103" t="n">
+        <v>10</v>
+      </c>
+      <c r="W103" t="n">
         <v>9</v>
       </c>
-      <c r="U103" t="n">
-        <v>11</v>
-      </c>
-      <c r="V103" t="n">
+      <c r="X103" t="n">
         <v>17</v>
       </c>
-      <c r="W103" t="n">
-        <v>17</v>
-      </c>
-      <c r="X103" t="n">
-        <v>22</v>
-      </c>
       <c r="Y103" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z103" t="n">
         <v>48</v>
       </c>
-      <c r="Z103" t="n">
-        <v>52</v>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
+          <t>Campo do Cevadeiro</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
+          <t>Estrada Nacional 10, Vila Franca de Xira</t>
         </is>
       </c>
       <c r="AC103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD103" t="n">
         <v>4</v>
       </c>
-      <c r="AD103" t="n">
-        <v>5</v>
-      </c>
       <c r="AE103" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="AF103" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AI103" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AJ103" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AK103" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AL103" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AM103" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AN103" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AO103" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR103" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="AS103" t="n">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="AT103" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AU103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV103" t="n">
         <v>0</v>
       </c>
       <c r="AW103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB103" t="n">
-        <v>-1</v>
+        <v>10708</v>
       </c>
       <c r="BC103" t="n">
         <v>0</v>
       </c>
       <c r="BD103" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE103" t="n">
         <v>0</v>
@@ -49863,70 +49863,70 @@
         <v>-1</v>
       </c>
       <c r="BG103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH103" t="n">
         <v>1</v>
       </c>
       <c r="BI103" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BJ103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BK103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BL103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM103" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BN103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO103" t="n">
         <v>4</v>
       </c>
-      <c r="BO103" t="n">
-        <v>0</v>
-      </c>
       <c r="BP103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR103" t="n">
         <v>4</v>
       </c>
       <c r="BS103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BT103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BU103" t="n">
         <v>1</v>
       </c>
       <c r="BV103" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BW103" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="BX103" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="BY103" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="BZ103" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="CA103" t="n">
-        <v>1.97</v>
+        <v>1.28</v>
       </c>
       <c r="CB103" t="n">
-        <v>3.27</v>
+        <v>1.88</v>
       </c>
       <c r="CC103" t="n">
         <v>0</v>
@@ -49959,10 +49959,10 @@
         <v>0</v>
       </c>
       <c r="CM103" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN103" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CO103" t="n">
         <v>0</v>
@@ -49974,7 +49974,7 @@
         <v>1</v>
       </c>
       <c r="CR103" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="CS103" t="n">
         <v>15</v>
@@ -49983,64 +49983,64 @@
         <v>1</v>
       </c>
       <c r="CU103" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CV103" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CW103" t="n">
         <v>1</v>
       </c>
       <c r="CX103" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CZ103" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>70</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ103" t="n">
         <v>40</v>
       </c>
-      <c r="DA103" t="n">
-        <v>70</v>
-      </c>
-      <c r="DB103" t="n">
-        <v>30</v>
-      </c>
-      <c r="DC103" t="n">
-        <v>40</v>
-      </c>
-      <c r="DD103" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE103" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DF103" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DG103" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DH103" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="DI103" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DJ103" t="n">
-        <v>60</v>
-      </c>
       <c r="DK103" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="DL103" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="DM103" t="n">
-        <v>1.56</v>
+        <v>0.86</v>
       </c>
       <c r="DN103" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="DO103" t="n">
         <v>17</v>
@@ -50052,10 +50052,10 @@
         <v>1</v>
       </c>
       <c r="DR103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT103" t="b">
         <v>0</v>
@@ -50064,17 +50064,17 @@
         <v>0</v>
       </c>
       <c r="DV103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW103" t="n">
-        <v>16.23</v>
+        <v>16.26</v>
       </c>
       <c r="DX103" t="n">
-        <v>6.33</v>
+        <v>5.37</v>
       </c>
       <c r="DY103" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ103" t="inlineStr">
@@ -50084,82 +50084,82 @@
       </c>
       <c r="EA103" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB103" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EC103" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="ED103" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EE103" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EF103" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EG103" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EH103" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI103" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EJ103" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="EK103" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EL103" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM103" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN103" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EO103" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EP103" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.81</t>
         </is>
       </c>
     </row>
@@ -51938,7 +51938,7 @@
         <v>50</v>
       </c>
       <c r="DD107" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE107" t="n">
         <v>1.13</v>
@@ -53825,7 +53825,7 @@
         <v>1.22</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF111" t="n">
         <v>1.17</v>
@@ -55423,146 +55423,138 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L115" t="n">
+        <v>8</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
         <v>4</v>
       </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1</v>
-      </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q115" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T115" t="n">
+        <v>7</v>
+      </c>
+      <c r="U115" t="n">
+        <v>24</v>
+      </c>
+      <c r="V115" t="n">
+        <v>9</v>
+      </c>
+      <c r="W115" t="n">
+        <v>12</v>
+      </c>
+      <c r="X115" t="n">
         <v>14</v>
       </c>
-      <c r="U115" t="n">
-        <v>10</v>
-      </c>
-      <c r="V115" t="n">
-        <v>17</v>
-      </c>
-      <c r="W115" t="n">
-        <v>10</v>
-      </c>
-      <c r="X115" t="n">
-        <v>19</v>
-      </c>
       <c r="Y115" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="Z115" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Complexo Desportivo FC Alverca</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AG115" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AJ115" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL115" t="n">
         <v>1.92</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW115" t="n">
         <v>0</v>
@@ -55571,22 +55563,22 @@
         <v>1</v>
       </c>
       <c r="AY115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB115" t="n">
-        <v>10708</v>
+        <v>15804</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55601,64 +55593,64 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BW115" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="BX115" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="BY115" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="BZ115" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="CA115" t="n">
-        <v>1.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB115" t="n">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
@@ -55691,10 +55683,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55709,70 +55701,70 @@
         <v>21</v>
       </c>
       <c r="CS115" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV115" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
       </c>
       <c r="CX115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY115" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CZ115" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="DA115" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="DB115" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="DC115" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.11</v>
+        <v>0.63</v>
       </c>
       <c r="DF115" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="DG115" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="DH115" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="DI115" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DJ115" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="DK115" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DM115" t="n">
-        <v>1.21</v>
+        <v>0.87</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="DO115" t="n">
         <v>17</v>
@@ -55781,13 +55773,13 @@
         <v>1</v>
       </c>
       <c r="DQ115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT115" t="b">
         <v>0</v>
@@ -55796,17 +55788,17 @@
         <v>0</v>
       </c>
       <c r="DV115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW115" t="n">
-        <v>16.34</v>
+        <v>16.07</v>
       </c>
       <c r="DX115" t="n">
-        <v>5.53</v>
+        <v>5.47</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
@@ -55816,39 +55808,23 @@
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="ED115" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EE115" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EF115" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EG115" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr"/>
+      <c r="EF115" t="inlineStr"/>
+      <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -55856,26 +55832,42 @@
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="EK115" t="inlineStr"/>
-      <c r="EL115" t="inlineStr"/>
-      <c r="EM115" t="inlineStr"/>
-      <c r="EN115" t="inlineStr"/>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EM115" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN115" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
       <c r="EO115" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -55895,138 +55887,146 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" t="n">
         <v>4</v>
       </c>
-      <c r="J116" t="n">
-        <v>5</v>
-      </c>
-      <c r="K116" t="n">
-        <v>3</v>
-      </c>
-      <c r="L116" t="n">
-        <v>8</v>
-      </c>
       <c r="M116" t="n">
         <v>1</v>
       </c>
       <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
         <v>4</v>
       </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>9</v>
-      </c>
       <c r="R116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T116" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U116" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V116" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X116" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y116" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="Z116" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Complexo Desportivo FC Alverca</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
+        </is>
+      </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AG116" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI116" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AJ116" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL116" t="n">
         <v>1.92</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AN116" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AU116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW116" t="n">
         <v>0</v>
@@ -56035,22 +56035,22 @@
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>15804</v>
+        <v>10708</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -56065,64 +56065,64 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR116" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU116" t="n">
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="BW116" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="BX116" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="BY116" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="BZ116" t="n">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="CA116" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="CB116" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
@@ -56155,10 +56155,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -56173,70 +56173,70 @@
         <v>21</v>
       </c>
       <c r="CS116" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CV116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CW116" t="n">
         <v>1</v>
       </c>
       <c r="CX116" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY116" t="n">
         <v>6</v>
       </c>
-      <c r="CY116" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ116" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="DA116" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="DB116" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="DC116" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DD116" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE116" t="n">
         <v>1.11</v>
       </c>
-      <c r="DE116" t="n">
-        <v>0.63</v>
-      </c>
       <c r="DF116" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG116" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="DH116" t="n">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="DI116" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DJ116" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="DK116" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DM116" t="n">
-        <v>0.87</v>
+        <v>1.21</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="DO116" t="n">
         <v>17</v>
@@ -56245,13 +56245,13 @@
         <v>1</v>
       </c>
       <c r="DQ116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT116" t="b">
         <v>0</v>
@@ -56260,17 +56260,17 @@
         <v>0</v>
       </c>
       <c r="DV116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>16.07</v>
+        <v>16.34</v>
       </c>
       <c r="DX116" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
@@ -56280,23 +56280,39 @@
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="ED116" t="inlineStr"/>
-      <c r="EE116" t="inlineStr"/>
-      <c r="EF116" t="inlineStr"/>
-      <c r="EG116" t="inlineStr"/>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
       <c r="EH116" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -56304,42 +56320,26 @@
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="EK116" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="EL116" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EM116" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN116" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr"/>
+      <c r="EL116" t="inlineStr"/>
+      <c r="EM116" t="inlineStr"/>
+      <c r="EN116" t="inlineStr"/>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -58606,7 +58606,7 @@
         <v>67</v>
       </c>
       <c r="DD121" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE121" t="n">
         <v>0.13</v>
@@ -63873,7 +63873,7 @@
         <v>0.63</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF132" t="n">
         <v>0.33</v>
@@ -68654,7 +68654,7 @@
         <v>60</v>
       </c>
       <c r="DD142" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE142" t="n">
         <v>1.22</v>
@@ -72473,7 +72473,7 @@
         <v>1.13</v>
       </c>
       <c r="DE150" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF150" t="n">
         <v>0.86</v>
@@ -74548,6 +74548,470 @@
       <c r="EP154" t="inlineStr">
         <is>
           <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>18</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>46038.84375</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>3</v>
+      </c>
+      <c r="J155" t="n">
+        <v>4</v>
+      </c>
+      <c r="K155" t="n">
+        <v>6</v>
+      </c>
+      <c r="L155" t="n">
+        <v>10</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>2</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>4</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1</v>
+      </c>
+      <c r="S155" t="n">
+        <v>12</v>
+      </c>
+      <c r="T155" t="n">
+        <v>5</v>
+      </c>
+      <c r="U155" t="n">
+        <v>16</v>
+      </c>
+      <c r="V155" t="n">
+        <v>6</v>
+      </c>
+      <c r="W155" t="n">
+        <v>12</v>
+      </c>
+      <c r="X155" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Estádio José Alvalade</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>Rua Professor Fernando da Fonseca, Lisboa</t>
+        </is>
+      </c>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>114</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>35</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV155" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW155" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX155" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY155" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ155" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CA155" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="CB155" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR155" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS155" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU155" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV155" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX155" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY155" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ155" t="n">
+        <v>71</v>
+      </c>
+      <c r="DA155" t="n">
+        <v>95</v>
+      </c>
+      <c r="DB155" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC155" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD155" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DE155" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF155" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DG155" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH155" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DI155" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DJ155" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK155" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL155" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DM155" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DN155" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="DO155" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW155" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="DX155" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="DY155" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ155" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="EA155" t="inlineStr">
+        <is>
+          <t>16.64</t>
+        </is>
+      </c>
+      <c r="EB155" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="EC155" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="ED155" t="inlineStr"/>
+      <c r="EE155" t="inlineStr"/>
+      <c r="EF155" t="inlineStr"/>
+      <c r="EG155" t="inlineStr"/>
+      <c r="EH155" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EI155" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EJ155" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EK155" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EL155" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EM155" t="inlineStr"/>
+      <c r="EN155" t="inlineStr"/>
+      <c r="EO155" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EP155" t="inlineStr">
+        <is>
+          <t>1.61</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP171" headerRowCount="1">
-  <autoFilter ref="A1:EP171"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP172" headerRowCount="1">
+  <autoFilter ref="A1:EP172"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP171"/>
+  <dimension ref="A1:EP172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2293,7 +2293,7 @@
         <v>1.11</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE9" t="n">
         <v>1.11</v>
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -9475,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -11821,7 +11821,7 @@
         <v>1.4</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11851,7 +11851,7 @@
         <v>1.87</v>
       </c>
       <c r="DO23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP23" t="b">
         <v>0</v>
@@ -12298,7 +12298,7 @@
         <v>100</v>
       </c>
       <c r="DD24" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE24" t="n">
         <v>1</v>
@@ -12331,7 +12331,7 @@
         <v>3.21</v>
       </c>
       <c r="DO24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -13771,7 +13771,7 @@
         <v>1.94</v>
       </c>
       <c r="DO27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14375,37 +14375,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
         <v>45899.70833333334</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>4</v>
@@ -14414,7 +14414,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
@@ -14423,122 +14423,122 @@
         <v>3</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y29" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="Z29" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Estádio Dom Afonso Henriques</t>
+          <t>Estádio Clube Desportivo das Aves</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Rua de São Gonçalo 505, Guimarães</t>
+          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.78</v>
+        <v>4.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.15</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AO29" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>-1</v>
+        <v>1033</v>
       </c>
       <c r="BC29" t="n">
         <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
         <v>0</v>
@@ -14547,184 +14547,184 @@
         <v>-1</v>
       </c>
       <c r="BG29" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH29" t="n">
         <v>1</v>
       </c>
       <c r="BI29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BK29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL29" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BN29" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO29" t="n">
         <v>0</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR29" t="n">
         <v>4</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX29" t="n">
         <v>8</v>
       </c>
-      <c r="BU29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>20</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>105</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>61</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="CB29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS29" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU29" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV29" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX29" t="n">
-        <v>9</v>
-      </c>
       <c r="CY29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ29" t="n">
         <v>100</v>
       </c>
-      <c r="DA29" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB29" t="n">
-        <v>100</v>
-      </c>
-      <c r="DC29" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE29" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DF29" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH29" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DJ29" t="n">
-        <v>0</v>
-      </c>
       <c r="DK29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL29" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="DM29" t="n">
-        <v>0.64</v>
+        <v>1.71</v>
       </c>
       <c r="DN29" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="DO29" t="n">
         <v>19</v>
@@ -14733,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="DQ29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR29" t="b">
         <v>0</v>
@@ -14748,13 +14748,13 @@
         <v>0</v>
       </c>
       <c r="DV29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW29" t="n">
-        <v>25.71</v>
+        <v>26.39</v>
       </c>
       <c r="DX29" t="n">
-        <v>5.57</v>
+        <v>5.3</v>
       </c>
       <c r="DY29" t="inlineStr">
         <is>
@@ -14763,32 +14763,32 @@
       </c>
       <c r="DZ29" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="EA29" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EB29" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EC29" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="ED29" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EE29" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EF29" t="inlineStr">
@@ -14798,52 +14798,52 @@
       </c>
       <c r="EG29" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EH29" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI29" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EJ29" t="inlineStr">
+        <is>
+          <t>4.56</t>
+        </is>
+      </c>
+      <c r="EK29" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EL29" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="EI29" t="inlineStr">
+      <c r="EM29" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EN29" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EO29" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="EJ29" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
-      </c>
-      <c r="EK29" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="EL29" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EM29" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN29" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="EO29" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
       <c r="EP29" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -14863,37 +14863,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>45899.70833333334</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -14902,7 +14902,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>3</v>
@@ -14911,122 +14911,122 @@
         <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y30" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Z30" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Estádio Clube Desportivo das Aves</t>
+          <t>Estádio Dom Afonso Henriques</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Rua Luís Gonzaga Mendes de Carvalho 265, Vila das Aves</t>
+          <t>Rua de São Gonçalo 505, Guimarães</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>4.05</v>
+        <v>1.78</v>
       </c>
       <c r="AF30" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.79</v>
+        <v>4.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AO30" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
-        <v>1033</v>
+        <v>-1</v>
       </c>
       <c r="BC30" t="n">
         <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE30" t="n">
         <v>0</v>
@@ -15035,70 +15035,70 @@
         <v>-1</v>
       </c>
       <c r="BG30" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH30" t="n">
         <v>1</v>
       </c>
       <c r="BI30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BK30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL30" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BN30" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO30" t="n">
         <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR30" t="n">
         <v>4</v>
       </c>
       <c r="BS30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BU30" t="n">
         <v>1</v>
       </c>
       <c r="BV30" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="BW30" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="BX30" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="BY30" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="BZ30" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.35</v>
+        <v>0.93</v>
       </c>
       <c r="CB30" t="n">
-        <v>2.69</v>
+        <v>2.12</v>
       </c>
       <c r="CC30" t="n">
         <v>0</v>
@@ -15131,10 +15131,10 @@
         <v>0</v>
       </c>
       <c r="CM30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO30" t="n">
         <v>0</v>
@@ -15146,73 +15146,73 @@
         <v>1</v>
       </c>
       <c r="CR30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CS30" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="CT30" t="n">
         <v>1</v>
       </c>
       <c r="CU30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW30" t="n">
         <v>1</v>
       </c>
       <c r="CX30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CY30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CZ30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DA30" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DC30" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.67</v>
+        <v>0.89</v>
       </c>
       <c r="DF30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH30" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DI30" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="DJ30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK30" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL30" t="n">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="DM30" t="n">
-        <v>1.71</v>
+        <v>0.64</v>
       </c>
       <c r="DN30" t="n">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="DO30" t="n">
         <v>19</v>
@@ -15221,7 +15221,7 @@
         <v>1</v>
       </c>
       <c r="DQ30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR30" t="b">
         <v>0</v>
@@ -15236,13 +15236,13 @@
         <v>0</v>
       </c>
       <c r="DV30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW30" t="n">
-        <v>26.39</v>
+        <v>25.71</v>
       </c>
       <c r="DX30" t="n">
-        <v>5.3</v>
+        <v>5.57</v>
       </c>
       <c r="DY30" t="inlineStr">
         <is>
@@ -15251,32 +15251,32 @@
       </c>
       <c r="DZ30" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="EA30" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EB30" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EC30" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="ED30" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EE30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EF30" t="inlineStr">
@@ -15286,52 +15286,52 @@
       </c>
       <c r="EG30" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EH30" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EI30" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ30" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EK30" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EL30" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EM30" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EN30" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EO30" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EP30" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -15703,7 +15703,7 @@
         <v>3.82</v>
       </c>
       <c r="DO31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -19159,12 +19159,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -19180,19 +19180,19 @@
         <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -19201,122 +19201,122 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
         <v>4</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
       </c>
       <c r="V39" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y39" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Z39" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
+          <t>Estádio António Coimbra da Mota</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
+          <t>Rua Dom Bosco, Estoril</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.25</v>
+        <v>4.42</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AJ39" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AR39" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU39" t="n">
         <v>4</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW39" t="n">
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY39" t="n">
         <v>1</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB39" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
@@ -19337,64 +19337,64 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM39" t="n">
         <v>2</v>
       </c>
       <c r="BN39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BO39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BP39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BT39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BW39" t="n">
         <v>39</v>
       </c>
       <c r="BX39" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BY39" t="n">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="CB39" t="n">
-        <v>3.32</v>
+        <v>2.82</v>
       </c>
       <c r="CC39" t="n">
         <v>0</v>
@@ -19442,34 +19442,34 @@
         <v>1</v>
       </c>
       <c r="CR39" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CS39" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CV39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW39" t="n">
         <v>1</v>
       </c>
       <c r="CX39" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="CY39" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ39" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA39" t="n">
         <v>75</v>
-      </c>
-      <c r="DA39" t="n">
-        <v>100</v>
       </c>
       <c r="DB39" t="n">
         <v>25</v>
@@ -19478,37 +19478,37 @@
         <v>75</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.1</v>
+        <v>0.22</v>
       </c>
       <c r="DF39" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DG39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DH39" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="DI39" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="DJ39" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK39" t="n">
         <v>25</v>
       </c>
-      <c r="DK39" t="n">
-        <v>0</v>
-      </c>
       <c r="DL39" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="DM39" t="n">
-        <v>1.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DN39" t="n">
-        <v>2.79</v>
+        <v>2.26</v>
       </c>
       <c r="DO39" t="n">
         <v>19</v>
@@ -19535,99 +19535,83 @@
         <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>22.33</v>
+        <v>20.1</v>
       </c>
       <c r="DX39" t="n">
-        <v>8.09</v>
+        <v>9.27</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="ED39" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EE39" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EF39" t="inlineStr">
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="ED39" t="inlineStr"/>
+      <c r="EE39" t="inlineStr"/>
+      <c r="EF39" t="inlineStr"/>
+      <c r="EG39" t="inlineStr"/>
+      <c r="EH39" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI39" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="EG39" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EH39" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EI39" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -19647,12 +19631,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -19668,19 +19652,19 @@
         <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -19689,122 +19673,122 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R40" t="n">
         <v>4</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U40" t="n">
         <v>15</v>
       </c>
       <c r="V40" t="n">
+        <v>15</v>
+      </c>
+      <c r="W40" t="n">
         <v>12</v>
       </c>
-      <c r="W40" t="n">
-        <v>11</v>
-      </c>
       <c r="X40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y40" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Z40" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Estádio António Coimbra da Mota</t>
+          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Rua Dom Bosco, Estoril</t>
+          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.42</v>
+        <v>3.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AI40" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU40" t="n">
         <v>4</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY40" t="n">
         <v>1</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
@@ -19825,64 +19809,64 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM40" t="n">
         <v>2</v>
       </c>
       <c r="BN40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BO40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BP40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BT40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BW40" t="n">
         <v>39</v>
       </c>
       <c r="BX40" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BY40" t="n">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="CB40" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="CC40" t="n">
         <v>0</v>
@@ -19930,34 +19914,34 @@
         <v>1</v>
       </c>
       <c r="CR40" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS40" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU40" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX40" t="n">
         <v>10</v>
       </c>
-      <c r="CS40" t="n">
-        <v>31</v>
-      </c>
-      <c r="CT40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU40" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV40" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX40" t="n">
-        <v>17</v>
-      </c>
       <c r="CY40" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CZ40" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DA40" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB40" t="n">
         <v>25</v>
@@ -19966,37 +19950,37 @@
         <v>75</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.22</v>
+        <v>1.1</v>
       </c>
       <c r="DF40" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DG40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DH40" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="DI40" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="DJ40" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK40" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL40" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="DM40" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="DN40" t="n">
-        <v>2.26</v>
+        <v>2.79</v>
       </c>
       <c r="DO40" t="n">
         <v>19</v>
@@ -20023,83 +20007,99 @@
         <v>1</v>
       </c>
       <c r="DW40" t="n">
-        <v>20.1</v>
+        <v>22.33</v>
       </c>
       <c r="DX40" t="n">
-        <v>9.27</v>
+        <v>8.09</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="ED40" t="inlineStr"/>
-      <c r="EE40" t="inlineStr"/>
-      <c r="EF40" t="inlineStr"/>
-      <c r="EG40" t="inlineStr"/>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="ED40" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EE40" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EF40" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG40" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
     </row>
@@ -20438,7 +20438,7 @@
         <v>100</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE41" t="n">
         <v>1</v>
@@ -20471,7 +20471,7 @@
         <v>3.36</v>
       </c>
       <c r="DO41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -22301,7 +22301,7 @@
         <v>1.89</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF45" t="n">
         <v>2</v>
@@ -22331,7 +22331,7 @@
         <v>3.35</v>
       </c>
       <c r="DO45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22819,7 +22819,7 @@
         <v>2.94</v>
       </c>
       <c r="DO46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -25715,7 +25715,7 @@
         <v>3.03</v>
       </c>
       <c r="DO52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -27581,7 +27581,7 @@
         <v>2.2</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF56" t="n">
         <v>1.67</v>
@@ -27611,7 +27611,7 @@
         <v>3.98</v>
       </c>
       <c r="DO56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -31435,7 +31435,7 @@
         <v>2.94</v>
       </c>
       <c r="DO64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32015,170 +32015,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="n">
         <v>5</v>
       </c>
-      <c r="J66" t="n">
-        <v>2</v>
-      </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L66" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
         <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>7</v>
       </c>
       <c r="R66" t="n">
+        <v>5</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8</v>
+      </c>
+      <c r="T66" t="n">
+        <v>10</v>
+      </c>
+      <c r="U66" t="n">
+        <v>15</v>
+      </c>
+      <c r="V66" t="n">
+        <v>15</v>
+      </c>
+      <c r="W66" t="n">
+        <v>13</v>
+      </c>
+      <c r="X66" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Estádio Cidade de Barcelos</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>strada Nacional 103, Vila Boa, Barcelos</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
         <v>4</v>
       </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="n">
-        <v>6</v>
-      </c>
-      <c r="U66" t="n">
-        <v>17</v>
-      </c>
-      <c r="V66" t="n">
-        <v>10</v>
-      </c>
-      <c r="W66" t="n">
-        <v>12</v>
-      </c>
-      <c r="X66" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Estádio da Madeira</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
-        </is>
-      </c>
-      <c r="AC66" t="n">
-        <v>1</v>
-      </c>
       <c r="AD66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="AF66" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AG66" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AI66" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ66" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AN66" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AO66" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AR66" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AU66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
         <v>2</v>
       </c>
       <c r="BB66" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32193,73 +32193,73 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM66" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT66" t="n">
         <v>4</v>
       </c>
-      <c r="BN66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT66" t="n">
-        <v>3</v>
-      </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BW66" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="BX66" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="BY66" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BZ66" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="CB66" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="CC66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD66" t="n">
         <v>0</v>
       </c>
       <c r="CE66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF66" t="n">
         <v>0</v>
@@ -32280,10 +32280,10 @@
         <v>0</v>
       </c>
       <c r="CL66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN66" t="n">
         <v>0</v>
@@ -32298,73 +32298,73 @@
         <v>1</v>
       </c>
       <c r="CR66" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS66" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
       </c>
       <c r="CX66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY66" t="n">
         <v>8</v>
       </c>
       <c r="CZ66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA66" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DB66" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="n">
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DF66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DG66" t="n">
         <v>1</v>
       </c>
       <c r="DH66" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="DI66" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="DJ66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK66" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="DN66" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="DO66" t="n">
         <v>19</v>
@@ -32376,114 +32376,114 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU66" t="b">
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>24.96</v>
+        <v>25.52</v>
       </c>
       <c r="DX66" t="n">
-        <v>6.88</v>
+        <v>6.19</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EH66" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI66" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ66" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EK66" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EL66" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EM66" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN66" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EO66" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP66" t="inlineStr">
+        <is>
           <t>1.72</t>
-        </is>
-      </c>
-      <c r="EH66" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI66" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ66" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="EK66" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="EL66" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EM66" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EN66" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EO66" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EP66" t="inlineStr">
-        <is>
-          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -32503,170 +32503,170 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45934.60416666666</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>7</v>
       </c>
       <c r="R67" t="n">
+        <v>4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="n">
+        <v>6</v>
+      </c>
+      <c r="U67" t="n">
+        <v>17</v>
+      </c>
+      <c r="V67" t="n">
+        <v>10</v>
+      </c>
+      <c r="W67" t="n">
+        <v>12</v>
+      </c>
+      <c r="X67" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Estádio da Madeira</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Rua do Esmeraldo, nº 46, Ilha da Madeira</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="n">
         <v>5</v>
       </c>
-      <c r="S67" t="n">
-        <v>8</v>
-      </c>
-      <c r="T67" t="n">
-        <v>10</v>
-      </c>
-      <c r="U67" t="n">
-        <v>15</v>
-      </c>
-      <c r="V67" t="n">
-        <v>15</v>
-      </c>
-      <c r="W67" t="n">
-        <v>13</v>
-      </c>
-      <c r="X67" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Estádio Cidade de Barcelos</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>strada Nacional 103, Vila Boa, Barcelos</t>
-        </is>
-      </c>
-      <c r="AC67" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>3</v>
-      </c>
       <c r="AE67" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="AF67" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AG67" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI67" t="n">
         <v>2.25</v>
       </c>
       <c r="AJ67" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AK67" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AL67" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AN67" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AO67" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR67" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AS67" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AU67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
       </c>
       <c r="BB67" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32681,181 +32681,181 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM67" t="n">
         <v>4</v>
       </c>
-      <c r="BJ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL67" t="n">
+      <c r="BN67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC67" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE67" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX67" t="n">
         <v>6</v>
-      </c>
-      <c r="BM67" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN67" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ67" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT67" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV67" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW67" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX67" t="n">
-        <v>83</v>
-      </c>
-      <c r="BY67" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ67" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA67" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CB67" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CC67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR67" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS67" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU67" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV67" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX67" t="n">
-        <v>8</v>
       </c>
       <c r="CY67" t="n">
         <v>8</v>
       </c>
       <c r="CZ67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA67" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DB67" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DC67" t="n">
         <v>50</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="DE67" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DF67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DG67" t="n">
         <v>1</v>
       </c>
       <c r="DH67" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="DI67" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DJ67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK67" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="DM67" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="DN67" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="DO67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32864,69 +32864,69 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU67" t="b">
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW67" t="n">
-        <v>25.52</v>
+        <v>24.96</v>
       </c>
       <c r="DX67" t="n">
-        <v>6.19</v>
+        <v>6.88</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EA67" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EB67" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EC67" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="ED67" t="inlineStr">
         <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EE67" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF67" t="inlineStr">
+        <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="EE67" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="EF67" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
@@ -32936,42 +32936,42 @@
       </c>
       <c r="EI67" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EJ67" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="EK67" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EL67" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM67" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EN67" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EO67" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EP67" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -35682,7 +35682,7 @@
         <v>84</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE73" t="n">
         <v>2.56</v>
@@ -35715,7 +35715,7 @@
         <v>3.37</v>
       </c>
       <c r="DO73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -36173,7 +36173,7 @@
         <v>1.6</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF74" t="n">
         <v>1.5</v>
@@ -36203,7 +36203,7 @@
         <v>2.87</v>
       </c>
       <c r="DO74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36811,76 +36811,76 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45955.8125</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>8</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>9</v>
+      </c>
+      <c r="T76" t="n">
         <v>5</v>
       </c>
-      <c r="L76" t="n">
-        <v>9</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2</v>
-      </c>
-      <c r="N76" t="n">
+      <c r="U76" t="n">
+        <v>17</v>
+      </c>
+      <c r="V76" t="n">
         <v>5</v>
       </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>2</v>
-      </c>
-      <c r="R76" t="n">
-        <v>2</v>
-      </c>
-      <c r="S76" t="n">
-        <v>14</v>
-      </c>
-      <c r="T76" t="n">
-        <v>6</v>
-      </c>
-      <c r="U76" t="n">
-        <v>16</v>
-      </c>
-      <c r="V76" t="n">
-        <v>8</v>
-      </c>
       <c r="W76" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X76" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y76" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Z76" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
@@ -36888,85 +36888,85 @@
         <v>2</v>
       </c>
       <c r="AD76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AU76" t="n">
         <v>5</v>
       </c>
-      <c r="AE76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU76" t="n">
-        <v>3</v>
-      </c>
       <c r="AV76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW76" t="n">
         <v>0</v>
       </c>
       <c r="AX76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
         <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB76" t="n">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36981,178 +36981,178 @@
         <v>1</v>
       </c>
       <c r="BI76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BM76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN76" t="n">
         <v>6</v>
       </c>
       <c r="BO76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP76" t="n">
         <v>1</v>
       </c>
       <c r="BQ76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
         <v>5</v>
       </c>
-      <c r="BU76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV76" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW76" t="n">
-        <v>28</v>
-      </c>
-      <c r="BX76" t="n">
-        <v>94</v>
-      </c>
-      <c r="BY76" t="n">
-        <v>63</v>
-      </c>
-      <c r="BZ76" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CA76" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="CB76" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS76" t="n">
-        <v>24</v>
-      </c>
-      <c r="CT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU76" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV76" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX76" t="n">
-        <v>7</v>
-      </c>
       <c r="CY76" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CZ76" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DA76" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB76" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="DC76" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="DD76" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.1</v>
+        <v>0.89</v>
       </c>
       <c r="DF76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DG76" t="n">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="DH76" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL76" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DM76" t="n">
         <v>0.88</v>
       </c>
-      <c r="DI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ76" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK76" t="n">
-        <v>25</v>
-      </c>
-      <c r="DL76" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DM76" t="n">
-        <v>1.1</v>
-      </c>
       <c r="DN76" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="DO76" t="n">
         <v>19</v>
@@ -37167,111 +37167,103 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU76" t="b">
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW76" t="n">
-        <v>21.83</v>
+        <v>22.85</v>
       </c>
       <c r="DX76" t="n">
-        <v>4.62</v>
+        <v>4.75</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>13.66</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EG76" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EH76" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EI76" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ76" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EK76" t="inlineStr">
+        <is>
           <t>2.12</t>
         </is>
       </c>
-      <c r="EJ76" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="EK76" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
-      </c>
       <c r="EL76" t="inlineStr">
         <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EM76" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN76" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EM76" t="inlineStr"/>
+      <c r="EN76" t="inlineStr"/>
       <c r="EO76" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EP76" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.77</t>
         </is>
       </c>
     </row>
@@ -37291,41 +37283,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
         <v>45955.8125</v>
       </c>
       <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4</v>
+      </c>
+      <c r="K77" t="n">
         <v>5</v>
       </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
+      <c r="L77" t="n">
+        <v>9</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" t="n">
         <v>5</v>
       </c>
-      <c r="J77" t="n">
-        <v>9</v>
-      </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" t="n">
-        <v>10</v>
-      </c>
-      <c r="M77" t="n">
-        <v>2</v>
-      </c>
-      <c r="N77" t="n">
-        <v>2</v>
-      </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
@@ -37333,34 +37325,34 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
+        <v>2</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2</v>
+      </c>
+      <c r="S77" t="n">
+        <v>14</v>
+      </c>
+      <c r="T77" t="n">
+        <v>6</v>
+      </c>
+      <c r="U77" t="n">
+        <v>16</v>
+      </c>
+      <c r="V77" t="n">
         <v>8</v>
       </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>9</v>
-      </c>
-      <c r="T77" t="n">
-        <v>5</v>
-      </c>
-      <c r="U77" t="n">
-        <v>17</v>
-      </c>
-      <c r="V77" t="n">
-        <v>5</v>
-      </c>
       <c r="W77" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X77" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y77" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Z77" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
@@ -37368,85 +37360,85 @@
         <v>2</v>
       </c>
       <c r="AD77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="AF77" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="AG77" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="AJ77" t="n">
-        <v>2.08</v>
+        <v>3.54</v>
       </c>
       <c r="AK77" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL77" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AM77" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AN77" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AO77" t="n">
-        <v>2.41</v>
+        <v>2.19</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AR77" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AS77" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="AT77" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AU77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW77" t="n">
         <v>0</v>
       </c>
       <c r="AX77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ77" t="n">
         <v>2</v>
       </c>
       <c r="BA77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB77" t="n">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="BC77" t="n">
         <v>0</v>
       </c>
       <c r="BD77" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="BE77" t="n">
         <v>0</v>
@@ -37461,73 +37453,73 @@
         <v>1</v>
       </c>
       <c r="BI77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN77" t="n">
         <v>6</v>
       </c>
       <c r="BO77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP77" t="n">
         <v>1</v>
       </c>
       <c r="BQ77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU77" t="n">
         <v>1</v>
       </c>
       <c r="BV77" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="BW77" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="BX77" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="BY77" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="BZ77" t="n">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="CA77" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="CB77" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="CC77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD77" t="n">
         <v>0</v>
       </c>
       <c r="CE77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF77" t="n">
         <v>0</v>
@@ -37545,13 +37537,13 @@
         <v>1</v>
       </c>
       <c r="CK77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL77" t="n">
         <v>0</v>
       </c>
       <c r="CM77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
@@ -37560,79 +37552,79 @@
         <v>0</v>
       </c>
       <c r="CP77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ77" t="n">
         <v>1</v>
       </c>
       <c r="CR77" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="CS77" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CT77" t="n">
         <v>1</v>
       </c>
       <c r="CU77" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY77" t="n">
         <v>15</v>
       </c>
-      <c r="CV77" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX77" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY77" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ77" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DA77" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB77" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="DC77" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DD77" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DG77" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DH77" t="n">
-        <v>2.25</v>
+        <v>0.88</v>
       </c>
       <c r="DI77" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DJ77" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DK77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL77" t="n">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="DM77" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="DN77" t="n">
-        <v>3.06</v>
+        <v>2.46</v>
       </c>
       <c r="DO77" t="n">
         <v>19</v>
@@ -37647,103 +37639,111 @@
         <v>1</v>
       </c>
       <c r="DS77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU77" t="b">
         <v>0</v>
       </c>
       <c r="DV77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW77" t="n">
-        <v>22.85</v>
+        <v>21.83</v>
       </c>
       <c r="DX77" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>13.66</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="EC77" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EF77" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EG77" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EH77" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI77" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EJ77" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="EK77" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EL77" t="inlineStr">
         <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="EM77" t="inlineStr"/>
-      <c r="EN77" t="inlineStr"/>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EM77" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN77" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
       <c r="EO77" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EP77" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -40043,7 +40043,7 @@
         <v>3.06</v>
       </c>
       <c r="DO82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -43870,7 +43870,7 @@
         <v>88</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE90" t="n">
         <v>1.6</v>
@@ -43903,7 +43903,7 @@
         <v>3.54</v>
       </c>
       <c r="DO90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44391,7 +44391,7 @@
         <v>2.73</v>
       </c>
       <c r="DO91" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -46721,7 +46721,7 @@
         <v>0.3</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF96" t="n">
         <v>0.2</v>
@@ -46751,7 +46751,7 @@
         <v>2.63</v>
       </c>
       <c r="DO96" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47667,7 +47667,7 @@
         <v>3.3</v>
       </c>
       <c r="DO98" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -49203,40 +49203,40 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
         <v>45990.64583333334</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
         <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K102" t="n">
         <v>4</v>
       </c>
       <c r="L102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
@@ -49245,128 +49245,128 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
       </c>
       <c r="T102" t="n">
+        <v>9</v>
+      </c>
+      <c r="U102" t="n">
+        <v>11</v>
+      </c>
+      <c r="V102" t="n">
+        <v>17</v>
+      </c>
+      <c r="W102" t="n">
+        <v>17</v>
+      </c>
+      <c r="X102" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
+        </is>
+      </c>
+      <c r="AC102" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD102" t="n">
         <v>5</v>
       </c>
-      <c r="U102" t="n">
-        <v>5</v>
-      </c>
-      <c r="V102" t="n">
-        <v>10</v>
-      </c>
-      <c r="W102" t="n">
-        <v>9</v>
-      </c>
-      <c r="X102" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>Campo do Cevadeiro</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>Estrada Nacional 10, Vila Franca de Xira</t>
-        </is>
-      </c>
-      <c r="AC102" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD102" t="n">
+      <c r="AE102" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU102" t="n">
         <v>4</v>
       </c>
-      <c r="AE102" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH102" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI102" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AK102" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL102" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO102" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AP102" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AQ102" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR102" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS102" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT102" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AU102" t="n">
-        <v>2</v>
-      </c>
       <c r="AV102" t="n">
         <v>0</v>
       </c>
       <c r="AW102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB102" t="n">
-        <v>10708</v>
+        <v>-1</v>
       </c>
       <c r="BC102" t="n">
         <v>0</v>
       </c>
       <c r="BD102" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE102" t="n">
         <v>0</v>
@@ -49375,70 +49375,70 @@
         <v>-1</v>
       </c>
       <c r="BG102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH102" t="n">
         <v>1</v>
       </c>
       <c r="BI102" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BK102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BL102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM102" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BN102" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ102" t="n">
         <v>4</v>
-      </c>
-      <c r="BP102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ102" t="n">
-        <v>1</v>
       </c>
       <c r="BR102" t="n">
         <v>4</v>
       </c>
       <c r="BS102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BT102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BU102" t="n">
         <v>1</v>
       </c>
       <c r="BV102" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BW102" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="BX102" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="BY102" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BZ102" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="CA102" t="n">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="CB102" t="n">
-        <v>1.88</v>
+        <v>3.27</v>
       </c>
       <c r="CC102" t="n">
         <v>0</v>
@@ -49471,10 +49471,10 @@
         <v>0</v>
       </c>
       <c r="CM102" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN102" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CO102" t="n">
         <v>0</v>
@@ -49486,7 +49486,7 @@
         <v>1</v>
       </c>
       <c r="CR102" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="CS102" t="n">
         <v>15</v>
@@ -49495,64 +49495,64 @@
         <v>1</v>
       </c>
       <c r="CU102" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV102" t="n">
         <v>17</v>
       </c>
-      <c r="CV102" t="n">
-        <v>9</v>
-      </c>
       <c r="CW102" t="n">
         <v>1</v>
       </c>
       <c r="CX102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CZ102" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB102" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC102" t="n">
+        <v>40</v>
+      </c>
+      <c r="DD102" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE102" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF102" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG102" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DH102" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DI102" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DJ102" t="n">
         <v>60</v>
       </c>
-      <c r="DA102" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB102" t="n">
-        <v>70</v>
-      </c>
-      <c r="DC102" t="n">
-        <v>80</v>
-      </c>
-      <c r="DD102" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="DE102" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DF102" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DG102" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DH102" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DI102" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ102" t="n">
-        <v>40</v>
-      </c>
       <c r="DK102" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DL102" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="DM102" t="n">
-        <v>0.86</v>
+        <v>1.56</v>
       </c>
       <c r="DN102" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="DO102" t="n">
         <v>19</v>
@@ -49564,10 +49564,10 @@
         <v>1</v>
       </c>
       <c r="DR102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT102" t="b">
         <v>0</v>
@@ -49576,17 +49576,17 @@
         <v>0</v>
       </c>
       <c r="DV102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW102" t="n">
-        <v>16.26</v>
+        <v>16.23</v>
       </c>
       <c r="DX102" t="n">
-        <v>5.37</v>
+        <v>6.33</v>
       </c>
       <c r="DY102" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="DZ102" t="inlineStr">
@@ -49596,82 +49596,82 @@
       </c>
       <c r="EA102" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EB102" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EC102" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="ED102" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EE102" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EF102" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EG102" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EH102" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI102" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EJ102" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="EK102" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="EL102" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EM102" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EN102" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EO102" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EP102" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -49691,170 +49691,170 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
         <v>45990.64583333334</v>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
         <v>2</v>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K103" t="n">
         <v>4</v>
       </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N103" t="n">
+        <v>4</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
         <v>5</v>
-      </c>
-      <c r="O103" t="n">
-        <v>1</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>6</v>
-      </c>
-      <c r="R103" t="n">
-        <v>8</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
       </c>
       <c r="T103" t="n">
+        <v>5</v>
+      </c>
+      <c r="U103" t="n">
+        <v>5</v>
+      </c>
+      <c r="V103" t="n">
+        <v>10</v>
+      </c>
+      <c r="W103" t="n">
         <v>9</v>
       </c>
-      <c r="U103" t="n">
-        <v>11</v>
-      </c>
-      <c r="V103" t="n">
+      <c r="X103" t="n">
         <v>17</v>
       </c>
-      <c r="W103" t="n">
-        <v>17</v>
-      </c>
-      <c r="X103" t="n">
-        <v>22</v>
-      </c>
       <c r="Y103" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z103" t="n">
         <v>48</v>
       </c>
-      <c r="Z103" t="n">
-        <v>52</v>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Parque Desportivo Comendador Joaquim de Almeida Freitas</t>
+          <t>Campo do Cevadeiro</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>Avenida Comendador Joaquim de Almeida Freitas, Moreira de Cónegos</t>
+          <t>Estrada Nacional 10, Vila Franca de Xira</t>
         </is>
       </c>
       <c r="AC103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD103" t="n">
         <v>4</v>
       </c>
-      <c r="AD103" t="n">
-        <v>5</v>
-      </c>
       <c r="AE103" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="AF103" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AI103" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AJ103" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AK103" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AL103" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AM103" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AN103" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AO103" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AR103" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="AS103" t="n">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="AT103" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AU103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV103" t="n">
         <v>0</v>
       </c>
       <c r="AW103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB103" t="n">
-        <v>-1</v>
+        <v>10708</v>
       </c>
       <c r="BC103" t="n">
         <v>0</v>
       </c>
       <c r="BD103" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE103" t="n">
         <v>0</v>
@@ -49863,70 +49863,70 @@
         <v>-1</v>
       </c>
       <c r="BG103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH103" t="n">
         <v>1</v>
       </c>
       <c r="BI103" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BJ103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BK103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BL103" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM103" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BN103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO103" t="n">
         <v>4</v>
       </c>
-      <c r="BO103" t="n">
-        <v>0</v>
-      </c>
       <c r="BP103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR103" t="n">
         <v>4</v>
       </c>
       <c r="BS103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BT103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BU103" t="n">
         <v>1</v>
       </c>
       <c r="BV103" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BW103" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="BX103" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="BY103" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="BZ103" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="CA103" t="n">
-        <v>1.97</v>
+        <v>1.28</v>
       </c>
       <c r="CB103" t="n">
-        <v>3.27</v>
+        <v>1.88</v>
       </c>
       <c r="CC103" t="n">
         <v>0</v>
@@ -49959,10 +49959,10 @@
         <v>0</v>
       </c>
       <c r="CM103" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN103" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CO103" t="n">
         <v>0</v>
@@ -49974,7 +49974,7 @@
         <v>1</v>
       </c>
       <c r="CR103" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="CS103" t="n">
         <v>15</v>
@@ -49983,64 +49983,64 @@
         <v>1</v>
       </c>
       <c r="CU103" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CV103" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CW103" t="n">
         <v>1</v>
       </c>
       <c r="CX103" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CZ103" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>70</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ103" t="n">
         <v>40</v>
       </c>
-      <c r="DA103" t="n">
-        <v>70</v>
-      </c>
-      <c r="DB103" t="n">
-        <v>30</v>
-      </c>
-      <c r="DC103" t="n">
-        <v>40</v>
-      </c>
-      <c r="DD103" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE103" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF103" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DG103" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DH103" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="DI103" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DJ103" t="n">
-        <v>60</v>
-      </c>
       <c r="DK103" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="DL103" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="DM103" t="n">
-        <v>1.56</v>
+        <v>0.86</v>
       </c>
       <c r="DN103" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="DO103" t="n">
         <v>19</v>
@@ -50052,10 +50052,10 @@
         <v>1</v>
       </c>
       <c r="DR103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT103" t="b">
         <v>0</v>
@@ -50064,17 +50064,17 @@
         <v>0</v>
       </c>
       <c r="DV103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW103" t="n">
-        <v>16.23</v>
+        <v>16.26</v>
       </c>
       <c r="DX103" t="n">
-        <v>6.33</v>
+        <v>5.37</v>
       </c>
       <c r="DY103" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ103" t="inlineStr">
@@ -50084,82 +50084,82 @@
       </c>
       <c r="EA103" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EB103" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EC103" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="ED103" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EE103" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EF103" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EG103" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EH103" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI103" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EJ103" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="EK103" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EL103" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EM103" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EN103" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EO103" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EP103" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.81</t>
         </is>
       </c>
     </row>
@@ -51003,7 +51003,7 @@
         <v>2.67</v>
       </c>
       <c r="DO105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -52410,7 +52410,7 @@
         <v>90</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE108" t="n">
         <v>0.89</v>
@@ -52443,7 +52443,7 @@
         <v>3.13</v>
       </c>
       <c r="DO108" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -55423,146 +55423,138 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L115" t="n">
+        <v>8</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
         <v>4</v>
       </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1</v>
-      </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q115" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T115" t="n">
+        <v>7</v>
+      </c>
+      <c r="U115" t="n">
+        <v>24</v>
+      </c>
+      <c r="V115" t="n">
+        <v>9</v>
+      </c>
+      <c r="W115" t="n">
+        <v>12</v>
+      </c>
+      <c r="X115" t="n">
         <v>14</v>
       </c>
-      <c r="U115" t="n">
-        <v>10</v>
-      </c>
-      <c r="V115" t="n">
-        <v>17</v>
-      </c>
-      <c r="W115" t="n">
-        <v>10</v>
-      </c>
-      <c r="X115" t="n">
-        <v>19</v>
-      </c>
       <c r="Y115" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="Z115" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Complexo Desportivo FC Alverca</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE115" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AG115" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AJ115" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL115" t="n">
         <v>1.92</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW115" t="n">
         <v>0</v>
@@ -55571,22 +55563,22 @@
         <v>1</v>
       </c>
       <c r="AY115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB115" t="n">
-        <v>10708</v>
+        <v>15804</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55601,64 +55593,64 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="BW115" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="BX115" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="BY115" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="BZ115" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="CA115" t="n">
-        <v>1.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB115" t="n">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
@@ -55691,10 +55683,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55709,70 +55701,70 @@
         <v>21</v>
       </c>
       <c r="CS115" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV115" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
       </c>
       <c r="CX115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY115" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="CZ115" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="DA115" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="DB115" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="DC115" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="DE115" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF115" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="DG115" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="DH115" t="n">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="DI115" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DJ115" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="DK115" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DM115" t="n">
-        <v>1.21</v>
+        <v>0.87</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="DO115" t="n">
         <v>19</v>
@@ -55781,13 +55773,13 @@
         <v>1</v>
       </c>
       <c r="DQ115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT115" t="b">
         <v>0</v>
@@ -55796,17 +55788,17 @@
         <v>0</v>
       </c>
       <c r="DV115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW115" t="n">
-        <v>16.34</v>
+        <v>16.07</v>
       </c>
       <c r="DX115" t="n">
-        <v>5.53</v>
+        <v>5.47</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
@@ -55816,39 +55808,23 @@
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="ED115" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="EE115" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EF115" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EG115" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr"/>
+      <c r="EF115" t="inlineStr"/>
+      <c r="EG115" t="inlineStr"/>
       <c r="EH115" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -55856,26 +55832,42 @@
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="EK115" t="inlineStr"/>
-      <c r="EL115" t="inlineStr"/>
-      <c r="EM115" t="inlineStr"/>
-      <c r="EN115" t="inlineStr"/>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EM115" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN115" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
       <c r="EO115" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.96</t>
         </is>
       </c>
     </row>
@@ -55895,138 +55887,146 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45998.75</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" t="n">
         <v>4</v>
       </c>
-      <c r="J116" t="n">
-        <v>5</v>
-      </c>
-      <c r="K116" t="n">
-        <v>3</v>
-      </c>
-      <c r="L116" t="n">
-        <v>8</v>
-      </c>
       <c r="M116" t="n">
         <v>1</v>
       </c>
       <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
         <v>4</v>
       </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>9</v>
-      </c>
       <c r="R116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T116" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U116" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="V116" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X116" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Y116" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="Z116" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Complexo Desportivo FC Alverca</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>R. César Augusto Gonçalves Ferreira 16, Alverca do Ribatejo</t>
+        </is>
+      </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AG116" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI116" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AJ116" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL116" t="n">
         <v>1.92</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AN116" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR116" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AU116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW116" t="n">
         <v>0</v>
@@ -56035,22 +56035,22 @@
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>15804</v>
+        <v>10708</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -56065,64 +56065,64 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR116" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU116" t="n">
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="BW116" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="BX116" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="BY116" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="BZ116" t="n">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="CA116" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="CB116" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
@@ -56155,10 +56155,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -56173,70 +56173,70 @@
         <v>21</v>
       </c>
       <c r="CS116" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CV116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CW116" t="n">
         <v>1</v>
       </c>
       <c r="CX116" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY116" t="n">
         <v>6</v>
       </c>
-      <c r="CY116" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ116" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="DA116" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="DB116" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="DC116" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="DD116" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DF116" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG116" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="DH116" t="n">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="DI116" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DJ116" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="DK116" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DM116" t="n">
-        <v>0.87</v>
+        <v>1.21</v>
       </c>
       <c r="DN116" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="DO116" t="n">
         <v>19</v>
@@ -56245,13 +56245,13 @@
         <v>1</v>
       </c>
       <c r="DQ116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT116" t="b">
         <v>0</v>
@@ -56260,17 +56260,17 @@
         <v>0</v>
       </c>
       <c r="DV116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW116" t="n">
-        <v>16.07</v>
+        <v>16.34</v>
       </c>
       <c r="DX116" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
@@ -56280,23 +56280,39 @@
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="ED116" t="inlineStr"/>
-      <c r="EE116" t="inlineStr"/>
-      <c r="EF116" t="inlineStr"/>
-      <c r="EG116" t="inlineStr"/>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
       <c r="EH116" t="inlineStr">
         <is>
           <t>1.38</t>
@@ -56304,42 +56320,26 @@
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="EK116" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="EL116" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EM116" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN116" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr"/>
+      <c r="EL116" t="inlineStr"/>
+      <c r="EM116" t="inlineStr"/>
+      <c r="EN116" t="inlineStr"/>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -56711,7 +56711,7 @@
         <v>3.31</v>
       </c>
       <c r="DO117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -57169,7 +57169,7 @@
         <v>1.5</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF118" t="n">
         <v>1.83</v>
@@ -57199,7 +57199,7 @@
         <v>2.85</v>
       </c>
       <c r="DO118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP118" t="b">
         <v>0</v>
@@ -57649,7 +57649,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF119" t="n">
         <v>0.33</v>
@@ -57679,7 +57679,7 @@
         <v>2.43</v>
       </c>
       <c r="DO119" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -61470,7 +61470,7 @@
         <v>75</v>
       </c>
       <c r="DD127" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE127" t="n">
         <v>1</v>
@@ -61503,7 +61503,7 @@
         <v>2.55</v>
       </c>
       <c r="DO127" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -62463,7 +62463,7 @@
         <v>2.67</v>
       </c>
       <c r="DO129" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -64871,7 +64871,7 @@
         <v>3.06</v>
       </c>
       <c r="DO134" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -67257,7 +67257,7 @@
         <v>0.9</v>
       </c>
       <c r="DE139" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DF139" t="n">
         <v>1</v>
@@ -67287,7 +67287,7 @@
         <v>2.66</v>
       </c>
       <c r="DO139" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -69126,7 +69126,7 @@
         <v>86</v>
       </c>
       <c r="DD143" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE143" t="n">
         <v>0.22</v>
@@ -69159,7 +69159,7 @@
         <v>2.65</v>
       </c>
       <c r="DO143" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -69639,7 +69639,7 @@
         <v>3.6</v>
       </c>
       <c r="DO144" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -72983,7 +72983,7 @@
         <v>3.11</v>
       </c>
       <c r="DO151" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -75383,7 +75383,7 @@
         <v>3.02</v>
       </c>
       <c r="DO156" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -78203,7 +78203,7 @@
         <v>3.06</v>
       </c>
       <c r="DO162" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -80745,10 +80745,10 @@
         <v>6</v>
       </c>
       <c r="Y168" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z168" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
@@ -81159,40 +81159,40 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F169" s="2" t="n">
         <v>46047.75</v>
       </c>
       <c r="G169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J169" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L169" t="n">
         <v>7</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -81201,306 +81201,306 @@
         <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T169" t="n">
         <v>2</v>
       </c>
       <c r="U169" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X169" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y169" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="Z169" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="AA169" t="inlineStr"/>
       <c r="AB169" t="inlineStr"/>
       <c r="AC169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE169" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AF169" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU169" t="n">
         <v>4</v>
       </c>
-      <c r="AG169" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="AH169" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI169" t="n">
+      <c r="AV169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>78</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>54548</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS169" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV169" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW169" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX169" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY169" t="n">
+        <v>65</v>
+      </c>
+      <c r="BZ169" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CA169" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CB169" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CC169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR169" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS169" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU169" t="n">
+        <v>23</v>
+      </c>
+      <c r="CV169" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW169" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX169" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY169" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ169" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA169" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB169" t="n">
+        <v>53</v>
+      </c>
+      <c r="DC169" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DE169" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF169" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DG169" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH169" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI169" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ169" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK169" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL169" t="n">
         <v>1.94</v>
       </c>
-      <c r="AJ169" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AK169" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL169" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM169" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN169" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO169" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AP169" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ169" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR169" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AS169" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT169" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU169" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV169" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX169" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ169" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA169" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB169" t="n">
-        <v>1033</v>
-      </c>
-      <c r="BC169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD169" t="n">
-        <v>33</v>
-      </c>
-      <c r="BE169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF169" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG169" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH169" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ169" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK169" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL169" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM169" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN169" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR169" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT169" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU169" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV169" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW169" t="n">
-        <v>40</v>
-      </c>
-      <c r="BX169" t="n">
-        <v>106</v>
-      </c>
-      <c r="BY169" t="n">
-        <v>72</v>
-      </c>
-      <c r="BZ169" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="CA169" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="CB169" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CC169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI169" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ169" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN169" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP169" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ169" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR169" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS169" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT169" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU169" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV169" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW169" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX169" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY169" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ169" t="n">
-        <v>62</v>
-      </c>
-      <c r="DA169" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB169" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC169" t="n">
-        <v>73</v>
-      </c>
-      <c r="DD169" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DE169" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DF169" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DG169" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DH169" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DI169" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DJ169" t="n">
-        <v>39</v>
-      </c>
-      <c r="DK169" t="n">
-        <v>33</v>
-      </c>
-      <c r="DL169" t="n">
-        <v>1.56</v>
-      </c>
       <c r="DM169" t="n">
-        <v>1.2</v>
+        <v>0.93</v>
       </c>
       <c r="DN169" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="DO169" t="n">
         <v>19</v>
@@ -81515,7 +81515,7 @@
         <v>1</v>
       </c>
       <c r="DS169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT169" t="b">
         <v>0</v>
@@ -81527,14 +81527,14 @@
         <v>0</v>
       </c>
       <c r="DW169" t="n">
-        <v>12.42</v>
+        <v>12.26</v>
       </c>
       <c r="DX169" t="n">
-        <v>6.27</v>
+        <v>8.76</v>
       </c>
       <c r="DY169" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="DZ169" t="inlineStr">
@@ -81544,74 +81544,58 @@
       </c>
       <c r="EA169" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="EB169" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="EC169" t="inlineStr">
         <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="ED169" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="ED169" t="inlineStr"/>
       <c r="EE169" t="inlineStr"/>
       <c r="EF169" t="inlineStr"/>
-      <c r="EG169" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
+      <c r="EG169" t="inlineStr"/>
       <c r="EH169" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="EI169" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EJ169" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EK169" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EL169" t="inlineStr">
         <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EM169" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EN169" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EM169" t="inlineStr"/>
+      <c r="EN169" t="inlineStr"/>
       <c r="EO169" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EP169" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.54</t>
         </is>
       </c>
     </row>
@@ -81631,348 +81615,348 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F170" s="2" t="n">
         <v>46047.75</v>
       </c>
       <c r="G170" t="n">
+        <v>3</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>3</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="n">
         <v>4</v>
-      </c>
-      <c r="H170" t="n">
-        <v>0</v>
-      </c>
-      <c r="I170" t="n">
-        <v>4</v>
-      </c>
-      <c r="J170" t="n">
-        <v>6</v>
-      </c>
-      <c r="K170" t="n">
-        <v>1</v>
       </c>
       <c r="L170" t="n">
         <v>7</v>
       </c>
       <c r="M170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
         <v>4</v>
       </c>
-      <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>8</v>
-      </c>
       <c r="R170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T170" t="n">
         <v>2</v>
       </c>
       <c r="U170" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X170" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y170" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="Z170" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="AA170" t="inlineStr"/>
       <c r="AB170" t="inlineStr"/>
       <c r="AC170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF170" t="n">
         <v>4</v>
       </c>
-      <c r="AE170" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF170" t="n">
+      <c r="AG170" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>1033</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>2529</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV170" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW170" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX170" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY170" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ170" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CA170" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CB170" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR170" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS170" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU170" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV170" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW170" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX170" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY170" t="n">
         <v>7</v>
       </c>
-      <c r="AG170" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH170" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI170" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ170" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AK170" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL170" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM170" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN170" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO170" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AP170" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AQ170" t="n">
+      <c r="CZ170" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA170" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB170" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC170" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD170" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE170" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DF170" t="n">
         <v>1.22</v>
       </c>
-      <c r="AR170" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS170" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AT170" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AU170" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV170" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX170" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ170" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA170" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB170" t="n">
-        <v>78</v>
-      </c>
-      <c r="BC170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD170" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF170" t="n">
-        <v>54548</v>
-      </c>
-      <c r="BG170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH170" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI170" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ170" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM170" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO170" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS170" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU170" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV170" t="n">
-        <v>71</v>
-      </c>
-      <c r="BW170" t="n">
-        <v>17</v>
-      </c>
-      <c r="BX170" t="n">
-        <v>113</v>
-      </c>
-      <c r="BY170" t="n">
-        <v>65</v>
-      </c>
-      <c r="BZ170" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CA170" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="CB170" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CC170" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE170" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI170" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ170" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN170" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP170" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ170" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR170" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS170" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT170" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU170" t="n">
-        <v>23</v>
-      </c>
-      <c r="CV170" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW170" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX170" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY170" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ170" t="n">
-        <v>53</v>
-      </c>
-      <c r="DA170" t="n">
-        <v>82</v>
-      </c>
-      <c r="DB170" t="n">
-        <v>53</v>
-      </c>
-      <c r="DC170" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD170" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DE170" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF170" t="n">
-        <v>2.11</v>
-      </c>
       <c r="DG170" t="n">
-        <v>1.13</v>
+        <v>0.78</v>
       </c>
       <c r="DH170" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="DI170" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="DJ170" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="DK170" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="DL170" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="DM170" t="n">
-        <v>0.93</v>
+        <v>1.2</v>
       </c>
       <c r="DN170" t="n">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="DO170" t="n">
         <v>19</v>
@@ -81987,7 +81971,7 @@
         <v>1</v>
       </c>
       <c r="DS170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT170" t="b">
         <v>0</v>
@@ -81999,14 +81983,14 @@
         <v>0</v>
       </c>
       <c r="DW170" t="n">
-        <v>12.26</v>
+        <v>12.42</v>
       </c>
       <c r="DX170" t="n">
-        <v>8.76</v>
+        <v>6.27</v>
       </c>
       <c r="DY170" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="DZ170" t="inlineStr">
@@ -82016,58 +82000,74 @@
       </c>
       <c r="EA170" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="EB170" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="EC170" t="inlineStr">
         <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="ED170" t="inlineStr"/>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="ED170" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
       <c r="EE170" t="inlineStr"/>
       <c r="EF170" t="inlineStr"/>
-      <c r="EG170" t="inlineStr"/>
+      <c r="EG170" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
       <c r="EH170" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EI170" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EJ170" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="EK170" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EL170" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EM170" t="inlineStr"/>
-      <c r="EN170" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EM170" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EN170" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
       <c r="EO170" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EP170" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.82</t>
         </is>
       </c>
     </row>
@@ -82138,13 +82138,13 @@
         <v>10</v>
       </c>
       <c r="T171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U171" t="n">
         <v>17</v>
       </c>
       <c r="V171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W171" t="n">
         <v>9</v>
@@ -82311,10 +82311,10 @@
         <v>2.02</v>
       </c>
       <c r="CA171" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="CB171" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="CC171" t="n">
         <v>1</v>
@@ -82548,6 +82548,494 @@
       <c r="EP171" t="inlineStr">
         <is>
           <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Liga_Portugal_2025-2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>19</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>46048.84375</v>
+      </c>
+      <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>3</v>
+      </c>
+      <c r="J172" t="n">
+        <v>11</v>
+      </c>
+      <c r="K172" t="n">
+        <v>3</v>
+      </c>
+      <c r="L172" t="n">
+        <v>14</v>
+      </c>
+      <c r="M172" t="n">
+        <v>2</v>
+      </c>
+      <c r="N172" t="n">
+        <v>2</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>6</v>
+      </c>
+      <c r="R172" t="n">
+        <v>5</v>
+      </c>
+      <c r="S172" t="n">
+        <v>8</v>
+      </c>
+      <c r="T172" t="n">
+        <v>6</v>
+      </c>
+      <c r="U172" t="n">
+        <v>14</v>
+      </c>
+      <c r="V172" t="n">
+        <v>11</v>
+      </c>
+      <c r="W172" t="n">
+        <v>13</v>
+      </c>
+      <c r="X172" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>Estádio Do Dragão</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>Via Futebol Clube do Porto, Porto</t>
+        </is>
+      </c>
+      <c r="AC172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>82</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>35</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>34273</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV172" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW172" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX172" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY172" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ172" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CA172" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB172" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM172" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP172" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR172" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS172" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU172" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV172" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW172" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX172" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY172" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ172" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA172" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB172" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC172" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD172" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DE172" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF172" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DG172" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH172" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DI172" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DJ172" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK172" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL172" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DM172" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN172" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DO172" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR172" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS172" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT172" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU172" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV172" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW172" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="DX172" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="DY172" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="DZ172" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA172" t="inlineStr">
+        <is>
+          <t>9.61</t>
+        </is>
+      </c>
+      <c r="EB172" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="EC172" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="ED172" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EE172" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EF172" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EG172" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EH172" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI172" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EJ172" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EK172" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EL172" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EM172" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EN172" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EO172" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EP172" t="inlineStr">
+        <is>
+          <t>1.63</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -83112,19 +83112,19 @@
         <v>1</v>
       </c>
       <c r="R179" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
       </c>
       <c r="T179" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U179" t="n">
         <v>6</v>
       </c>
       <c r="V179" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W179" t="n">
         <v>19</v>
@@ -83302,7 +83302,7 @@
         <v>2.85</v>
       </c>
       <c r="CB179" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CC179" t="n">
         <v>0</v>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -87698,8 +87698,16 @@
       <c r="Z189" t="n">
         <v>34</v>
       </c>
-      <c r="AA189" t="inlineStr"/>
-      <c r="AB189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>Estádio Municipal 22 de Junho</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>Alameda dos Bargos, Vila Nova de Famalicão</t>
+        </is>
+      </c>
       <c r="AC189" t="n">
         <v>3</v>
       </c>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -100654,13 +100654,13 @@
         <v>8</v>
       </c>
       <c r="T217" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U217" t="n">
         <v>13</v>
       </c>
       <c r="V217" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W217" t="n">
         <v>16</v>
@@ -100835,10 +100835,10 @@
         <v>1.46</v>
       </c>
       <c r="CA217" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="CB217" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="CC217" t="n">
         <v>0</v>

--- a/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
+++ b/data/matches/leagues/Liga_Portugal_2025-2026.xlsx
@@ -103797,10 +103797,10 @@
         <v>17</v>
       </c>
       <c r="Y224" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z224" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA224" t="inlineStr"/>
       <c r="AB224" t="inlineStr"/>
@@ -105020,42 +105020,26 @@
       </c>
       <c r="DW226" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="DX226" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="DY226" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="DZ226" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EA226" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EB226" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EC226" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="DZ226" t="inlineStr"/>
+      <c r="EA226" t="inlineStr"/>
+      <c r="EB226" t="inlineStr"/>
+      <c r="EC226" t="inlineStr"/>
       <c r="ED226" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EE226" t="inlineStr">
@@ -105065,7 +105049,7 @@
       </c>
       <c r="EF226" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="EG226" t="inlineStr"/>
@@ -105074,12 +105058,12 @@
       <c r="EJ226" t="inlineStr"/>
       <c r="EK226" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EL226" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
